--- a/research/traditional_assets/database/data/new_zealand/new_zealand_green_renewable_energy.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_green_renewable_energy.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -590,49 +590,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0682</v>
+        <v>0.05825</v>
       </c>
       <c r="E2">
-        <v>0.0482</v>
+        <v>-0.1024</v>
       </c>
       <c r="F2">
         <v>0.07400000000000001</v>
       </c>
       <c r="G2">
-        <v>0.2007844728477717</v>
+        <v>0.2002797608213508</v>
       </c>
       <c r="H2">
-        <v>0.2007844728477717</v>
+        <v>0.2002797608213508</v>
       </c>
       <c r="I2">
-        <v>0.138601474267938</v>
+        <v>0.1372479624648613</v>
       </c>
       <c r="J2">
-        <v>0.1001010647490664</v>
+        <v>0.08387375483963749</v>
       </c>
       <c r="K2">
-        <v>261.3</v>
+        <v>261.389</v>
       </c>
       <c r="L2">
-        <v>0.08835463582876851</v>
+        <v>0.08810409799044094</v>
       </c>
       <c r="M2">
         <v>266.72</v>
       </c>
       <c r="N2">
-        <v>0.03091796399550234</v>
+        <v>0.03082399167918641</v>
       </c>
       <c r="O2">
-        <v>1.020742441637964</v>
+        <v>1.020394890374117</v>
       </c>
       <c r="P2">
         <v>265.5</v>
       </c>
       <c r="Q2">
-        <v>0.03077654259450311</v>
+        <v>0.03068300011556686</v>
       </c>
       <c r="R2">
-        <v>1.016073478760046</v>
+        <v>1.015727517225285</v>
       </c>
       <c r="S2">
         <v>1.220000000000027</v>
@@ -641,73 +641,73 @@
         <v>0.004574085182963509</v>
       </c>
       <c r="U2">
-        <v>134.6</v>
+        <v>138.57</v>
       </c>
       <c r="V2">
-        <v>0.01560272178237333</v>
+        <v>0.01601409915636196</v>
       </c>
       <c r="W2">
-        <v>0.07124550114516305</v>
+        <v>0.03760935771543867</v>
       </c>
       <c r="X2">
-        <v>0.07259822294604953</v>
+        <v>0.07174003031868814</v>
       </c>
       <c r="Y2">
-        <v>-0.001352721800886483</v>
+        <v>-0.03413067260324947</v>
       </c>
       <c r="Z2">
-        <v>0.6859488797142459</v>
+        <v>0.68397699927287</v>
       </c>
       <c r="AA2">
-        <v>0.06866421322282526</v>
+        <v>0.008475301787353395</v>
       </c>
       <c r="AB2">
-        <v>0.06976397564669747</v>
+        <v>0.07026710460971766</v>
       </c>
       <c r="AC2">
-        <v>-0.001099762423872205</v>
+        <v>-0.06179180282236427</v>
       </c>
       <c r="AD2">
-        <v>838.6</v>
+        <v>838.702</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>838.6</v>
+        <v>838.702</v>
       </c>
       <c r="AG2">
-        <v>704</v>
+        <v>700.1320000000001</v>
       </c>
       <c r="AH2">
-        <v>0.08859729749717388</v>
+        <v>0.08836160258718616</v>
       </c>
       <c r="AI2">
-        <v>0.1430935926968689</v>
+        <v>0.1423893442024569</v>
       </c>
       <c r="AJ2">
-        <v>0.07544985906737972</v>
+        <v>0.07485535326562269</v>
       </c>
       <c r="AK2">
-        <v>0.1229501039137952</v>
+        <v>0.1217275375058766</v>
       </c>
       <c r="AL2">
-        <v>44.5</v>
+        <v>44.662</v>
       </c>
       <c r="AM2">
-        <v>37.19</v>
+        <v>37.233</v>
       </c>
       <c r="AN2">
-        <v>1.412260020208825</v>
+        <v>1.411495235562796</v>
       </c>
       <c r="AO2">
-        <v>9.211235955056178</v>
+        <v>9.117146567551833</v>
       </c>
       <c r="AP2">
-        <v>1.185584371842371</v>
+        <v>1.178288572419109</v>
       </c>
       <c r="AQ2">
-        <v>11.02178004840011</v>
+        <v>10.93626621545403</v>
       </c>
     </row>
     <row r="3">
@@ -787,10 +787,10 @@
         <v>0.07124550114516305</v>
       </c>
       <c r="X3">
-        <v>0.07259822294604953</v>
+        <v>0.07258099407133946</v>
       </c>
       <c r="Y3">
-        <v>-0.001352721800886483</v>
+        <v>-0.001335492926176407</v>
       </c>
       <c r="Z3">
         <v>0.6859488797142459</v>
@@ -799,10 +799,10 @@
         <v>0.06866421322282526</v>
       </c>
       <c r="AB3">
-        <v>0.06976397564669747</v>
+        <v>0.06974827320372562</v>
       </c>
       <c r="AC3">
-        <v>-0.001099762423872205</v>
+        <v>-0.001084059980900359</v>
       </c>
       <c r="AD3">
         <v>838.6</v>
@@ -845,6 +845,137 @@
       </c>
       <c r="AQ3">
         <v>11.02178004840011</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NZ Windfarms Limited (NZSE:NWF)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Green &amp; Renewable Energy</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.0483</v>
+      </c>
+      <c r="E4">
+        <v>-0.253</v>
+      </c>
+      <c r="G4">
+        <v>0.04182590233545648</v>
+      </c>
+      <c r="H4">
+        <v>0.04182590233545648</v>
+      </c>
+      <c r="I4">
+        <v>-0.2876857749469214</v>
+      </c>
+      <c r="J4">
+        <v>-0.1438428874734607</v>
+      </c>
+      <c r="K4">
+        <v>0.089</v>
+      </c>
+      <c r="L4">
+        <v>0.009447983014861995</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>-0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>3.97</v>
+      </c>
+      <c r="V4">
+        <v>0.1509505703422053</v>
+      </c>
+      <c r="W4">
+        <v>0.003973214285714286</v>
+      </c>
+      <c r="X4">
+        <v>0.07089906656603681</v>
+      </c>
+      <c r="Y4">
+        <v>-0.06692585228032252</v>
+      </c>
+      <c r="Z4">
+        <v>0.3595145408747424</v>
+      </c>
+      <c r="AA4">
+        <v>-0.05171360964811847</v>
+      </c>
+      <c r="AB4">
+        <v>0.07078593601570972</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1224995456638282</v>
+      </c>
+      <c r="AD4">
+        <v>0.102</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0.102</v>
+      </c>
+      <c r="AG4">
+        <v>-3.868</v>
+      </c>
+      <c r="AH4">
+        <v>0.003863343686084387</v>
+      </c>
+      <c r="AI4">
+        <v>0.003434112180997912</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.172432239657632</v>
+      </c>
+      <c r="AK4">
+        <v>-0.1503186693611068</v>
+      </c>
+      <c r="AL4">
+        <v>0.162</v>
+      </c>
+      <c r="AM4">
+        <v>0.04300000000000001</v>
+      </c>
+      <c r="AN4">
+        <v>0.2588832487309645</v>
+      </c>
+      <c r="AO4">
+        <v>-16.7283950617284</v>
+      </c>
+      <c r="AP4">
+        <v>-9.817258883248732</v>
+      </c>
+      <c r="AQ4">
+        <v>-63.02325581395347</v>
       </c>
     </row>
   </sheetData>
@@ -1139,49 +1270,49 @@
         <v>8.773033707865171</v>
       </c>
       <c r="F2">
-        <v>3.09719839753525</v>
+        <v>2.54852885936585</v>
       </c>
       <c r="G2">
         <v>1.41226002020882</v>
       </c>
       <c r="H2">
-        <v>3.66624957898282</v>
+        <v>4.46326035702257</v>
       </c>
       <c r="I2">
         <v>0.0885972974971739</v>
       </c>
       <c r="J2">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="K2">
         <v>8626.700000000001</v>
       </c>
       <c r="L2">
-        <v>7702.4298976834</v>
+        <v>7400.63709266422</v>
       </c>
       <c r="M2">
         <v>9330.700000000001</v>
       </c>
       <c r="N2">
-        <v>9744.8488976834</v>
+        <v>9916.32109266422</v>
       </c>
       <c r="O2">
         <v>838.6</v>
       </c>
       <c r="P2">
-        <v>2177.019</v>
+        <v>2650.284</v>
       </c>
       <c r="Q2">
-        <v>0.06976397564669749</v>
+        <v>0.06974827320372561</v>
       </c>
       <c r="R2">
-        <v>0.0682866012526672</v>
+        <v>0.06769536787480609</v>
       </c>
       <c r="S2">
         <v>0.040608</v>
       </c>
       <c r="T2">
-        <v>0.041688</v>
+        <v>0.041616</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1190,20 +1321,20 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="W2">
-        <v>0.07259822294604951</v>
+        <v>0.0725809940713395</v>
       </c>
       <c r="X2">
-        <v>0.0762316379904768</v>
+        <v>0.077837344270564</v>
       </c>
       <c r="Y2">
         <v>0.618498708345022</v>
       </c>
       <c r="Z2">
-        <v>0.7023573476430029</v>
+        <v>0.739892477380231</v>
       </c>
       <c r="AA2">
         <v>838.6</v>
@@ -1236,7 +1367,7 @@
         <v>8626.700000000001</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.04330000000000001</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1555,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.0708452770977631</v>
+        <v>0.07082917521137813</v>
       </c>
       <c r="C2">
-        <v>9183.819231265106</v>
+        <v>9183.916071606847</v>
       </c>
       <c r="D2">
-        <v>9049.219231265106</v>
+        <v>9049.316071606847</v>
       </c>
       <c r="E2">
         <v>-838.6</v>
@@ -1475,19 +1606,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.0708452770977631</v>
+        <v>0.07082917521137813</v>
       </c>
       <c r="T2">
         <v>0.5780409979533054</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.28</v>
       </c>
       <c r="W2">
-        <v>0.037224</v>
+        <v>0.036216</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1637,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.07068939032188935</v>
+        <v>0.07066325352078627</v>
       </c>
       <c r="C3">
-        <v>9128.693881672263</v>
+        <v>9131.348596226577</v>
       </c>
       <c r="D3">
-        <v>9088.746881672263</v>
+        <v>9091.401596226577</v>
       </c>
       <c r="E3">
         <v>-743.947</v>
@@ -1539,37 +1670,37 @@
         <v>390.4</v>
       </c>
       <c r="M3">
-        <v>4.8935601</v>
+        <v>4.7610459</v>
       </c>
       <c r="N3">
-        <v>385.5064399</v>
+        <v>385.6389541</v>
       </c>
       <c r="O3">
-        <v>107.941803172</v>
+        <v>107.978907148</v>
       </c>
       <c r="P3">
-        <v>277.564636728</v>
+        <v>277.660046952</v>
       </c>
       <c r="Q3">
-        <v>480.964636728</v>
+        <v>481.060046952</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.07102742456756501</v>
+        <v>0.07101120557655179</v>
       </c>
       <c r="T3">
         <v>0.582244932483875</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.28</v>
       </c>
       <c r="W3">
-        <v>0.037224</v>
+        <v>0.036216</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1708,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>79.77831926494578</v>
+        <v>81.99878938365202</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1719,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.07053350354601563</v>
+        <v>0.07049733183019441</v>
       </c>
       <c r="C4">
-        <v>9073.915366403913</v>
+        <v>9079.174402970768</v>
       </c>
       <c r="D4">
-        <v>9128.621366403913</v>
+        <v>9133.880402970768</v>
       </c>
       <c r="E4">
         <v>-649.294</v>
@@ -1621,37 +1752,37 @@
         <v>390.4</v>
       </c>
       <c r="M4">
-        <v>9.7871202</v>
+        <v>9.5220918</v>
       </c>
       <c r="N4">
-        <v>380.6128798</v>
+        <v>380.8779082</v>
       </c>
       <c r="O4">
-        <v>106.571606344</v>
+        <v>106.645814296</v>
       </c>
       <c r="P4">
-        <v>274.041273456</v>
+        <v>274.232093904</v>
       </c>
       <c r="Q4">
-        <v>477.441273456</v>
+        <v>477.6320939039999</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.071213289332669</v>
+        <v>0.07119695084713715</v>
       </c>
       <c r="T4">
         <v>0.5865346615967009</v>
       </c>
       <c r="U4">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.28</v>
       </c>
       <c r="W4">
-        <v>0.037224</v>
+        <v>0.036216</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1790,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>39.88915963247289</v>
+        <v>40.99939469182601</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1801,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.07037761677014188</v>
+        <v>0.07033141013960255</v>
       </c>
       <c r="C5">
-        <v>9019.488270508698</v>
+        <v>9027.399030450728</v>
       </c>
       <c r="D5">
-        <v>9168.847270508699</v>
+        <v>9176.758030450728</v>
       </c>
       <c r="E5">
         <v>-554.6410000000001</v>
@@ -1703,37 +1834,37 @@
         <v>390.4</v>
       </c>
       <c r="M5">
-        <v>14.6806803</v>
+        <v>14.2831377</v>
       </c>
       <c r="N5">
-        <v>375.7193197</v>
+        <v>376.1168623</v>
       </c>
       <c r="O5">
-        <v>105.201409516</v>
+        <v>105.312721444</v>
       </c>
       <c r="P5">
-        <v>270.517910184</v>
+        <v>270.804140856</v>
       </c>
       <c r="Q5">
-        <v>473.917910184</v>
+        <v>474.204140856</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.07140298636097102</v>
+        <v>0.07138652591711603</v>
       </c>
       <c r="T5">
         <v>0.5909128387324718</v>
       </c>
       <c r="U5">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.28</v>
       </c>
       <c r="W5">
-        <v>0.037224</v>
+        <v>0.036216</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1872,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>26.59277308831526</v>
+        <v>27.33292979455068</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1883,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.07022172999426815</v>
+        <v>0.0701654884490107</v>
       </c>
       <c r="C6">
-        <v>8965.417260210275</v>
+        <v>8976.028121768994</v>
       </c>
       <c r="D6">
-        <v>9209.429260210274</v>
+        <v>9220.040121768992</v>
       </c>
       <c r="E6">
         <v>-459.988</v>
@@ -1785,37 +1916,37 @@
         <v>390.4</v>
       </c>
       <c r="M6">
-        <v>19.5742404</v>
+        <v>19.0441836</v>
       </c>
       <c r="N6">
-        <v>370.8257596</v>
+        <v>371.3558164</v>
       </c>
       <c r="O6">
-        <v>103.831212688</v>
+        <v>103.979628592</v>
       </c>
       <c r="P6">
-        <v>266.994546912</v>
+        <v>267.376187808</v>
       </c>
       <c r="Q6">
-        <v>470.394546912</v>
+        <v>470.776187808</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.071596635410696</v>
+        <v>0.07158005046771948</v>
       </c>
       <c r="T6">
         <v>0.5953822278919046</v>
       </c>
       <c r="U6">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.28</v>
       </c>
       <c r="W6">
-        <v>0.037224</v>
+        <v>0.036216</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1954,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>19.94457981623644</v>
+        <v>20.49969734591301</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1965,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.0700658432183944</v>
+        <v>0.06999956675841883</v>
       </c>
       <c r="C7">
-        <v>8911.707084711781</v>
+        <v>8925.067426995169</v>
       </c>
       <c r="D7">
-        <v>9250.37208471178</v>
+        <v>9263.732426995168</v>
       </c>
       <c r="E7">
         <v>-365.3349999999999</v>
@@ -1867,37 +1998,37 @@
         <v>390.4</v>
       </c>
       <c r="M7">
-        <v>24.46780050000001</v>
+        <v>23.8052295</v>
       </c>
       <c r="N7">
-        <v>365.9321995</v>
+        <v>366.5947705</v>
       </c>
       <c r="O7">
-        <v>102.46101586</v>
+        <v>102.64653574</v>
       </c>
       <c r="P7">
-        <v>263.4711836399999</v>
+        <v>263.94823476</v>
       </c>
       <c r="Q7">
-        <v>466.8711836399999</v>
+        <v>467.34823476</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.07179436128252044</v>
+        <v>0.07177764921938824</v>
       </c>
       <c r="T7">
         <v>0.5999457094546938</v>
       </c>
       <c r="U7">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.28</v>
       </c>
       <c r="W7">
-        <v>0.037224</v>
+        <v>0.036216</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +2036,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>15.95566385298915</v>
+        <v>16.3997578767304</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +2047,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.06990995644252068</v>
+        <v>0.06983364506782698</v>
       </c>
       <c r="C8">
-        <v>8858.362578048571</v>
+        <v>8874.52280571248</v>
       </c>
       <c r="D8">
-        <v>9291.68057804857</v>
+        <v>9307.84080571248</v>
       </c>
       <c r="E8">
         <v>-270.682</v>
@@ -1949,37 +2080,37 @@
         <v>390.4</v>
       </c>
       <c r="M8">
-        <v>29.3613606</v>
+        <v>28.5662754</v>
       </c>
       <c r="N8">
-        <v>361.0386394</v>
+        <v>361.8337246</v>
       </c>
       <c r="O8">
-        <v>101.090819032</v>
+        <v>101.313442888</v>
       </c>
       <c r="P8">
-        <v>259.947820368</v>
+        <v>260.520281712</v>
       </c>
       <c r="Q8">
-        <v>463.3478203679999</v>
+        <v>463.920281712</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07199629408778796</v>
+        <v>0.07197945219981594</v>
       </c>
       <c r="T8">
         <v>0.6046062863698829</v>
       </c>
       <c r="U8">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.28</v>
       </c>
       <c r="W8">
-        <v>0.037224</v>
+        <v>0.036216</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +2118,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>13.29638654415763</v>
+        <v>13.66646489727534</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +2129,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.06975406966664693</v>
+        <v>0.06966772337723511</v>
       </c>
       <c r="C9">
-        <v>8805.388660990884</v>
+        <v>8824.400229637471</v>
       </c>
       <c r="D9">
-        <v>9333.359660990884</v>
+        <v>9352.371229637471</v>
       </c>
       <c r="E9">
         <v>-176.0289999999999</v>
@@ -2031,37 +2162,37 @@
         <v>390.4</v>
       </c>
       <c r="M9">
-        <v>34.25492070000001</v>
+        <v>33.32732130000001</v>
       </c>
       <c r="N9">
-        <v>356.1450793</v>
+        <v>357.0726787</v>
       </c>
       <c r="O9">
-        <v>99.72062220399999</v>
+        <v>99.980350036</v>
       </c>
       <c r="P9">
-        <v>256.424457096</v>
+        <v>257.092328664</v>
       </c>
       <c r="Q9">
-        <v>459.8244570959999</v>
+        <v>460.492328664</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07220256953402897</v>
+        <v>0.07218559502928507</v>
       </c>
       <c r="T9">
         <v>0.6093670907456136</v>
       </c>
       <c r="U9">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.28</v>
       </c>
       <c r="W9">
-        <v>0.037224</v>
+        <v>0.036216</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2200,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.39690275213511</v>
+        <v>11.71411276909314</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2211,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.0695981828907732</v>
+        <v>0.06950180168664326</v>
       </c>
       <c r="C10">
-        <v>8752.790342997871</v>
+        <v>8774.705785315191</v>
       </c>
       <c r="D10">
-        <v>9375.41434299787</v>
+        <v>9397.329785315191</v>
       </c>
       <c r="E10">
         <v>-81.37599999999998</v>
@@ -2113,37 +2244,37 @@
         <v>390.4</v>
       </c>
       <c r="M10">
-        <v>39.1484808</v>
+        <v>38.0883672</v>
       </c>
       <c r="N10">
-        <v>351.2515192</v>
+        <v>352.3116328</v>
       </c>
       <c r="O10">
-        <v>98.350425376</v>
+        <v>98.64725718400001</v>
       </c>
       <c r="P10">
-        <v>252.901093824</v>
+        <v>253.664375616</v>
       </c>
       <c r="Q10">
-        <v>456.301093824</v>
+        <v>457.064375616</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07241332922910131</v>
+        <v>0.07239621922461223</v>
       </c>
       <c r="T10">
         <v>0.6142313908686428</v>
       </c>
       <c r="U10">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.28</v>
       </c>
       <c r="W10">
-        <v>0.037224</v>
+        <v>0.036216</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2282,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>9.972289908118221</v>
+        <v>10.2498486729565</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2293,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.06944229611489948</v>
+        <v>0.06933587999605141</v>
       </c>
       <c r="C11">
-        <v>8700.572724224761</v>
+        <v>8725.44567689257</v>
       </c>
       <c r="D11">
-        <v>9417.849724224761</v>
+        <v>9442.72267689257</v>
       </c>
       <c r="E11">
         <v>13.27700000000004</v>
@@ -2195,37 +2326,37 @@
         <v>390.4</v>
       </c>
       <c r="M11">
-        <v>44.0420409</v>
+        <v>42.8494131</v>
       </c>
       <c r="N11">
-        <v>346.3579591</v>
+        <v>347.5505869</v>
       </c>
       <c r="O11">
-        <v>96.980228548</v>
+        <v>97.314164332</v>
       </c>
       <c r="P11">
-        <v>249.3777305519999</v>
+        <v>250.236422568</v>
       </c>
       <c r="Q11">
-        <v>452.777730552</v>
+        <v>453.6364225679999</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.07262872100538403</v>
+        <v>0.07261147252313341</v>
       </c>
       <c r="T11">
         <v>0.6192025986866837</v>
       </c>
       <c r="U11">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.28</v>
       </c>
       <c r="W11">
-        <v>0.037224</v>
+        <v>0.036216</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2364,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>8.864257696105085</v>
+        <v>9.110976598183559</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2375,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.06936560933902573</v>
+        <v>0.06927795830545955</v>
       </c>
       <c r="C12">
-        <v>8626.936625857021</v>
+        <v>8646.74234415202</v>
       </c>
       <c r="D12">
-        <v>9438.866625857021</v>
+        <v>9458.672344152021</v>
       </c>
       <c r="E12">
         <v>107.9300000000002</v>
@@ -2277,37 +2408,37 @@
         <v>390.4</v>
       </c>
       <c r="M12">
-        <v>49.97678400000001</v>
+        <v>49.03025400000001</v>
       </c>
       <c r="N12">
-        <v>340.423216</v>
+        <v>341.369746</v>
       </c>
       <c r="O12">
-        <v>95.31850048</v>
+        <v>95.58352888</v>
       </c>
       <c r="P12">
-        <v>245.10471552</v>
+        <v>245.7862171199999</v>
       </c>
       <c r="Q12">
-        <v>448.50471552</v>
+        <v>449.1862171199999</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.07284889926558415</v>
+        <v>0.07283150922828838</v>
       </c>
       <c r="T12">
         <v>0.62428427778957</v>
       </c>
       <c r="U12">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.28</v>
       </c>
       <c r="W12">
-        <v>0.038016</v>
+        <v>0.037296</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2446,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>7.811627094692605</v>
+        <v>7.962430706559259</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2457,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.06921764256315199</v>
+        <v>0.06912283661486769</v>
       </c>
       <c r="C13">
-        <v>8573.10189344325</v>
+        <v>8595.071175103172</v>
       </c>
       <c r="D13">
-        <v>9479.684893443251</v>
+        <v>9501.654175103173</v>
       </c>
       <c r="E13">
         <v>202.5830000000002</v>
@@ -2359,37 +2490,37 @@
         <v>390.4</v>
       </c>
       <c r="M13">
-        <v>54.97446240000001</v>
+        <v>53.93327940000001</v>
       </c>
       <c r="N13">
-        <v>335.4255376</v>
+        <v>336.4667206</v>
       </c>
       <c r="O13">
-        <v>93.919150528</v>
+        <v>94.210681768</v>
       </c>
       <c r="P13">
-        <v>241.506387072</v>
+        <v>242.256038832</v>
       </c>
       <c r="Q13">
-        <v>444.906387072</v>
+        <v>445.656038832</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.07307402535185617</v>
+        <v>0.07305649057850301</v>
       </c>
       <c r="T13">
         <v>0.629480151928476</v>
       </c>
       <c r="U13">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.28</v>
       </c>
       <c r="W13">
-        <v>0.038016</v>
+        <v>0.037296</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2528,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>7.101479176993278</v>
+        <v>7.238573369599326</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2539,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.06925975578727825</v>
+        <v>0.06911459492427582</v>
       </c>
       <c r="C14">
-        <v>8466.795599574114</v>
+        <v>8502.712751876436</v>
       </c>
       <c r="D14">
-        <v>9468.031599574113</v>
+        <v>9503.948751876434</v>
       </c>
       <c r="E14">
         <v>297.236</v>
@@ -2441,37 +2572,37 @@
         <v>390.4</v>
       </c>
       <c r="M14">
-        <v>62.47098</v>
+        <v>60.767226</v>
       </c>
       <c r="N14">
-        <v>327.92902</v>
+        <v>329.632774</v>
       </c>
       <c r="O14">
-        <v>91.8201256</v>
+        <v>92.29717672000001</v>
       </c>
       <c r="P14">
-        <v>236.1088944</v>
+        <v>237.33559728</v>
       </c>
       <c r="Q14">
-        <v>439.5088944</v>
+        <v>440.73559728</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.07330426794008893</v>
+        <v>0.07328658514122252</v>
       </c>
       <c r="T14">
         <v>0.6347941141159936</v>
       </c>
       <c r="U14">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.28</v>
       </c>
       <c r="W14">
-        <v>0.0396</v>
+        <v>0.03852</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2610,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>6.249301675754086</v>
+        <v>6.424515741429434</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2621,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.06912762901140451</v>
+        <v>0.06897171323368397</v>
       </c>
       <c r="C15">
-        <v>8408.800287277274</v>
+        <v>8448.016466913685</v>
       </c>
       <c r="D15">
-        <v>9504.689287277273</v>
+        <v>9543.905466913684</v>
       </c>
       <c r="E15">
         <v>391.8890000000002</v>
@@ -2523,37 +2654,37 @@
         <v>390.4</v>
       </c>
       <c r="M15">
-        <v>67.67689500000002</v>
+        <v>65.83116150000001</v>
       </c>
       <c r="N15">
-        <v>322.723105</v>
+        <v>324.5688385</v>
       </c>
       <c r="O15">
-        <v>90.36246939999999</v>
+        <v>90.87927478</v>
       </c>
       <c r="P15">
-        <v>232.3606356</v>
+        <v>233.68956372</v>
       </c>
       <c r="Q15">
-        <v>435.7606356</v>
+        <v>437.08956372</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.0735398034613845</v>
+        <v>0.07352196923411949</v>
       </c>
       <c r="T15">
         <v>0.6402302363537989</v>
       </c>
       <c r="U15">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.28</v>
       </c>
       <c r="W15">
-        <v>0.0396</v>
+        <v>0.03852</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2692,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.76858616223454</v>
+        <v>5.930322222857939</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2703,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.06914670223553078</v>
+        <v>0.0689094715430921</v>
       </c>
       <c r="C16">
-        <v>8308.838028360629</v>
+        <v>8370.874538729113</v>
       </c>
       <c r="D16">
-        <v>9499.380028360629</v>
+        <v>9561.416538729112</v>
       </c>
       <c r="E16">
         <v>486.5420000000003</v>
@@ -2605,37 +2736,37 @@
         <v>390.4</v>
       </c>
       <c r="M16">
-        <v>74.87052300000002</v>
+        <v>71.95521060000002</v>
       </c>
       <c r="N16">
-        <v>315.5294769999999</v>
+        <v>318.4447894</v>
       </c>
       <c r="O16">
-        <v>88.34825355999999</v>
+        <v>89.164541032</v>
       </c>
       <c r="P16">
-        <v>227.1812234399999</v>
+        <v>229.280248368</v>
       </c>
       <c r="Q16">
-        <v>430.5812234399999</v>
+        <v>432.680248368</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.07378081655294277</v>
+        <v>0.0737628273756885</v>
       </c>
       <c r="T16">
         <v>0.6457927800389952</v>
       </c>
       <c r="U16">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.28</v>
       </c>
       <c r="W16">
-        <v>0.04068</v>
+        <v>0.039096</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2774,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.214335152968009</v>
+        <v>5.425597350694154</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2785,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.06902537545965703</v>
+        <v>0.06877234985250025</v>
       </c>
       <c r="C17">
-        <v>8248.059279479428</v>
+        <v>8315.026982483922</v>
       </c>
       <c r="D17">
-        <v>9533.254279479428</v>
+        <v>9600.221982483921</v>
       </c>
       <c r="E17">
         <v>581.1950000000001</v>
@@ -2687,37 +2818,37 @@
         <v>390.4</v>
       </c>
       <c r="M17">
-        <v>80.2184175</v>
+        <v>77.0948685</v>
       </c>
       <c r="N17">
-        <v>310.1815825</v>
+        <v>313.3051315</v>
       </c>
       <c r="O17">
-        <v>86.85084310000001</v>
+        <v>87.72543682</v>
       </c>
       <c r="P17">
-        <v>223.3307394</v>
+        <v>225.57969468</v>
       </c>
       <c r="Q17">
-        <v>426.7307393999999</v>
+        <v>428.97969468</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.07402750054077299</v>
+        <v>0.07400935276764735</v>
       </c>
       <c r="T17">
         <v>0.6514862071050195</v>
       </c>
       <c r="U17">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V17">
         <v>0.28</v>
       </c>
       <c r="W17">
-        <v>0.04068</v>
+        <v>0.039096</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2856,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>4.866712809436811</v>
+        <v>5.063890860647877</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2867,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.06890404868378332</v>
+        <v>0.06863522816190838</v>
       </c>
       <c r="C18">
-        <v>8187.522982489507</v>
+        <v>8259.495697154347</v>
       </c>
       <c r="D18">
-        <v>9567.370982489507</v>
+        <v>9639.343697154347</v>
       </c>
       <c r="E18">
         <v>675.8480000000001</v>
@@ -2769,37 +2900,37 @@
         <v>390.4</v>
       </c>
       <c r="M18">
-        <v>85.56631200000001</v>
+        <v>82.23452640000001</v>
       </c>
       <c r="N18">
-        <v>304.8336879999999</v>
+        <v>308.1654736</v>
       </c>
       <c r="O18">
-        <v>85.35343263999999</v>
+        <v>86.28633260800001</v>
       </c>
       <c r="P18">
-        <v>219.4802553599999</v>
+        <v>221.879140992</v>
       </c>
       <c r="Q18">
-        <v>422.88025536</v>
+        <v>425.279140992</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.0742800579568849</v>
+        <v>0.0742617478117957</v>
       </c>
       <c r="T18">
         <v>0.6573151919583302</v>
       </c>
       <c r="U18">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.28</v>
       </c>
       <c r="W18">
-        <v>0.04068</v>
+        <v>0.039096</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2938,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.562543258847009</v>
+        <v>4.747397681857386</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2949,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.06878272190790957</v>
+        <v>0.06849810647131653</v>
       </c>
       <c r="C19">
-        <v>8127.231749730934</v>
+        <v>8204.284565053136</v>
       </c>
       <c r="D19">
-        <v>9601.732749730934</v>
+        <v>9678.785565053136</v>
       </c>
       <c r="E19">
         <v>770.5010000000003</v>
@@ -2851,37 +2982,37 @@
         <v>390.4</v>
       </c>
       <c r="M19">
-        <v>90.91420650000002</v>
+        <v>87.37418430000002</v>
       </c>
       <c r="N19">
-        <v>299.4857934999999</v>
+        <v>303.0258157</v>
       </c>
       <c r="O19">
-        <v>83.85602218</v>
+        <v>84.84722839599999</v>
       </c>
       <c r="P19">
-        <v>215.6297713199999</v>
+        <v>218.178587304</v>
       </c>
       <c r="Q19">
-        <v>419.02977132</v>
+        <v>421.5785873039999</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07453870109386695</v>
+        <v>0.07452022466423679</v>
       </c>
       <c r="T19">
         <v>0.6632846342779857</v>
       </c>
       <c r="U19">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.28</v>
       </c>
       <c r="W19">
-        <v>0.04068</v>
+        <v>0.039096</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +3020,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>4.294158361267773</v>
+        <v>4.468138994689303</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +3031,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.06884283513203585</v>
+        <v>0.06849058478072467</v>
       </c>
       <c r="C20">
-        <v>8015.522885949665</v>
+        <v>8111.804454698921</v>
       </c>
       <c r="D20">
-        <v>9584.676885949664</v>
+        <v>9680.958454698921</v>
       </c>
       <c r="E20">
         <v>865.1540000000001</v>
@@ -2933,37 +3064,37 @@
         <v>390.4</v>
       </c>
       <c r="M20">
-        <v>98.64735660000001</v>
+        <v>94.21759620000002</v>
       </c>
       <c r="N20">
-        <v>291.7526434</v>
+        <v>296.1824038</v>
       </c>
       <c r="O20">
-        <v>81.69074015199999</v>
+        <v>82.931073064</v>
       </c>
       <c r="P20">
-        <v>210.061903248</v>
+        <v>213.251330736</v>
       </c>
       <c r="Q20">
-        <v>413.461903248</v>
+        <v>416.651330736</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.07480365260004371</v>
+        <v>0.07478500583015203</v>
       </c>
       <c r="T20">
         <v>0.669399672751779</v>
       </c>
       <c r="U20">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.28</v>
       </c>
       <c r="W20">
-        <v>0.041688</v>
+        <v>0.039816</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +3102,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.95753128573949</v>
+        <v>4.143599664454186</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +3113,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.06873158835616211</v>
+        <v>0.06836066309013282</v>
       </c>
       <c r="C21">
-        <v>7952.481670142136</v>
+        <v>8054.83820835495</v>
       </c>
       <c r="D21">
-        <v>9616.288670142136</v>
+        <v>9718.64520835495</v>
       </c>
       <c r="E21">
         <v>959.8070000000001</v>
@@ -3015,37 +3146,37 @@
         <v>390.4</v>
       </c>
       <c r="M21">
-        <v>104.1277653</v>
+        <v>99.45190710000001</v>
       </c>
       <c r="N21">
-        <v>286.2722347</v>
+        <v>290.9480928999999</v>
       </c>
       <c r="O21">
-        <v>80.15622571599999</v>
+        <v>81.46546601199999</v>
       </c>
       <c r="P21">
-        <v>206.116008984</v>
+        <v>209.482626888</v>
       </c>
       <c r="Q21">
-        <v>409.516008984</v>
+        <v>412.882626888</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07507514611871864</v>
+        <v>0.07505632480263311</v>
       </c>
       <c r="T21">
         <v>0.6756656998298637</v>
       </c>
       <c r="U21">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V21">
         <v>0.28</v>
       </c>
       <c r="W21">
-        <v>0.041688</v>
+        <v>0.039816</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3184,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.749240165437411</v>
+        <v>3.925515471588175</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3195,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.06862034158028837</v>
+        <v>0.06823074139954097</v>
       </c>
       <c r="C22">
-        <v>7889.649665700629</v>
+        <v>7998.166528304485</v>
       </c>
       <c r="D22">
-        <v>9648.109665700629</v>
+        <v>9756.626528304485</v>
       </c>
       <c r="E22">
         <v>1054.46</v>
@@ -3097,37 +3228,37 @@
         <v>390.4</v>
       </c>
       <c r="M22">
-        <v>109.608174</v>
+        <v>104.686218</v>
       </c>
       <c r="N22">
-        <v>280.791826</v>
+        <v>285.7137819999999</v>
       </c>
       <c r="O22">
-        <v>78.62171128</v>
+        <v>79.99985895999998</v>
       </c>
       <c r="P22">
-        <v>202.17011472</v>
+        <v>205.7139230399999</v>
       </c>
       <c r="Q22">
-        <v>405.57011472</v>
+        <v>409.1139230399999</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.07535342697536046</v>
+        <v>0.0753344267494262</v>
       </c>
       <c r="T22">
         <v>0.6820883775849004</v>
       </c>
       <c r="U22">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V22">
         <v>0.28</v>
       </c>
       <c r="W22">
-        <v>0.041688</v>
+        <v>0.039816</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3266,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.56177815716554</v>
+        <v>3.729239698008766</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3277,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.06850909480441464</v>
+        <v>0.0681008197089491</v>
       </c>
       <c r="C23">
-        <v>7827.028956407217</v>
+        <v>7941.792881670275</v>
       </c>
       <c r="D23">
-        <v>9680.141956407217</v>
+        <v>9794.905881670275</v>
       </c>
       <c r="E23">
         <v>1149.113</v>
@@ -3179,37 +3310,37 @@
         <v>390.4</v>
       </c>
       <c r="M23">
-        <v>115.0885827</v>
+        <v>109.9205289</v>
       </c>
       <c r="N23">
-        <v>275.3114173</v>
+        <v>280.4794711</v>
       </c>
       <c r="O23">
-        <v>77.08719684399999</v>
+        <v>78.534251908</v>
       </c>
       <c r="P23">
-        <v>198.224220456</v>
+        <v>201.945219192</v>
       </c>
       <c r="Q23">
-        <v>401.624220456</v>
+        <v>405.3452191919999</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.07563875291698055</v>
+        <v>0.0756195692518343</v>
       </c>
       <c r="T23">
         <v>0.6886736547767736</v>
       </c>
       <c r="U23">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V23">
         <v>0.28</v>
       </c>
       <c r="W23">
-        <v>0.041688</v>
+        <v>0.039816</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3348,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.392169673490991</v>
+        <v>3.551656855246445</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3359,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.06839784802854089</v>
+        <v>0.06797089801835723</v>
       </c>
       <c r="C24">
-        <v>7764.621653809261</v>
+        <v>7885.720790201305</v>
       </c>
       <c r="D24">
-        <v>9712.387653809261</v>
+        <v>9833.486790201305</v>
       </c>
       <c r="E24">
         <v>1243.766000000001</v>
@@ -3261,37 +3392,37 @@
         <v>390.4</v>
       </c>
       <c r="M24">
-        <v>120.5689914</v>
+        <v>115.1548398</v>
       </c>
       <c r="N24">
-        <v>269.8310086</v>
+        <v>275.2451601999999</v>
       </c>
       <c r="O24">
-        <v>75.552682408</v>
+        <v>77.06864485599999</v>
       </c>
       <c r="P24">
-        <v>194.278326192</v>
+        <v>198.1765153439999</v>
       </c>
       <c r="Q24">
-        <v>397.678326192</v>
+        <v>401.576515344</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.07593139490838575</v>
+        <v>0.075912023100458</v>
       </c>
       <c r="T24">
         <v>0.6954277852299767</v>
       </c>
       <c r="U24">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.28</v>
       </c>
       <c r="W24">
-        <v>0.041688</v>
+        <v>0.039816</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3430,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.237980142877764</v>
+        <v>3.390217907280697</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3441,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.06828660125266717</v>
+        <v>0.06784097632776537</v>
       </c>
       <c r="C25">
-        <v>7702.429897683403</v>
+        <v>7829.953831352901</v>
       </c>
       <c r="D25">
-        <v>9744.848897683403</v>
+        <v>9872.372831352901</v>
       </c>
       <c r="E25">
         <v>1338.419</v>
@@ -3343,37 +3474,37 @@
         <v>390.4</v>
       </c>
       <c r="M25">
-        <v>126.0494001</v>
+        <v>120.3891507</v>
       </c>
       <c r="N25">
-        <v>264.3505999</v>
+        <v>270.0108493</v>
       </c>
       <c r="O25">
-        <v>74.018167972</v>
+        <v>75.603037804</v>
       </c>
       <c r="P25">
-        <v>190.3324319279999</v>
+        <v>194.407811496</v>
       </c>
       <c r="Q25">
-        <v>393.732431928</v>
+        <v>397.807811496</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.07623163799047683</v>
+        <v>0.07621207315294204</v>
       </c>
       <c r="T25">
         <v>0.7023573476430033</v>
       </c>
       <c r="U25">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V25">
         <v>0.28</v>
       </c>
       <c r="W25">
-        <v>0.041688</v>
+        <v>0.039816</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3512,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.097198397535253</v>
+        <v>3.242817128703276</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3523,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.06862463447679343</v>
+        <v>0.06771105463717352</v>
       </c>
       <c r="C26">
-        <v>7509.805820787476</v>
+        <v>7774.495639392535</v>
       </c>
       <c r="D26">
-        <v>9646.877820787477</v>
+        <v>9911.567639392535</v>
       </c>
       <c r="E26">
         <v>1433.072</v>
@@ -3425,45 +3556,45 @@
         <v>390.4</v>
       </c>
       <c r="M26">
-        <v>137.436156</v>
+        <v>125.6234616</v>
       </c>
       <c r="N26">
-        <v>252.963844</v>
+        <v>264.7765384</v>
       </c>
       <c r="O26">
-        <v>70.82987632</v>
+        <v>74.137430752</v>
       </c>
       <c r="P26">
-        <v>182.13396768</v>
+        <v>190.639107648</v>
       </c>
       <c r="Q26">
-        <v>385.5339676799999</v>
+        <v>394.039107648</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.07653978220630714</v>
+        <v>0.07652001925943884</v>
       </c>
       <c r="T26">
         <v>0.709469266961636</v>
       </c>
       <c r="U26">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V26">
         <v>0.28</v>
       </c>
       <c r="W26">
-        <v>0.04355999999999999</v>
+        <v>0.039816</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.840591670797312</v>
+        <v>3.107699748340639</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3605,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.06853210770091968</v>
+        <v>0.06803113294658165</v>
       </c>
       <c r="C27">
-        <v>7441.773208078333</v>
+        <v>7583.836999724557</v>
       </c>
       <c r="D27">
-        <v>9673.498208078334</v>
+        <v>9815.561999724558</v>
       </c>
       <c r="E27">
         <v>1527.725</v>
@@ -3507,37 +3638,37 @@
         <v>390.4</v>
       </c>
       <c r="M27">
-        <v>143.1626625</v>
+        <v>136.773585</v>
       </c>
       <c r="N27">
-        <v>247.2373375</v>
+        <v>253.626415</v>
       </c>
       <c r="O27">
-        <v>69.2264545</v>
+        <v>71.0153962</v>
       </c>
       <c r="P27">
-        <v>178.010883</v>
+        <v>182.6110188</v>
       </c>
       <c r="Q27">
-        <v>381.410883</v>
+        <v>386.0110188</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.07685614360122624</v>
+        <v>0.07683617726210888</v>
       </c>
       <c r="T27">
         <v>0.7167708374620987</v>
       </c>
       <c r="U27">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V27">
         <v>0.28</v>
       </c>
       <c r="W27">
-        <v>0.04355999999999999</v>
+        <v>0.041616</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3676,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.726968003965419</v>
+        <v>2.854352322489755</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3687,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.06843958092504596</v>
+        <v>0.06791921125598981</v>
       </c>
       <c r="C28">
-        <v>7373.887918873659</v>
+        <v>7522.5420782649</v>
       </c>
       <c r="D28">
-        <v>9700.26591887366</v>
+        <v>9848.9200782649</v>
       </c>
       <c r="E28">
         <v>1622.378000000001</v>
@@ -3589,37 +3720,37 @@
         <v>390.4</v>
       </c>
       <c r="M28">
-        <v>148.889169</v>
+        <v>142.2445284</v>
       </c>
       <c r="N28">
-        <v>241.5108309999999</v>
+        <v>248.1554715999999</v>
       </c>
       <c r="O28">
-        <v>67.62303267999999</v>
+        <v>69.48353204799999</v>
       </c>
       <c r="P28">
-        <v>173.8877983199999</v>
+        <v>178.671939552</v>
       </c>
       <c r="Q28">
-        <v>377.28779832</v>
+        <v>382.071939552</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.07718105530411615</v>
+        <v>0.07716088007566189</v>
       </c>
       <c r="T28">
         <v>0.7242697477058173</v>
       </c>
       <c r="U28">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V28">
         <v>0.28</v>
       </c>
       <c r="W28">
-        <v>0.04355999999999999</v>
+        <v>0.041616</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3758,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.622084619197518</v>
+        <v>2.744569540855533</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3769,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.06834705414917221</v>
+        <v>0.06780728956539794</v>
       </c>
       <c r="C29">
-        <v>7306.151179551548</v>
+        <v>7461.474664105827</v>
       </c>
       <c r="D29">
-        <v>9727.182179551548</v>
+        <v>9882.505664105827</v>
       </c>
       <c r="E29">
         <v>1717.031</v>
@@ -3671,37 +3802,37 @@
         <v>390.4</v>
       </c>
       <c r="M29">
-        <v>154.6156755</v>
+        <v>147.7154718</v>
       </c>
       <c r="N29">
-        <v>235.7843245</v>
+        <v>242.6845282</v>
       </c>
       <c r="O29">
-        <v>66.01961086</v>
+        <v>67.95166789599999</v>
       </c>
       <c r="P29">
-        <v>169.76471364</v>
+        <v>174.732860304</v>
       </c>
       <c r="Q29">
-        <v>373.1647136399999</v>
+        <v>378.132860304</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.07751486869749617</v>
+        <v>0.07749447885670951</v>
       </c>
       <c r="T29">
         <v>0.7319741075452542</v>
       </c>
       <c r="U29">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V29">
         <v>0.28</v>
       </c>
       <c r="W29">
-        <v>0.04355999999999999</v>
+        <v>0.041616</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3840,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.524970374042055</v>
+        <v>2.642918817120144</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3851,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.06879884737329847</v>
+        <v>0.06769536787480608</v>
       </c>
       <c r="C30">
-        <v>7081.467533085907</v>
+        <v>7400.637092664217</v>
       </c>
       <c r="D30">
-        <v>9597.151533085907</v>
+        <v>9916.321092664217</v>
       </c>
       <c r="E30">
         <v>1811.684000000001</v>
@@ -3753,45 +3884,45 @@
         <v>390.4</v>
       </c>
       <c r="M30">
-        <v>167.4979488</v>
+        <v>153.1864152000001</v>
       </c>
       <c r="N30">
-        <v>222.9020511999999</v>
+        <v>237.2135847999999</v>
       </c>
       <c r="O30">
-        <v>62.41257433599998</v>
+        <v>66.41980374399998</v>
       </c>
       <c r="P30">
-        <v>160.489476864</v>
+        <v>170.7937810559999</v>
       </c>
       <c r="Q30">
-        <v>363.889476864</v>
+        <v>374.1937810559999</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.07785795468513676</v>
+        <v>0.077837344270564</v>
       </c>
       <c r="T30">
         <v>0.739892477380231</v>
       </c>
       <c r="U30">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V30">
         <v>0.28</v>
       </c>
       <c r="W30">
-        <v>0.045504</v>
+        <v>0.041616</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.330774811255479</v>
+        <v>2.548528859365852</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3933,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.06872576059742473</v>
+        <v>0.06831424618421422</v>
       </c>
       <c r="C31">
-        <v>7007.613429744784</v>
+        <v>7121.843732017476</v>
       </c>
       <c r="D31">
-        <v>9617.950429744784</v>
+        <v>9732.180732017476</v>
       </c>
       <c r="E31">
         <v>1906.337</v>
@@ -3835,37 +3966,37 @@
         <v>390.4</v>
       </c>
       <c r="M31">
-        <v>173.4800184</v>
+        <v>168.2646381</v>
       </c>
       <c r="N31">
-        <v>216.9199815999999</v>
+        <v>222.1353619</v>
       </c>
       <c r="O31">
-        <v>60.73759484799999</v>
+        <v>62.19790133199999</v>
       </c>
       <c r="P31">
-        <v>156.182386752</v>
+        <v>159.937460568</v>
       </c>
       <c r="Q31">
-        <v>359.5823867519999</v>
+        <v>363.337460568</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.07821070506679539</v>
+        <v>0.07818986786509045</v>
       </c>
       <c r="T31">
         <v>0.7480338998866155</v>
       </c>
       <c r="U31">
-        <v>0.06320000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="V31">
         <v>0.28</v>
       </c>
       <c r="W31">
-        <v>0.045504</v>
+        <v>0.044136</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +4004,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.250403266039773</v>
+        <v>2.320154753894187</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +4015,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.069667873821551</v>
+        <v>0.06883232449362237</v>
       </c>
       <c r="C32">
-        <v>6651.576578179092</v>
+        <v>6878.220469504364</v>
       </c>
       <c r="D32">
-        <v>9356.566578179092</v>
+        <v>9583.210469504364</v>
       </c>
       <c r="E32">
         <v>2000.99</v>
@@ -3917,37 +4048,37 @@
         <v>390.4</v>
       </c>
       <c r="M32">
-        <v>192.808161</v>
+        <v>182.017719</v>
       </c>
       <c r="N32">
-        <v>197.591839</v>
+        <v>208.3822809999999</v>
       </c>
       <c r="O32">
-        <v>55.32571492</v>
+        <v>58.34703867999999</v>
       </c>
       <c r="P32">
-        <v>142.26612408</v>
+        <v>150.03524232</v>
       </c>
       <c r="Q32">
-        <v>345.66612408</v>
+        <v>353.4352423199999</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.07857353403078715</v>
+        <v>0.07855246356231767</v>
       </c>
       <c r="T32">
         <v>0.7564079344646112</v>
       </c>
       <c r="U32">
-        <v>0.0679</v>
+        <v>0.0641</v>
       </c>
       <c r="V32">
         <v>0.28</v>
       </c>
       <c r="W32">
-        <v>0.048888</v>
+        <v>0.046152</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +4086,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.024810557681736</v>
+        <v>2.144846128963961</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +4097,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.07275342704567726</v>
+        <v>0.06876576280303051</v>
       </c>
       <c r="C33">
-        <v>5792.187043802134</v>
+        <v>6802.451048403076</v>
       </c>
       <c r="D33">
-        <v>8591.830043802134</v>
+        <v>9602.094048403076</v>
       </c>
       <c r="E33">
         <v>2095.643</v>
@@ -3999,45 +4130,45 @@
         <v>390.4</v>
       </c>
       <c r="M33">
-        <v>240.3145017</v>
+        <v>188.0849763000001</v>
       </c>
       <c r="N33">
-        <v>150.0854983</v>
+        <v>202.3150236999999</v>
       </c>
       <c r="O33">
-        <v>42.02393952399999</v>
+        <v>56.64820663599998</v>
       </c>
       <c r="P33">
-        <v>108.061558776</v>
+        <v>145.6668170639999</v>
       </c>
       <c r="Q33">
-        <v>311.4615587759999</v>
+        <v>349.0668170639999</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.07894687977634386</v>
+        <v>0.07892556927975436</v>
       </c>
       <c r="T33">
         <v>0.7650246946825486</v>
       </c>
       <c r="U33">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V33">
         <v>0.28</v>
       </c>
       <c r="W33">
-        <v>0.058968</v>
+        <v>0.046152</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>1.624537833706604</v>
+        <v>2.075657544158671</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4179,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.07281498026980351</v>
+        <v>0.06869920111243864</v>
       </c>
       <c r="C34">
-        <v>5683.548117357584</v>
+        <v>6726.75619387738</v>
       </c>
       <c r="D34">
-        <v>8577.844117357585</v>
+        <v>9621.05219387738</v>
       </c>
       <c r="E34">
         <v>2190.296</v>
@@ -4081,45 +4212,45 @@
         <v>390.4</v>
       </c>
       <c r="M34">
-        <v>248.0665824</v>
+        <v>194.1522336</v>
       </c>
       <c r="N34">
-        <v>142.3334176</v>
+        <v>196.2477664</v>
       </c>
       <c r="O34">
-        <v>39.85335692799999</v>
+        <v>54.94937459199999</v>
       </c>
       <c r="P34">
-        <v>102.480060672</v>
+        <v>141.298391808</v>
       </c>
       <c r="Q34">
-        <v>305.880060672</v>
+        <v>344.698391808</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.07933120627912282</v>
+        <v>0.07930964869476272</v>
       </c>
       <c r="T34">
         <v>0.7738948890245431</v>
       </c>
       <c r="U34">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V34">
         <v>0.28</v>
       </c>
       <c r="W34">
-        <v>0.058968</v>
+        <v>0.046152</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>1.573771026403272</v>
+        <v>2.010793245903713</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4261,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.07287653349392978</v>
+        <v>0.07141255942184678</v>
       </c>
       <c r="C35">
-        <v>5574.954649969835</v>
+        <v>5915.437367533572</v>
       </c>
       <c r="D35">
-        <v>8563.903649969836</v>
+        <v>8904.386367533572</v>
       </c>
       <c r="E35">
         <v>2284.949000000001</v>
@@ -4163,37 +4294,37 @@
         <v>390.4</v>
       </c>
       <c r="M35">
-        <v>255.8186631</v>
+        <v>236.7650142000001</v>
       </c>
       <c r="N35">
-        <v>134.5813368999999</v>
+        <v>153.6349857999999</v>
       </c>
       <c r="O35">
-        <v>37.68277433199999</v>
+        <v>43.01779602399998</v>
       </c>
       <c r="P35">
-        <v>96.89856256799996</v>
+        <v>110.6171897759999</v>
       </c>
       <c r="Q35">
-        <v>300.298562568</v>
+        <v>314.017189776</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.07972700521482058</v>
+        <v>0.0797051931669355</v>
       </c>
       <c r="T35">
         <v>0.7830298652871941</v>
       </c>
       <c r="U35">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V35">
         <v>0.28</v>
       </c>
       <c r="W35">
-        <v>0.058968</v>
+        <v>0.054576</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4332,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.526080995300143</v>
+        <v>1.648892262731948</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4343,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08602093712374446</v>
+        <v>0.07143023773125493</v>
       </c>
       <c r="C36">
-        <v>3273.933197944331</v>
+        <v>5816.464991802459</v>
       </c>
       <c r="D36">
-        <v>6357.535197944331</v>
+        <v>8900.06699180246</v>
       </c>
       <c r="E36">
         <v>2379.602000000001</v>
@@ -4245,45 +4376,45 @@
         <v>390.4</v>
       </c>
       <c r="M36">
-        <v>421.2626418</v>
+        <v>243.9397116000001</v>
       </c>
       <c r="N36">
-        <v>-30.86264180000006</v>
+        <v>146.4602883999999</v>
       </c>
       <c r="O36">
-        <v>-8.641539704000019</v>
+        <v>41.00888075199998</v>
       </c>
       <c r="P36">
-        <v>-22.22110209600005</v>
+        <v>105.4514076479999</v>
       </c>
       <c r="Q36">
-        <v>181.178897904</v>
+        <v>308.851407648</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.08039946457657277</v>
+        <v>0.08011272383523474</v>
       </c>
       <c r="T36">
-        <v>0.7985501200255611</v>
+        <v>0.7924416590123498</v>
       </c>
       <c r="U36">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V36">
-        <v>0.2594865747717959</v>
+        <v>0.28</v>
       </c>
       <c r="W36">
-        <v>0.0969332073623719</v>
+        <v>0.054576</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y36">
-        <v>0.9267377670421283</v>
+        <v>1.600395431475126</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4425,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08687193712374446</v>
+        <v>0.07144791604066308</v>
       </c>
       <c r="C37">
-        <v>3074.97656120988</v>
+        <v>5717.496804560052</v>
       </c>
       <c r="D37">
-        <v>6253.23156120988</v>
+        <v>8895.751804560052</v>
       </c>
       <c r="E37">
         <v>2474.255000000001</v>
@@ -4327,45 +4458,45 @@
         <v>390.4</v>
       </c>
       <c r="M37">
-        <v>433.6527195</v>
+        <v>251.1144090000001</v>
       </c>
       <c r="N37">
-        <v>-43.25271950000007</v>
+        <v>139.2855909999999</v>
       </c>
       <c r="O37">
-        <v>-12.11076146000002</v>
+        <v>38.99996547999999</v>
       </c>
       <c r="P37">
-        <v>-31.14195804000005</v>
+        <v>100.2856255199999</v>
       </c>
       <c r="Q37">
-        <v>172.25804196</v>
+        <v>303.6856255199999</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.08093176403159695</v>
+        <v>0.08053279390871243</v>
       </c>
       <c r="T37">
-        <v>0.8108355064874927</v>
+        <v>0.802143046390587</v>
       </c>
       <c r="U37">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V37">
-        <v>0.2520726726354589</v>
+        <v>0.28</v>
       </c>
       <c r="W37">
-        <v>0.09790368715201841</v>
+        <v>0.054576</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y37">
-        <v>0.9002595451266389</v>
+        <v>1.554669847718694</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4507,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08772293712374446</v>
+        <v>0.07146559435007122</v>
       </c>
       <c r="C38">
-        <v>2879.38715442788</v>
+        <v>5618.532799716962</v>
       </c>
       <c r="D38">
-        <v>6152.29515442788</v>
+        <v>8891.440799716962</v>
       </c>
       <c r="E38">
         <v>2568.908</v>
@@ -4409,45 +4540,45 @@
         <v>390.4</v>
       </c>
       <c r="M38">
-        <v>446.0427972</v>
+        <v>258.2891064</v>
       </c>
       <c r="N38">
-        <v>-55.64279720000002</v>
+        <v>132.1108935999999</v>
       </c>
       <c r="O38">
-        <v>-15.57998321600001</v>
+        <v>36.99105020799999</v>
       </c>
       <c r="P38">
-        <v>-40.06281398400002</v>
+        <v>95.11984339199995</v>
       </c>
       <c r="Q38">
-        <v>163.337186016</v>
+        <v>298.519843392</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.08148069784459065</v>
+        <v>0.08096599117198627</v>
       </c>
       <c r="T38">
-        <v>0.8235048112763598</v>
+        <v>0.8121476021243942</v>
       </c>
       <c r="U38">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V38">
-        <v>0.2450706539511407</v>
+        <v>0.28</v>
       </c>
       <c r="W38">
-        <v>0.09882025139779567</v>
+        <v>0.054576</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.8752523355397879</v>
+        <v>1.511484574170953</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4589,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08857393712374446</v>
+        <v>0.08377924249822243</v>
       </c>
       <c r="C39">
-        <v>2687.004511541763</v>
+        <v>3279.982212282349</v>
       </c>
       <c r="D39">
-        <v>6054.565511541763</v>
+        <v>6647.543212282349</v>
       </c>
       <c r="E39">
         <v>2663.561000000001</v>
@@ -4491,37 +4622,37 @@
         <v>390.4</v>
       </c>
       <c r="M39">
-        <v>458.4328749</v>
+        <v>415.3562946000001</v>
       </c>
       <c r="N39">
-        <v>-68.03287490000002</v>
+        <v>-24.95629460000015</v>
       </c>
       <c r="O39">
-        <v>-19.04920497200001</v>
+        <v>-6.987762488000042</v>
       </c>
       <c r="P39">
-        <v>-48.98366992800001</v>
+        <v>-17.9685321120001</v>
       </c>
       <c r="Q39">
-        <v>154.416330072</v>
+        <v>185.4314678879999</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.08204705812783814</v>
+        <v>0.08166024126193011</v>
       </c>
       <c r="T39">
-        <v>0.8365763162172544</v>
+        <v>0.8281810914995404</v>
       </c>
       <c r="U39">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V39">
-        <v>0.238447122763272</v>
+        <v>0.2631764618019586</v>
       </c>
       <c r="W39">
-        <v>0.09968727163028769</v>
+        <v>0.08738727163028771</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4660,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.8515968670116856</v>
+        <v>0.939915935006995</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4671,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08942493712374446</v>
+        <v>0.08450724249822242</v>
       </c>
       <c r="C40">
-        <v>2497.678203120992</v>
+        <v>3087.60441243817</v>
       </c>
       <c r="D40">
-        <v>5959.892203120992</v>
+        <v>6549.81841243817</v>
       </c>
       <c r="E40">
         <v>2758.214</v>
@@ -4573,37 +4704,37 @@
         <v>390.4</v>
       </c>
       <c r="M40">
-        <v>470.8229526</v>
+        <v>426.5821404000001</v>
       </c>
       <c r="N40">
-        <v>-80.42295260000003</v>
+        <v>-36.18214040000009</v>
       </c>
       <c r="O40">
-        <v>-22.51842672800001</v>
+        <v>-10.13099931200003</v>
       </c>
       <c r="P40">
-        <v>-57.90452587200002</v>
+        <v>-26.05114108800007</v>
       </c>
       <c r="Q40">
-        <v>145.495474128</v>
+        <v>177.3488589119999</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.08263168809764196</v>
+        <v>0.08223863225002576</v>
       </c>
       <c r="T40">
-        <v>0.8500694826078553</v>
+        <v>0.8415388510398557</v>
       </c>
       <c r="U40">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V40">
-        <v>0.232172198480028</v>
+        <v>0.2562507654387493</v>
       </c>
       <c r="W40">
-        <v>0.1005086592189643</v>
+        <v>0.08820865921896434</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4742,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.829186423142957</v>
+        <v>0.9151813051383899</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4753,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.09027593712374446</v>
+        <v>0.08523524249822242</v>
       </c>
       <c r="C41">
-        <v>2311.267063744636</v>
+        <v>2898.058267759478</v>
       </c>
       <c r="D41">
-        <v>5868.134063744636</v>
+        <v>6454.925267759479</v>
       </c>
       <c r="E41">
         <v>2852.867000000001</v>
@@ -4655,37 +4786,37 @@
         <v>390.4</v>
       </c>
       <c r="M41">
-        <v>483.2130303</v>
+        <v>437.8079862000001</v>
       </c>
       <c r="N41">
-        <v>-92.81303030000004</v>
+        <v>-47.40798620000015</v>
       </c>
       <c r="O41">
-        <v>-25.98764848400001</v>
+        <v>-13.27423613600004</v>
       </c>
       <c r="P41">
-        <v>-66.82538181600003</v>
+        <v>-34.13375006400011</v>
       </c>
       <c r="Q41">
-        <v>136.574618184</v>
+        <v>169.2662499359999</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.08323548626317709</v>
+        <v>0.08283598687707536</v>
       </c>
       <c r="T41">
-        <v>0.8640050478965088</v>
+        <v>0.8553345699093615</v>
       </c>
       <c r="U41">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V41">
-        <v>0.2262190651856683</v>
+        <v>0.2496802329916018</v>
       </c>
       <c r="W41">
-        <v>0.101287924367196</v>
+        <v>0.08898792436719603</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4824,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.8079252328059581</v>
+        <v>0.8917151178271491</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4835,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1259562495774813</v>
+        <v>0.08596324249822243</v>
       </c>
       <c r="C42">
-        <v>-85.37829937666174</v>
+        <v>2711.222461619823</v>
       </c>
       <c r="D42">
-        <v>3566.141700623339</v>
+        <v>6362.742461619823</v>
       </c>
       <c r="E42">
         <v>2947.520000000001</v>
@@ -4737,45 +4868,45 @@
         <v>390.4</v>
       </c>
       <c r="M42">
-        <v>817.0446960000003</v>
+        <v>449.0338320000001</v>
       </c>
       <c r="N42">
-        <v>-426.6446960000003</v>
+        <v>-58.63383200000015</v>
       </c>
       <c r="O42">
-        <v>-119.4605148800001</v>
+        <v>-16.41747296000004</v>
       </c>
       <c r="P42">
-        <v>-307.1841811200002</v>
+        <v>-42.21635904000011</v>
       </c>
       <c r="Q42">
-        <v>-103.7841811200002</v>
+        <v>161.1836409599999</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.08530826512379143</v>
+        <v>0.08345325332502662</v>
       </c>
       <c r="T42">
-        <v>0.9118444531643802</v>
+        <v>0.8695901460745177</v>
       </c>
       <c r="U42">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V42">
-        <v>0.1337894983409818</v>
+        <v>0.2434382271668117</v>
       </c>
       <c r="W42">
-        <v>0.1869282262580162</v>
+        <v>0.08972822625801613</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y42">
-        <v>0.4778196369320777</v>
+        <v>0.8694222398814704</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4917,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1276562495774813</v>
+        <v>0.08669124249822241</v>
       </c>
       <c r="C43">
-        <v>-245.4618243543255</v>
+        <v>2526.982509909902</v>
       </c>
       <c r="D43">
-        <v>3500.711175645675</v>
+        <v>6273.155509909902</v>
       </c>
       <c r="E43">
         <v>3042.173000000001</v>
@@ -4819,45 +4950,45 @@
         <v>390.4</v>
       </c>
       <c r="M43">
-        <v>837.4708134000002</v>
+        <v>460.2596778000001</v>
       </c>
       <c r="N43">
-        <v>-447.0708134000002</v>
+        <v>-69.85967780000016</v>
       </c>
       <c r="O43">
-        <v>-125.1798277520001</v>
+        <v>-19.56070978400005</v>
       </c>
       <c r="P43">
-        <v>-321.8909856480002</v>
+        <v>-50.29896801600011</v>
       </c>
       <c r="Q43">
-        <v>-118.4909856480002</v>
+        <v>153.1010319839999</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.08597789673605907</v>
+        <v>0.0840914440593491</v>
       </c>
       <c r="T43">
-        <v>0.92729944389598</v>
+        <v>0.8843289621096788</v>
       </c>
       <c r="U43">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V43">
-        <v>0.1305263398448603</v>
+        <v>0.2375007094310358</v>
       </c>
       <c r="W43">
-        <v>0.1876324158614792</v>
+        <v>0.09043241586147915</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y43">
-        <v>0.4661654994459296</v>
+        <v>0.8482168193965565</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4999,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1293562495774813</v>
+        <v>0.08741924249822242</v>
       </c>
       <c r="C44">
-        <v>-403.1876082034114</v>
+        <v>2345.230286709344</v>
       </c>
       <c r="D44">
-        <v>3437.638391796589</v>
+        <v>6186.056286709344</v>
       </c>
       <c r="E44">
         <v>3136.826</v>
@@ -4901,45 +5032,45 @@
         <v>390.4</v>
       </c>
       <c r="M44">
-        <v>857.8969308000002</v>
+        <v>471.4855236000001</v>
       </c>
       <c r="N44">
-        <v>-467.4969308000002</v>
+        <v>-81.0855236000001</v>
       </c>
       <c r="O44">
-        <v>-130.8991406240001</v>
+        <v>-22.70394660800003</v>
       </c>
       <c r="P44">
-        <v>-336.5977901760001</v>
+        <v>-58.38157699200007</v>
       </c>
       <c r="Q44">
-        <v>-133.1977901760001</v>
+        <v>145.0184230079999</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.08667061909357734</v>
+        <v>0.08475164137071718</v>
       </c>
       <c r="T44">
-        <v>0.9432873653424623</v>
+        <v>0.8995760131805353</v>
       </c>
       <c r="U44">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V44">
-        <v>0.1274185698485541</v>
+        <v>0.2318459306350588</v>
       </c>
       <c r="W44">
-        <v>0.188303072626682</v>
+        <v>0.09110307262668203</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y44">
-        <v>0.4550663208876932</v>
+        <v>0.8280211808394957</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +5081,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1310562495774813</v>
+        <v>0.08814724249822242</v>
       </c>
       <c r="C45">
-        <v>-558.6808346878042</v>
+        <v>2165.86358893205</v>
       </c>
       <c r="D45">
-        <v>3376.798165312196</v>
+        <v>6101.342588932051</v>
       </c>
       <c r="E45">
         <v>3231.479000000001</v>
@@ -4983,45 +5114,45 @@
         <v>390.4</v>
       </c>
       <c r="M45">
-        <v>878.3230482000002</v>
+        <v>482.7113694000001</v>
       </c>
       <c r="N45">
-        <v>-487.9230482000003</v>
+        <v>-92.31136940000016</v>
       </c>
       <c r="O45">
-        <v>-136.6184534960001</v>
+        <v>-25.84718343200005</v>
       </c>
       <c r="P45">
-        <v>-351.3045947040002</v>
+        <v>-66.46418596800011</v>
       </c>
       <c r="Q45">
-        <v>-147.9045947040002</v>
+        <v>136.9358140319999</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.08738764749872782</v>
+        <v>0.08543500350002801</v>
       </c>
       <c r="T45">
-        <v>0.9598362664888214</v>
+        <v>0.9153580484994921</v>
       </c>
       <c r="U45">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V45">
-        <v>0.1244553472939365</v>
+        <v>0.2264541648063365</v>
       </c>
       <c r="W45">
-        <v>0.1889425360539685</v>
+        <v>0.0917425360539685</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y45">
-        <v>0.4444833831926305</v>
+        <v>0.8087648743083445</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5163,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1327562495774813</v>
+        <v>0.1260409504085061</v>
       </c>
       <c r="C46">
-        <v>-712.0579795478416</v>
+        <v>-467.9548878938058</v>
       </c>
       <c r="D46">
-        <v>3318.074020452159</v>
+        <v>3562.177112106195</v>
       </c>
       <c r="E46">
         <v>3326.132000000001</v>
@@ -5065,37 +5196,37 @@
         <v>390.4</v>
       </c>
       <c r="M46">
-        <v>898.7491656000003</v>
+        <v>836.2781856000003</v>
       </c>
       <c r="N46">
-        <v>-508.3491656000003</v>
+        <v>-445.8781856000003</v>
       </c>
       <c r="O46">
-        <v>-142.3377663680001</v>
+        <v>-124.8458919680001</v>
       </c>
       <c r="P46">
-        <v>-366.0113992320003</v>
+        <v>-321.0322936320002</v>
       </c>
       <c r="Q46">
-        <v>-162.6113992320003</v>
+        <v>-117.6322936320002</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.0881302840612051</v>
+        <v>0.08792439268803515</v>
       </c>
       <c r="T46">
-        <v>0.9769761998189788</v>
+        <v>0.97284971565901</v>
       </c>
       <c r="U46">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.1216268166736198</v>
+        <v>0.1307124852498364</v>
       </c>
       <c r="W46">
-        <v>0.1895529329618328</v>
+        <v>0.1745529329618328</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5234,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4343814881200707</v>
+        <v>0.4668303044637014</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5245,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1344562495774813</v>
+        <v>0.1275909504085062</v>
       </c>
       <c r="C47">
-        <v>-863.4275547412035</v>
+        <v>-622.2310522739303</v>
       </c>
       <c r="D47">
-        <v>3261.357445258797</v>
+        <v>3502.55394772607</v>
       </c>
       <c r="E47">
         <v>3420.785</v>
@@ -5147,37 +5278,37 @@
         <v>390.4</v>
       </c>
       <c r="M47">
-        <v>919.1752830000001</v>
+        <v>855.2845080000001</v>
       </c>
       <c r="N47">
-        <v>-528.7752830000002</v>
+        <v>-464.8845080000001</v>
       </c>
       <c r="O47">
-        <v>-148.0570792400001</v>
+        <v>-130.16766224</v>
       </c>
       <c r="P47">
-        <v>-380.7182037600001</v>
+        <v>-334.7168457600001</v>
       </c>
       <c r="Q47">
-        <v>-177.3182037600001</v>
+        <v>-131.3168457600001</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.08889992558959064</v>
+        <v>0.08869029073690851</v>
       </c>
       <c r="T47">
-        <v>0.9947394034520511</v>
+        <v>0.9905378923073558</v>
       </c>
       <c r="U47">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1189239985253172</v>
+        <v>0.1278077633553956</v>
       </c>
       <c r="W47">
-        <v>0.1901362011182366</v>
+        <v>0.1751362011182366</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5316,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.424728566161847</v>
+        <v>0.4564562976978416</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5327,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1361562495774813</v>
+        <v>0.1291409504085061</v>
       </c>
       <c r="C48">
-        <v>-1012.890777637737</v>
+        <v>-774.54414776051</v>
       </c>
       <c r="D48">
-        <v>3206.547222362263</v>
+        <v>3444.893852239491</v>
       </c>
       <c r="E48">
         <v>3515.438000000001</v>
@@ -5229,37 +5360,37 @@
         <v>390.4</v>
       </c>
       <c r="M48">
-        <v>939.6014004000002</v>
+        <v>874.2908304000001</v>
       </c>
       <c r="N48">
-        <v>-549.2014004000002</v>
+        <v>-483.8908304000001</v>
       </c>
       <c r="O48">
-        <v>-153.7763921120001</v>
+        <v>-135.4894325120001</v>
       </c>
       <c r="P48">
-        <v>-395.4250082880002</v>
+        <v>-348.4013978880001</v>
       </c>
       <c r="Q48">
-        <v>-192.0250082880002</v>
+        <v>-145.0013978880001</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.08969807235976826</v>
+        <v>0.0894845553801846</v>
       </c>
       <c r="T48">
-        <v>1.013160503515978</v>
+        <v>1.008881186609344</v>
       </c>
       <c r="U48">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1163386942095494</v>
+        <v>0.1250293337172349</v>
       </c>
       <c r="W48">
-        <v>0.1906941097895793</v>
+        <v>0.1756941097895793</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5398,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.4154953364626763</v>
+        <v>0.4465333347044101</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5409,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1378562495774813</v>
+        <v>0.1306909504085061</v>
       </c>
       <c r="C49">
-        <v>-1160.542173850827</v>
+        <v>-924.9895540738171</v>
       </c>
       <c r="D49">
-        <v>3153.548826149174</v>
+        <v>3389.101445926184</v>
       </c>
       <c r="E49">
         <v>3610.091000000001</v>
@@ -5311,37 +5442,37 @@
         <v>390.4</v>
       </c>
       <c r="M49">
-        <v>960.0275178000003</v>
+        <v>893.2971528000002</v>
       </c>
       <c r="N49">
-        <v>-569.6275178000003</v>
+        <v>-502.8971528000002</v>
       </c>
       <c r="O49">
-        <v>-159.4957049840001</v>
+        <v>-140.8112027840001</v>
       </c>
       <c r="P49">
-        <v>-410.1318128160002</v>
+        <v>-362.0859500160001</v>
       </c>
       <c r="Q49">
-        <v>-206.7318128160002</v>
+        <v>-158.6859500160001</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.09052633787599029</v>
+        <v>0.09030879227415034</v>
       </c>
       <c r="T49">
-        <v>1.032276739431374</v>
+        <v>1.027916680696313</v>
       </c>
       <c r="U49">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1138634028433888</v>
+        <v>0.1223691351275065</v>
       </c>
       <c r="W49">
-        <v>0.1912282776663967</v>
+        <v>0.1762282776663967</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5480,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.4066550101549599</v>
+        <v>0.4370326254553801</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5491,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1395562495774813</v>
+        <v>0.1322409504085061</v>
       </c>
       <c r="C50">
-        <v>-1306.470121258564</v>
+        <v>-1073.656570453079</v>
       </c>
       <c r="D50">
-        <v>3102.273878741436</v>
+        <v>3335.087429546922</v>
       </c>
       <c r="E50">
         <v>3704.744</v>
@@ -5393,37 +5524,37 @@
         <v>390.4</v>
       </c>
       <c r="M50">
-        <v>980.4536352000001</v>
+        <v>912.3034752000001</v>
       </c>
       <c r="N50">
-        <v>-590.0536352000001</v>
+        <v>-521.9034752000001</v>
       </c>
       <c r="O50">
-        <v>-165.2150178560001</v>
+        <v>-146.1329730560001</v>
       </c>
       <c r="P50">
-        <v>-424.8386173440001</v>
+        <v>-375.770502144</v>
       </c>
       <c r="Q50">
-        <v>-221.4386173440001</v>
+        <v>-172.370502144</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.09138645975822088</v>
+        <v>0.09116473058711477</v>
       </c>
       <c r="T50">
-        <v>1.05212821518967</v>
+        <v>1.047684309171242</v>
       </c>
       <c r="U50">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1114912486174848</v>
+        <v>0.1198197781456834</v>
       </c>
       <c r="W50">
-        <v>0.1917401885483468</v>
+        <v>0.1767401885483468</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5562,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3981830307767316</v>
+        <v>0.4279277790917264</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5573,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1412562495774813</v>
+        <v>0.1337909504085061</v>
       </c>
       <c r="C51">
-        <v>-1450.757341801158</v>
+        <v>-1220.628892595474</v>
       </c>
       <c r="D51">
-        <v>3052.639658198842</v>
+        <v>3282.768107404527</v>
       </c>
       <c r="E51">
         <v>3799.397</v>
@@ -5475,37 +5606,37 @@
         <v>390.4</v>
       </c>
       <c r="M51">
-        <v>1000.8797526</v>
+        <v>931.3097976000001</v>
       </c>
       <c r="N51">
-        <v>-610.4797526000002</v>
+        <v>-540.9097976000002</v>
       </c>
       <c r="O51">
-        <v>-170.9343307280001</v>
+        <v>-151.4547433280001</v>
       </c>
       <c r="P51">
-        <v>-439.5454218720001</v>
+        <v>-389.4550542720001</v>
       </c>
       <c r="Q51">
-        <v>-236.1454218720001</v>
+        <v>-186.0550542720001</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.09228031191034286</v>
+        <v>0.09205423510843075</v>
       </c>
       <c r="T51">
-        <v>1.072758180193389</v>
+        <v>1.068227138762835</v>
       </c>
       <c r="U51">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1092159170130464</v>
+        <v>0.1173744765508735</v>
       </c>
       <c r="W51">
-        <v>0.1922312051085846</v>
+        <v>0.1772312051085846</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5644,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3900568464751656</v>
+        <v>0.4191945591102626</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5655,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1429562495774813</v>
+        <v>0.1353409504085061</v>
       </c>
       <c r="C52">
-        <v>-1593.481346811274</v>
+        <v>-1365.985045396484</v>
       </c>
       <c r="D52">
-        <v>3004.568653188727</v>
+        <v>3232.064954603517</v>
       </c>
       <c r="E52">
         <v>3894.050000000001</v>
@@ -5557,37 +5688,37 @@
         <v>390.4</v>
       </c>
       <c r="M52">
-        <v>1021.30587</v>
+        <v>950.3161200000002</v>
       </c>
       <c r="N52">
-        <v>-630.9058700000003</v>
+        <v>-559.9161200000002</v>
       </c>
       <c r="O52">
-        <v>-176.6536436000001</v>
+        <v>-156.7765136000001</v>
       </c>
       <c r="P52">
-        <v>-454.2522264000002</v>
+        <v>-403.1396064000002</v>
       </c>
       <c r="Q52">
-        <v>-250.8522264000001</v>
+        <v>-199.7396064000002</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.09320991814854972</v>
+        <v>0.09297931981059937</v>
       </c>
       <c r="T52">
-        <v>1.094213343797256</v>
+        <v>1.089591681538091</v>
       </c>
       <c r="U52">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1070315986727854</v>
+        <v>0.1150269870198561</v>
       </c>
       <c r="W52">
-        <v>0.1927025810064129</v>
+        <v>0.1777025810064129</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5726,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3822557095456622</v>
+        <v>0.4108106679280573</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5737,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1446562495774813</v>
+        <v>0.1368909504085061</v>
       </c>
       <c r="C53">
-        <v>-1734.714840920067</v>
+        <v>-1509.798776197549</v>
       </c>
       <c r="D53">
-        <v>2957.988159079934</v>
+        <v>3182.904223802452</v>
       </c>
       <c r="E53">
         <v>3988.703000000001</v>
@@ -5639,37 +5770,37 @@
         <v>390.4</v>
       </c>
       <c r="M53">
-        <v>1041.7319874</v>
+        <v>969.3224424000002</v>
       </c>
       <c r="N53">
-        <v>-651.3319874000002</v>
+        <v>-578.9224424000003</v>
       </c>
       <c r="O53">
-        <v>-182.3729564720001</v>
+        <v>-162.0982838720001</v>
       </c>
       <c r="P53">
-        <v>-468.9590309280002</v>
+        <v>-416.8241585280002</v>
       </c>
       <c r="Q53">
-        <v>-265.5590309280002</v>
+        <v>-213.4241585280002</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.09417746749852011</v>
+        <v>0.09394216307204017</v>
       </c>
       <c r="T53">
-        <v>1.116544228364547</v>
+        <v>1.11182824646744</v>
       </c>
       <c r="U53">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1049329398752799</v>
+        <v>0.1127715559018197</v>
       </c>
       <c r="W53">
-        <v>0.1931554715749146</v>
+        <v>0.1781554715749146</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5808,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3747604995545708</v>
+        <v>0.4027555567922131</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5819,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1463562495774813</v>
+        <v>0.1384409504085062</v>
       </c>
       <c r="C54">
-        <v>-1874.526088965706</v>
+        <v>-1652.139412682887</v>
       </c>
       <c r="D54">
-        <v>2912.829911034295</v>
+        <v>3135.216587317114</v>
       </c>
       <c r="E54">
         <v>4083.356000000001</v>
@@ -5721,37 +5852,37 @@
         <v>390.4</v>
       </c>
       <c r="M54">
-        <v>1062.1581048</v>
+        <v>988.3287648000003</v>
       </c>
       <c r="N54">
-        <v>-671.7581048000003</v>
+        <v>-597.9287648000003</v>
       </c>
       <c r="O54">
-        <v>-188.0922693440001</v>
+        <v>-167.4200541440001</v>
       </c>
       <c r="P54">
-        <v>-483.6658354560002</v>
+        <v>-430.5087106560002</v>
       </c>
       <c r="Q54">
-        <v>-280.2658354560002</v>
+        <v>-227.1087106560002</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.09518533140473928</v>
+        <v>0.09494512480270767</v>
       </c>
       <c r="T54">
-        <v>1.139805566455475</v>
+        <v>1.134991334935512</v>
       </c>
       <c r="U54">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1029149987238322</v>
+        <v>0.110602872134477</v>
       </c>
       <c r="W54">
-        <v>0.1935909432753971</v>
+        <v>0.178590943275397</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5890,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3675535668708291</v>
+        <v>0.395010257623132</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5901,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1480562495774813</v>
+        <v>0.1399909504085061</v>
       </c>
       <c r="C55">
-        <v>-2012.979249798736</v>
+        <v>-1793.072189078243</v>
       </c>
       <c r="D55">
-        <v>2869.029750201265</v>
+        <v>3088.936810921758</v>
       </c>
       <c r="E55">
         <v>4178.009</v>
@@ -5803,37 +5934,37 @@
         <v>390.4</v>
       </c>
       <c r="M55">
-        <v>1082.5842222</v>
+        <v>1007.3350872</v>
       </c>
       <c r="N55">
-        <v>-692.1842222000001</v>
+        <v>-616.9350872000001</v>
       </c>
       <c r="O55">
-        <v>-193.8115822160001</v>
+        <v>-172.741824416</v>
       </c>
       <c r="P55">
-        <v>-498.3726399840001</v>
+        <v>-444.1932627840001</v>
       </c>
       <c r="Q55">
-        <v>-294.9726399840001</v>
+        <v>-240.7932627840001</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.09623608313675502</v>
+        <v>0.09599076575595678</v>
       </c>
       <c r="T55">
-        <v>1.164056748720486</v>
+        <v>1.15914008674265</v>
       </c>
       <c r="U55">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1009732062950806</v>
+        <v>0.1085160254904303</v>
       </c>
       <c r="W55">
-        <v>0.1940099820815216</v>
+        <v>0.1790099820815216</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5972,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3606185939110021</v>
+        <v>0.3875572338943938</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5983,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1497562495774813</v>
+        <v>0.1415409504085061</v>
       </c>
       <c r="C56">
-        <v>-2150.134680417051</v>
+        <v>-1932.658543879263</v>
       </c>
       <c r="D56">
-        <v>2826.52731958295</v>
+        <v>3044.003456120738</v>
       </c>
       <c r="E56">
         <v>4272.662</v>
@@ -5885,37 +6016,37 @@
         <v>390.4</v>
       </c>
       <c r="M56">
-        <v>1103.0103396</v>
+        <v>1026.3414096</v>
       </c>
       <c r="N56">
-        <v>-712.6103396000002</v>
+        <v>-635.9414096000002</v>
       </c>
       <c r="O56">
-        <v>-199.5308950880001</v>
+        <v>-178.0635946880001</v>
       </c>
       <c r="P56">
-        <v>-513.0794445120001</v>
+        <v>-457.8778149120001</v>
       </c>
       <c r="Q56">
-        <v>-309.6794445120001</v>
+        <v>-254.4778149120001</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.09733251972668447</v>
+        <v>0.09708186935934712</v>
       </c>
       <c r="T56">
-        <v>1.189362330214409</v>
+        <v>1.184338784280534</v>
       </c>
       <c r="U56">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.09910333210443097</v>
+        <v>0.1065064694628297</v>
       </c>
       <c r="W56">
-        <v>0.1944135009318638</v>
+        <v>0.1794135009318638</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +6054,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3539404718015391</v>
+        <v>0.3803802480815346</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +6065,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1514562495774813</v>
+        <v>0.1430909504085061</v>
       </c>
       <c r="C57">
-        <v>-2286.049213462355</v>
+        <v>-2070.956391966918</v>
       </c>
       <c r="D57">
-        <v>2785.265786537646</v>
+        <v>3000.358608033083</v>
       </c>
       <c r="E57">
         <v>4367.315000000001</v>
@@ -5967,37 +6098,37 @@
         <v>390.4</v>
       </c>
       <c r="M57">
-        <v>1123.436457</v>
+        <v>1045.347732</v>
       </c>
       <c r="N57">
-        <v>-733.0364570000003</v>
+        <v>-654.9477320000002</v>
       </c>
       <c r="O57">
-        <v>-205.2502079600001</v>
+        <v>-183.3853649600001</v>
       </c>
       <c r="P57">
-        <v>-527.7862490400001</v>
+        <v>-471.5623670400001</v>
       </c>
       <c r="Q57">
-        <v>-324.3862490400002</v>
+        <v>-268.1623670400002</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.09847768683172191</v>
+        <v>0.09822146645622151</v>
       </c>
       <c r="T57">
-        <v>1.215792604219174</v>
+        <v>1.210657423931213</v>
       </c>
       <c r="U57">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.09730145333889585</v>
+        <v>0.1045699881998692</v>
       </c>
       <c r="W57">
-        <v>0.1948023463694663</v>
+        <v>0.1798023463694663</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6136,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3475051904960565</v>
+        <v>0.3734642435709612</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6147,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1531562495774813</v>
+        <v>0.1446409504085061</v>
       </c>
       <c r="C58">
-        <v>-2420.776410761033</v>
+        <v>-2208.020373644335</v>
       </c>
       <c r="D58">
-        <v>2745.191589238968</v>
+        <v>2957.947626355666</v>
       </c>
       <c r="E58">
         <v>4461.968000000001</v>
@@ -6049,37 +6180,37 @@
         <v>390.4</v>
       </c>
       <c r="M58">
-        <v>1143.8625744</v>
+        <v>1064.3540544</v>
       </c>
       <c r="N58">
-        <v>-753.4625744000003</v>
+        <v>-673.9540544000002</v>
       </c>
       <c r="O58">
-        <v>-210.9695208320001</v>
+        <v>-188.7071352320001</v>
       </c>
       <c r="P58">
-        <v>-542.4930535680003</v>
+        <v>-485.2469191680001</v>
       </c>
       <c r="Q58">
-        <v>-339.0930535680003</v>
+        <v>-281.8469191680001</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.0996749069869883</v>
+        <v>0.09941286342113564</v>
       </c>
       <c r="T58">
-        <v>1.243424254315064</v>
+        <v>1.238172365384195</v>
       </c>
       <c r="U58">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.09556392738641556</v>
+        <v>0.1027026669820143</v>
       </c>
       <c r="W58">
-        <v>0.1951773044700116</v>
+        <v>0.1801773044700115</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6218,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3412997406657698</v>
+        <v>0.3667952392214797</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6229,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1548562495774813</v>
+        <v>0.1461909504085061</v>
       </c>
       <c r="C59">
-        <v>-2554.366795287925</v>
+        <v>-2343.902082846751</v>
       </c>
       <c r="D59">
-        <v>2706.254204712077</v>
+        <v>2916.71891715325</v>
       </c>
       <c r="E59">
         <v>4556.621000000001</v>
@@ -6131,37 +6262,37 @@
         <v>390.4</v>
       </c>
       <c r="M59">
-        <v>1164.2886918</v>
+        <v>1083.3603768</v>
       </c>
       <c r="N59">
-        <v>-773.8886918000004</v>
+        <v>-692.9603768000003</v>
       </c>
       <c r="O59">
-        <v>-216.6888337040001</v>
+        <v>-194.0289055040001</v>
       </c>
       <c r="P59">
-        <v>-557.1998580960003</v>
+        <v>-498.9314712960002</v>
       </c>
       <c r="Q59">
-        <v>-353.7998580960003</v>
+        <v>-295.5314712960002</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1009278118006392</v>
+        <v>0.1006596741983714</v>
       </c>
       <c r="T59">
-        <v>1.27234109743867</v>
+        <v>1.26696707155592</v>
       </c>
       <c r="U59">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.09388736725682933</v>
+        <v>0.1009008658068913</v>
       </c>
       <c r="W59">
-        <v>0.1955391061459762</v>
+        <v>0.1805391061459762</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6300,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3353120259172475</v>
+        <v>0.3603602350246117</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6311,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1565562495774813</v>
+        <v>0.1477409504085061</v>
       </c>
       <c r="C60">
-        <v>-2686.868063665324</v>
+        <v>-2478.650276528692</v>
       </c>
       <c r="D60">
-        <v>2668.405936334677</v>
+        <v>2876.623723471309</v>
       </c>
       <c r="E60">
         <v>4651.274</v>
@@ -6213,37 +6344,37 @@
         <v>390.4</v>
       </c>
       <c r="M60">
-        <v>1184.7148092</v>
+        <v>1102.3666992</v>
       </c>
       <c r="N60">
-        <v>-794.3148092000002</v>
+        <v>-711.9666992000001</v>
       </c>
       <c r="O60">
-        <v>-222.4081465760001</v>
+        <v>-199.3506757760001</v>
       </c>
       <c r="P60">
-        <v>-571.9066626240001</v>
+        <v>-512.6160234240001</v>
       </c>
       <c r="Q60">
-        <v>-368.5066626240001</v>
+        <v>-309.2160234240001</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1022403787482735</v>
+        <v>0.1019658569173802</v>
       </c>
       <c r="T60">
-        <v>1.302634933091972</v>
+        <v>1.297132954212013</v>
       </c>
       <c r="U60">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.09226861954550469</v>
+        <v>0.09916119570677248</v>
       </c>
       <c r="W60">
-        <v>0.1958884319020801</v>
+        <v>0.1808884319020801</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6382,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3295307840910882</v>
+        <v>0.3541471275241874</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6393,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1582562495774813</v>
+        <v>0.1492909504085061</v>
       </c>
       <c r="C61">
-        <v>-2818.325281076541</v>
+        <v>-2612.311067015079</v>
       </c>
       <c r="D61">
-        <v>2631.601718923459</v>
+        <v>2837.615932984922</v>
       </c>
       <c r="E61">
         <v>4745.927</v>
@@ -6295,37 +6426,37 @@
         <v>390.4</v>
       </c>
       <c r="M61">
-        <v>1205.1409266</v>
+        <v>1121.3730216</v>
       </c>
       <c r="N61">
-        <v>-814.7409266000001</v>
+        <v>-730.9730216000002</v>
       </c>
       <c r="O61">
-        <v>-228.1274594480001</v>
+        <v>-204.6724460480001</v>
       </c>
       <c r="P61">
-        <v>-586.613467152</v>
+        <v>-526.3005755520001</v>
       </c>
       <c r="Q61">
-        <v>-383.213467152</v>
+        <v>-322.9005755520001</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1036169733518899</v>
+        <v>0.1033357558665846</v>
       </c>
       <c r="T61">
-        <v>1.334406516825922</v>
+        <v>1.328770343339136</v>
       </c>
       <c r="U61">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.09070474463795379</v>
+        <v>0.09748049747445431</v>
       </c>
       <c r="W61">
-        <v>0.1962259161071296</v>
+        <v>0.1812259161071296</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6464,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3239455165641206</v>
+        <v>0.3481446338373367</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6475,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1599562495774813</v>
+        <v>0.1508409504085061</v>
       </c>
       <c r="C62">
-        <v>-2948.781060268716</v>
+        <v>-2744.928098911709</v>
       </c>
       <c r="D62">
-        <v>2595.798939731284</v>
+        <v>2799.651901088292</v>
       </c>
       <c r="E62">
         <v>4840.58</v>
@@ -6377,37 +6508,37 @@
         <v>390.4</v>
       </c>
       <c r="M62">
-        <v>1225.567044</v>
+        <v>1140.379344</v>
       </c>
       <c r="N62">
-        <v>-835.1670440000001</v>
+        <v>-749.9793440000002</v>
       </c>
       <c r="O62">
-        <v>-233.8467723200001</v>
+        <v>-209.9942163200001</v>
       </c>
       <c r="P62">
-        <v>-601.3202716800001</v>
+        <v>-539.9851276800001</v>
       </c>
       <c r="Q62">
-        <v>-397.9202716800002</v>
+        <v>-336.5851276800001</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1050623976856871</v>
+        <v>0.1047741497632492</v>
       </c>
       <c r="T62">
-        <v>1.36776667974657</v>
+        <v>1.361989601922614</v>
       </c>
       <c r="U62">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.08919299889398788</v>
+        <v>0.09585582251654673</v>
       </c>
       <c r="W62">
-        <v>0.1965521508386774</v>
+        <v>0.1815521508386774</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6546,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3185464246213853</v>
+        <v>0.3423422232733812</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6557,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1616562495774813</v>
+        <v>0.1523909504085061</v>
       </c>
       <c r="C63">
-        <v>-3078.275726139841</v>
+        <v>-2876.542712002079</v>
       </c>
       <c r="D63">
-        <v>2560.95727386016</v>
+        <v>2762.690287997921</v>
       </c>
       <c r="E63">
         <v>4935.233</v>
@@ -6459,37 +6590,37 @@
         <v>390.4</v>
       </c>
       <c r="M63">
-        <v>1245.9931614</v>
+        <v>1159.3856664</v>
       </c>
       <c r="N63">
-        <v>-855.5931614000002</v>
+        <v>-768.9856664000002</v>
       </c>
       <c r="O63">
-        <v>-239.5660851920001</v>
+        <v>-215.3159865920001</v>
       </c>
       <c r="P63">
-        <v>-616.0270762080002</v>
+        <v>-553.6696798080002</v>
       </c>
       <c r="Q63">
-        <v>-412.6270762080002</v>
+        <v>-350.2696798080002</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1065819463442945</v>
+        <v>0.1062863074494864</v>
       </c>
       <c r="T63">
-        <v>1.402837620252893</v>
+        <v>1.396912412228322</v>
       </c>
       <c r="U63">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.08773081858425036</v>
+        <v>0.09428441559004597</v>
       </c>
       <c r="W63">
-        <v>0.1968676893495188</v>
+        <v>0.1818676893495188</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6628,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3133243520866085</v>
+        <v>0.3367300556787355</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6639,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1633562495774813</v>
+        <v>0.1539409504085061</v>
       </c>
       <c r="C64">
-        <v>-3206.847467246489</v>
+        <v>-3007.194091408755</v>
       </c>
       <c r="D64">
-        <v>2527.038532753512</v>
+        <v>2726.691908591246</v>
       </c>
       <c r="E64">
         <v>5029.886</v>
@@ -6541,37 +6672,37 @@
         <v>390.4</v>
       </c>
       <c r="M64">
-        <v>1266.4192788</v>
+        <v>1178.3919888</v>
       </c>
       <c r="N64">
-        <v>-876.0192788000003</v>
+        <v>-787.9919888000003</v>
       </c>
       <c r="O64">
-        <v>-245.2853980640001</v>
+        <v>-220.6377568640001</v>
       </c>
       <c r="P64">
-        <v>-630.7338807360002</v>
+        <v>-567.3542319360001</v>
       </c>
       <c r="Q64">
-        <v>-427.3338807360002</v>
+        <v>-363.9542319360002</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1081814712480917</v>
+        <v>0.1078780523823676</v>
       </c>
       <c r="T64">
-        <v>1.439754399733232</v>
+        <v>1.433673265181699</v>
       </c>
       <c r="U64">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.08631580538127859</v>
+        <v>0.09276369920956135</v>
       </c>
       <c r="W64">
-        <v>0.1971730491987201</v>
+        <v>0.1821730491987201</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6710,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3082707335045664</v>
+        <v>0.3312989257484333</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6721,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1650562495774813</v>
+        <v>0.1554909504085061</v>
       </c>
       <c r="C65">
-        <v>-3334.532475429001</v>
+        <v>-3136.919406165939</v>
       </c>
       <c r="D65">
-        <v>2494.006524571</v>
+        <v>2691.619593834062</v>
       </c>
       <c r="E65">
         <v>5124.539000000001</v>
@@ -6623,37 +6754,37 @@
         <v>390.4</v>
       </c>
       <c r="M65">
-        <v>1286.8453962</v>
+        <v>1197.3983112</v>
       </c>
       <c r="N65">
-        <v>-896.4453962000003</v>
+        <v>-806.9983112000003</v>
       </c>
       <c r="O65">
-        <v>-251.0047109360001</v>
+        <v>-225.9595271360001</v>
       </c>
       <c r="P65">
-        <v>-645.4406852640002</v>
+        <v>-581.0387840640002</v>
       </c>
       <c r="Q65">
-        <v>-442.0406852640002</v>
+        <v>-377.6387840640002</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1098674569574996</v>
+        <v>0.109555837581891</v>
       </c>
       <c r="T65">
-        <v>1.478666680807103</v>
+        <v>1.472421191267691</v>
       </c>
       <c r="U65">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.08494571323236939</v>
+        <v>0.09129125953956831</v>
       </c>
       <c r="W65">
-        <v>0.1974687150844547</v>
+        <v>0.1824687150844547</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6792,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3033775472584621</v>
+        <v>0.3260402126413153</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6803,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1667562495774813</v>
+        <v>0.1570409504085061</v>
       </c>
       <c r="C66">
-        <v>-3461.365074627367</v>
+        <v>-3265.75393723346</v>
       </c>
       <c r="D66">
-        <v>2461.826925372633</v>
+        <v>2657.438062766541</v>
       </c>
       <c r="E66">
         <v>5219.192</v>
@@ -6705,37 +6836,37 @@
         <v>390.4</v>
       </c>
       <c r="M66">
-        <v>1307.2715136</v>
+        <v>1216.4046336</v>
       </c>
       <c r="N66">
-        <v>-916.8715136000002</v>
+        <v>-826.0046336000001</v>
       </c>
       <c r="O66">
-        <v>-256.7240238080001</v>
+        <v>-231.2812974080001</v>
       </c>
       <c r="P66">
-        <v>-660.1474897920001</v>
+        <v>-594.723336192</v>
       </c>
       <c r="Q66">
-        <v>-456.7474897920001</v>
+        <v>-391.3233361920001</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1116471085396524</v>
+        <v>0.1113268330702769</v>
       </c>
       <c r="T66">
-        <v>1.519740755273967</v>
+        <v>1.513321779914016</v>
       </c>
       <c r="U66">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.08361843646311364</v>
+        <v>0.08986483360926255</v>
       </c>
       <c r="W66">
-        <v>0.1977551414112601</v>
+        <v>0.1827551414112601</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6874,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2986372730825486</v>
+        <v>0.3209458343187949</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6885,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1684562495774813</v>
+        <v>0.1585909504085061</v>
       </c>
       <c r="C67">
-        <v>-3587.377839851647</v>
+        <v>-3393.731195878979</v>
       </c>
       <c r="D67">
-        <v>2430.467160148354</v>
+        <v>2624.113804121022</v>
       </c>
       <c r="E67">
         <v>5313.845</v>
@@ -6787,37 +6918,37 @@
         <v>390.4</v>
       </c>
       <c r="M67">
-        <v>1327.697631</v>
+        <v>1235.410956</v>
       </c>
       <c r="N67">
-        <v>-937.2976310000003</v>
+        <v>-845.0109560000002</v>
       </c>
       <c r="O67">
-        <v>-262.4433366800001</v>
+        <v>-236.6030676800001</v>
       </c>
       <c r="P67">
-        <v>-674.8542943200002</v>
+        <v>-608.4078883200001</v>
       </c>
       <c r="Q67">
-        <v>-471.4542943200003</v>
+        <v>-405.0078883200001</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1135284544979282</v>
+        <v>0.1131990283008562</v>
       </c>
       <c r="T67">
-        <v>1.563161919710366</v>
+        <v>1.556559545054416</v>
       </c>
       <c r="U67">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.08233199897906572</v>
+        <v>0.08848229770758159</v>
       </c>
       <c r="W67">
-        <v>0.1980327546203176</v>
+        <v>0.1830327546203176</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6956,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2940428534966633</v>
+        <v>0.3160082060985057</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6967,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1701562495774813</v>
+        <v>0.1601409504085061</v>
       </c>
       <c r="C68">
-        <v>-3712.601707173792</v>
+        <v>-3520.883033263441</v>
       </c>
       <c r="D68">
-        <v>2399.896292826209</v>
+        <v>2591.61496673656</v>
       </c>
       <c r="E68">
         <v>5408.498000000001</v>
@@ -6869,37 +7000,37 @@
         <v>390.4</v>
       </c>
       <c r="M68">
-        <v>1348.1237484</v>
+        <v>1254.4172784</v>
       </c>
       <c r="N68">
-        <v>-957.7237484000003</v>
+        <v>-864.0172784000002</v>
       </c>
       <c r="O68">
-        <v>-268.1626495520001</v>
+        <v>-241.9248379520001</v>
       </c>
       <c r="P68">
-        <v>-689.5610988480003</v>
+        <v>-622.0924404480002</v>
       </c>
       <c r="Q68">
-        <v>-486.1610988480003</v>
+        <v>-418.6924404480002</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1155204678655143</v>
+        <v>0.1151813526626461</v>
       </c>
       <c r="T68">
-        <v>1.609137270290083</v>
+        <v>1.602340708144252</v>
       </c>
       <c r="U68">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.08108454444907988</v>
+        <v>0.08714165683322431</v>
       </c>
       <c r="W68">
-        <v>0.1983019553078886</v>
+        <v>0.1833019553078886</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +7038,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2895876587467139</v>
+        <v>0.311220202975801</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +7049,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1718562495774813</v>
+        <v>0.1616909504085061</v>
       </c>
       <c r="C69">
-        <v>-3837.066075521604</v>
+        <v>-3647.239741983045</v>
       </c>
       <c r="D69">
-        <v>2370.084924478398</v>
+        <v>2559.911258016956</v>
       </c>
       <c r="E69">
         <v>5503.151000000001</v>
@@ -6951,37 +7082,37 @@
         <v>390.4</v>
       </c>
       <c r="M69">
-        <v>1368.5498658</v>
+        <v>1273.4236008</v>
       </c>
       <c r="N69">
-        <v>-978.1498658000004</v>
+        <v>-883.0236008000003</v>
       </c>
       <c r="O69">
-        <v>-273.8819624240001</v>
+        <v>-247.2466082240001</v>
       </c>
       <c r="P69">
-        <v>-704.2679033760003</v>
+        <v>-635.7769925760001</v>
       </c>
       <c r="Q69">
-        <v>-500.8679033760003</v>
+        <v>-432.3769925760001</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1176332093159844</v>
+        <v>0.1172838178948475</v>
       </c>
       <c r="T69">
-        <v>1.657899005753419</v>
+        <v>1.650896487178926</v>
       </c>
       <c r="U69">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.07987432736775033</v>
+        <v>0.08584103508944484</v>
       </c>
       <c r="W69">
-        <v>0.1985631201540395</v>
+        <v>0.1835631201540395</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +7120,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2852654548848226</v>
+        <v>0.3065751253194458</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7131,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1735562495774813</v>
+        <v>0.1632409504085061</v>
       </c>
       <c r="C70">
-        <v>-3960.798900978911</v>
+        <v>-3772.830150248206</v>
       </c>
       <c r="D70">
-        <v>2341.005099021091</v>
+        <v>2528.973849751796</v>
       </c>
       <c r="E70">
         <v>5597.804000000001</v>
@@ -7033,37 +7164,37 @@
         <v>390.4</v>
       </c>
       <c r="M70">
-        <v>1388.9759832</v>
+        <v>1292.4299232</v>
       </c>
       <c r="N70">
-        <v>-998.5759832000005</v>
+        <v>-902.0299232000003</v>
       </c>
       <c r="O70">
-        <v>-279.6012752960002</v>
+        <v>-252.5683784960001</v>
       </c>
       <c r="P70">
-        <v>-718.9747079040003</v>
+        <v>-649.4615447040002</v>
       </c>
       <c r="Q70">
-        <v>-515.5747079040003</v>
+        <v>-446.0615447040002</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1198779971071089</v>
+        <v>0.1195176872040615</v>
       </c>
       <c r="T70">
-        <v>1.709708349683213</v>
+        <v>1.702487002403268</v>
       </c>
       <c r="U70">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.07869970490645987</v>
+        <v>0.08457866692636475</v>
       </c>
       <c r="W70">
-        <v>0.198816603681186</v>
+        <v>0.183816603681186</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7202,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2810703746659281</v>
+        <v>0.3020666675941598</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7213,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1752562495774813</v>
+        <v>0.1647909504085061</v>
       </c>
       <c r="C71">
-        <v>-4083.826784227768</v>
+        <v>-3897.681709314937</v>
       </c>
       <c r="D71">
-        <v>2312.630215772234</v>
+        <v>2498.775290685065</v>
       </c>
       <c r="E71">
         <v>5692.457000000001</v>
@@ -7115,37 +7246,37 @@
         <v>390.4</v>
       </c>
       <c r="M71">
-        <v>1409.4021006</v>
+        <v>1311.4362456</v>
       </c>
       <c r="N71">
-        <v>-1019.002100600001</v>
+        <v>-921.0362456000004</v>
       </c>
       <c r="O71">
-        <v>-285.3205881680002</v>
+        <v>-257.8901487680001</v>
       </c>
       <c r="P71">
-        <v>-733.6815124320003</v>
+        <v>-663.1460968320002</v>
       </c>
       <c r="Q71">
-        <v>-530.2815124320003</v>
+        <v>-459.7460968320003</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1222676099170157</v>
+        <v>0.1218956771138699</v>
       </c>
       <c r="T71">
-        <v>1.764860231931059</v>
+        <v>1.757405937964664</v>
       </c>
       <c r="U71">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.07755912947303292</v>
+        <v>0.08335288914482324</v>
       </c>
       <c r="W71">
-        <v>0.1990627398597195</v>
+        <v>0.1840627398597195</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7284,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2769968909751176</v>
+        <v>0.2976888898029401</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7295,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1769562495774813</v>
+        <v>0.1663409504085061</v>
       </c>
       <c r="C72">
-        <v>-4206.175051707594</v>
+        <v>-4021.820574726044</v>
       </c>
       <c r="D72">
-        <v>2284.934948292407</v>
+        <v>2469.289425273957</v>
       </c>
       <c r="E72">
         <v>5787.110000000001</v>
@@ -7197,37 +7328,37 @@
         <v>390.4</v>
       </c>
       <c r="M72">
-        <v>1429.828218</v>
+        <v>1330.442568</v>
       </c>
       <c r="N72">
-        <v>-1039.428218</v>
+        <v>-940.0425680000002</v>
       </c>
       <c r="O72">
-        <v>-291.0399010400001</v>
+        <v>-263.2119190400001</v>
       </c>
       <c r="P72">
-        <v>-748.3883169600003</v>
+        <v>-676.8306489600002</v>
       </c>
       <c r="Q72">
-        <v>-544.9883169600004</v>
+        <v>-473.4306489600002</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1248165302475829</v>
+        <v>0.1244321996843323</v>
       </c>
       <c r="T72">
-        <v>1.823688906328761</v>
+        <v>1.815986135896819</v>
       </c>
       <c r="U72">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.07645114190913246</v>
+        <v>0.08216213358561149</v>
       </c>
       <c r="W72">
-        <v>0.1993018435760092</v>
+        <v>0.1843018435760092</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7366,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2730397925326158</v>
+        <v>0.2934361913771838</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7377,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1786562495774813</v>
+        <v>0.1678909504085062</v>
       </c>
       <c r="C73">
-        <v>-4327.867831011723</v>
+        <v>-4145.271681867445</v>
       </c>
       <c r="D73">
-        <v>2257.895168988277</v>
+        <v>2440.491318132556</v>
       </c>
       <c r="E73">
         <v>5881.763</v>
@@ -7279,37 +7410,37 @@
         <v>390.4</v>
       </c>
       <c r="M73">
-        <v>1450.2543354</v>
+        <v>1349.4488904</v>
       </c>
       <c r="N73">
-        <v>-1059.8543354</v>
+        <v>-959.0488904000002</v>
       </c>
       <c r="O73">
-        <v>-296.7592139120001</v>
+        <v>-268.5336893120001</v>
       </c>
       <c r="P73">
-        <v>-763.0951214880001</v>
+        <v>-690.5152010880001</v>
       </c>
       <c r="Q73">
-        <v>-559.6951214880002</v>
+        <v>-487.1152010880002</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1275412381871547</v>
+        <v>0.127143654845861</v>
       </c>
       <c r="T73">
-        <v>1.886574730684925</v>
+        <v>1.878606347479468</v>
       </c>
       <c r="U73">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.07537436526252497</v>
+        <v>0.08100492043651837</v>
       </c>
       <c r="W73">
-        <v>0.1995342119763471</v>
+        <v>0.1845342119763471</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7448,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2691941616518748</v>
+        <v>0.2893032872732798</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7459,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1803562495774813</v>
+        <v>0.1694409504085061</v>
       </c>
       <c r="C74">
-        <v>-4448.92812099312</v>
+        <v>-4268.058816298388</v>
       </c>
       <c r="D74">
-        <v>2231.487879006881</v>
+        <v>2412.357183701613</v>
       </c>
       <c r="E74">
         <v>5976.416</v>
@@ -7361,37 +7492,37 @@
         <v>390.4</v>
       </c>
       <c r="M74">
-        <v>1470.6804528</v>
+        <v>1368.4552128</v>
       </c>
       <c r="N74">
-        <v>-1080.2804528</v>
+        <v>-978.0552128000003</v>
       </c>
       <c r="O74">
-        <v>-302.4785267840001</v>
+        <v>-273.8554595840001</v>
       </c>
       <c r="P74">
-        <v>-777.8019260160002</v>
+        <v>-704.1997532160001</v>
       </c>
       <c r="Q74">
-        <v>-574.4019260160002</v>
+        <v>-500.7997532160001</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1304605681224102</v>
+        <v>0.1300487853760703</v>
       </c>
       <c r="T74">
-        <v>1.953952399637958</v>
+        <v>1.94569943131802</v>
       </c>
       <c r="U74">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.07432749907832323</v>
+        <v>0.07987985209712227</v>
       </c>
       <c r="W74">
-        <v>0.1997601256988979</v>
+        <v>0.1847601256988979</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7530,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2654553538511545</v>
+        <v>0.2852851860611509</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7541,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1820562495774813</v>
+        <v>0.1709909504085061</v>
       </c>
       <c r="C75">
-        <v>-4569.377857007441</v>
+        <v>-4390.204679272492</v>
       </c>
       <c r="D75">
-        <v>2205.69114299256</v>
+        <v>2384.864320727508</v>
       </c>
       <c r="E75">
         <v>6071.069</v>
@@ -7443,37 +7574,37 @@
         <v>390.4</v>
       </c>
       <c r="M75">
-        <v>1491.1065702</v>
+        <v>1387.4615352</v>
       </c>
       <c r="N75">
-        <v>-1100.7065702</v>
+        <v>-997.0615352000003</v>
       </c>
       <c r="O75">
-        <v>-308.1978396560002</v>
+        <v>-279.1772298560001</v>
       </c>
       <c r="P75">
-        <v>-792.5087305440003</v>
+        <v>-717.8843053440003</v>
       </c>
       <c r="Q75">
-        <v>-589.1087305440003</v>
+        <v>-514.4843053440003</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1335961447195365</v>
+        <v>0.1331691107603692</v>
       </c>
       <c r="T75">
-        <v>2.026321007031956</v>
+        <v>2.017762373218687</v>
       </c>
       <c r="U75">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.07330931415944208</v>
+        <v>0.07878560754784662</v>
       </c>
       <c r="W75">
-        <v>0.1999798500043924</v>
+        <v>0.1849798500043924</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7612,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2618189791408645</v>
+        <v>0.2813771698137379</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7623,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1837562495774813</v>
+        <v>0.1725409504085061</v>
       </c>
       <c r="C76">
-        <v>-4689.237971682421</v>
+        <v>-4511.730948828927</v>
       </c>
       <c r="D76">
-        <v>2180.48402831758</v>
+        <v>2357.991051171075</v>
       </c>
       <c r="E76">
         <v>6165.722000000001</v>
@@ -7525,37 +7656,37 @@
         <v>390.4</v>
       </c>
       <c r="M76">
-        <v>1511.5326876</v>
+        <v>1406.4678576</v>
       </c>
       <c r="N76">
-        <v>-1121.1326876</v>
+        <v>-1016.0678576</v>
       </c>
       <c r="O76">
-        <v>-313.9171525280001</v>
+        <v>-284.4990001280001</v>
       </c>
       <c r="P76">
-        <v>-807.2155350720002</v>
+        <v>-731.5688574720002</v>
       </c>
       <c r="Q76">
-        <v>-603.8155350720002</v>
+        <v>-528.1688574720002</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1369729195164417</v>
+        <v>0.1365294611742295</v>
       </c>
       <c r="T76">
-        <v>2.104256430379339</v>
+        <v>2.095368618342483</v>
       </c>
       <c r="U76">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.07231864775188204</v>
+        <v>0.07772093717557843</v>
       </c>
       <c r="W76">
-        <v>0.2001936358151439</v>
+        <v>0.1851936358151438</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7694,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2582808848281503</v>
+        <v>0.2775747756270658</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7705,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1854562495774813</v>
+        <v>0.1740909504085061</v>
       </c>
       <c r="C77">
-        <v>-4808.528451567418</v>
+        <v>-4632.658336799266</v>
       </c>
       <c r="D77">
-        <v>2155.846548432582</v>
+        <v>2331.716663200734</v>
       </c>
       <c r="E77">
         <v>6260.375</v>
@@ -7607,37 +7738,37 @@
         <v>390.4</v>
       </c>
       <c r="M77">
-        <v>1531.958805</v>
+        <v>1425.47418</v>
       </c>
       <c r="N77">
-        <v>-1141.558805</v>
+        <v>-1035.07418</v>
       </c>
       <c r="O77">
-        <v>-319.6364654000001</v>
+        <v>-289.8207704000001</v>
       </c>
       <c r="P77">
-        <v>-821.9223396</v>
+        <v>-745.2534095999999</v>
       </c>
       <c r="Q77">
-        <v>-618.5223396</v>
+        <v>-541.8534096</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1406198362970994</v>
+        <v>0.1401586396211987</v>
       </c>
       <c r="T77">
-        <v>2.188426687594513</v>
+        <v>2.179183363076183</v>
       </c>
       <c r="U77">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.0713543991151903</v>
+        <v>0.07668465801323739</v>
       </c>
       <c r="W77">
-        <v>0.200401720670942</v>
+        <v>0.1854017206709419</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7776,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2548371396971083</v>
+        <v>0.273873778618705</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7787,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1871562495774813</v>
+        <v>0.1756409504085061</v>
       </c>
       <c r="C78">
-        <v>-4927.26838998536</v>
+        <v>-4753.006642045108</v>
       </c>
       <c r="D78">
-        <v>2131.759610014641</v>
+        <v>2306.021357954893</v>
       </c>
       <c r="E78">
         <v>6355.028</v>
@@ -7689,37 +7820,37 @@
         <v>390.4</v>
       </c>
       <c r="M78">
-        <v>1552.3849224</v>
+        <v>1444.4805024</v>
       </c>
       <c r="N78">
-        <v>-1161.9849224</v>
+        <v>-1054.0805024</v>
       </c>
       <c r="O78">
-        <v>-325.3557782720001</v>
+        <v>-295.1425406720001</v>
       </c>
       <c r="P78">
-        <v>-836.6291441280002</v>
+        <v>-758.9379617280001</v>
       </c>
       <c r="Q78">
-        <v>-633.2291441280003</v>
+        <v>-555.5379617280001</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1445706628094786</v>
+        <v>0.1440902496054153</v>
       </c>
       <c r="T78">
-        <v>2.279611132910951</v>
+        <v>2.269982669871024</v>
       </c>
       <c r="U78">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.070415525442622</v>
+        <v>0.07567564935516846</v>
       </c>
       <c r="W78">
-        <v>0.2006043296094822</v>
+        <v>0.1856043296094822</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7858,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2514840194379356</v>
+        <v>0.2702701762684588</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7869,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1888562495774813</v>
+        <v>0.1771909504085061</v>
       </c>
       <c r="C79">
-        <v>-5045.476036380767</v>
+        <v>-4872.794800213973</v>
       </c>
       <c r="D79">
-        <v>2108.204963619233</v>
+        <v>2280.886199786029</v>
       </c>
       <c r="E79">
         <v>6449.681</v>
@@ -7771,37 +7902,37 @@
         <v>390.4</v>
       </c>
       <c r="M79">
-        <v>1572.8110398</v>
+        <v>1463.4868248</v>
       </c>
       <c r="N79">
-        <v>-1182.4110398</v>
+        <v>-1073.0868248</v>
       </c>
       <c r="O79">
-        <v>-331.0750911440001</v>
+        <v>-300.4643109440001</v>
       </c>
       <c r="P79">
-        <v>-851.3359486560001</v>
+        <v>-772.6225138560001</v>
       </c>
       <c r="Q79">
-        <v>-647.9359486560002</v>
+        <v>-569.2225138560001</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1488650394533689</v>
+        <v>0.1483637387186943</v>
       </c>
       <c r="T79">
-        <v>2.378724660428818</v>
+        <v>2.368677568561068</v>
       </c>
       <c r="U79">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.06950103809921133</v>
+        <v>0.07469284871419227</v>
       </c>
       <c r="W79">
-        <v>0.2008016759781902</v>
+        <v>0.1858016759781902</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7940,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2482179932114691</v>
+        <v>0.2667601739792581</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7951,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1905562495774814</v>
+        <v>0.1787409504085061</v>
       </c>
       <c r="C80">
-        <v>-5163.16884243198</v>
+        <v>-4992.040930276355</v>
       </c>
       <c r="D80">
-        <v>2085.165157568022</v>
+        <v>2256.293069723646</v>
       </c>
       <c r="E80">
         <v>6544.334000000001</v>
@@ -7853,37 +7984,37 @@
         <v>390.4</v>
       </c>
       <c r="M80">
-        <v>1593.2371572</v>
+        <v>1482.4931472</v>
       </c>
       <c r="N80">
-        <v>-1202.837157200001</v>
+        <v>-1092.0931472</v>
       </c>
       <c r="O80">
-        <v>-336.7944040160002</v>
+        <v>-305.7860812160001</v>
       </c>
       <c r="P80">
-        <v>-866.0427531840004</v>
+        <v>-786.3070659840001</v>
       </c>
       <c r="Q80">
-        <v>-662.6427531840004</v>
+        <v>-582.9070659840002</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1535498139739766</v>
+        <v>0.1530257268422713</v>
       </c>
       <c r="T80">
-        <v>2.486848508630128</v>
+        <v>2.47634473076839</v>
       </c>
       <c r="U80">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.06860999914922143</v>
+        <v>0.07373524808965133</v>
       </c>
       <c r="W80">
-        <v>0.2009939621835981</v>
+        <v>0.185993962183598</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +8022,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2450357112472193</v>
+        <v>0.2633401717487548</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +8033,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1922562495774813</v>
+        <v>0.1802909504085061</v>
       </c>
       <c r="C81">
-        <v>-5280.36350517236</v>
+        <v>-5110.762378084219</v>
       </c>
       <c r="D81">
-        <v>2062.623494827641</v>
+        <v>2232.224621915783</v>
       </c>
       <c r="E81">
         <v>6638.987000000001</v>
@@ -7935,37 +8066,37 @@
         <v>390.4</v>
       </c>
       <c r="M81">
-        <v>1613.6632746</v>
+        <v>1501.4994696</v>
       </c>
       <c r="N81">
-        <v>-1223.2632746</v>
+        <v>-1111.0994696</v>
       </c>
       <c r="O81">
-        <v>-342.5137168880001</v>
+        <v>-311.1078514880001</v>
       </c>
       <c r="P81">
-        <v>-880.7495577120003</v>
+        <v>-799.9916181120002</v>
       </c>
       <c r="Q81">
-        <v>-677.3495577120003</v>
+        <v>-596.5916181120002</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1586807574965469</v>
+        <v>0.1581317138347604</v>
       </c>
       <c r="T81">
-        <v>2.605269866183944</v>
+        <v>2.594265908424027</v>
       </c>
       <c r="U81">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.06774151814733255</v>
+        <v>0.07280189051889624</v>
       </c>
       <c r="W81">
-        <v>0.2011813803838056</v>
+        <v>0.1861813803838056</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +8104,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2419339933833305</v>
+        <v>0.2600067518532009</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +8115,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1939562495774813</v>
+        <v>0.1818409504085061</v>
       </c>
       <c r="C82">
-        <v>-5397.076007344481</v>
+        <v>-5228.975757171025</v>
       </c>
       <c r="D82">
-        <v>2040.563992655521</v>
+        <v>2208.664242828976</v>
       </c>
       <c r="E82">
         <v>6733.640000000001</v>
@@ -8017,37 +8148,37 @@
         <v>390.4</v>
       </c>
       <c r="M82">
-        <v>1634.089392000001</v>
+        <v>1520.505792</v>
       </c>
       <c r="N82">
-        <v>-1243.689392000001</v>
+        <v>-1130.105792</v>
       </c>
       <c r="O82">
-        <v>-348.2330297600002</v>
+        <v>-316.4296217600001</v>
       </c>
       <c r="P82">
-        <v>-895.4563622400004</v>
+        <v>-813.6761702400001</v>
       </c>
       <c r="Q82">
-        <v>-692.0563622400005</v>
+        <v>-610.2761702400002</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1643247953713743</v>
+        <v>0.1637482995264984</v>
       </c>
       <c r="T82">
-        <v>2.735533359493142</v>
+        <v>2.723979203845229</v>
       </c>
       <c r="U82">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.06689474917049089</v>
+        <v>0.07189186688741005</v>
       </c>
       <c r="W82">
-        <v>0.2013641131290081</v>
+        <v>0.1863641131290081</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8186,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2389098184660388</v>
+        <v>0.2567566674550359</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8197,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1956562495774813</v>
+        <v>0.1833909504085061</v>
       </c>
       <c r="C83">
-        <v>-5513.321655192195</v>
+        <v>-5346.696986994966</v>
       </c>
       <c r="D83">
-        <v>2018.971344807806</v>
+        <v>2185.596013005035</v>
       </c>
       <c r="E83">
         <v>6828.293000000001</v>
@@ -8099,37 +8230,37 @@
         <v>390.4</v>
       </c>
       <c r="M83">
-        <v>1654.5155094</v>
+        <v>1539.5121144</v>
       </c>
       <c r="N83">
-        <v>-1264.115509400001</v>
+        <v>-1149.1121144</v>
       </c>
       <c r="O83">
-        <v>-353.9523426320002</v>
+        <v>-321.7513920320001</v>
       </c>
       <c r="P83">
-        <v>-910.1631667680003</v>
+        <v>-827.3607223680002</v>
       </c>
       <c r="Q83">
-        <v>-706.7631667680004</v>
+        <v>-623.9607223680002</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1705629424961835</v>
+        <v>0.1699561047647352</v>
       </c>
       <c r="T83">
-        <v>2.879508799466465</v>
+        <v>2.867346530363399</v>
       </c>
       <c r="U83">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.06606888806962065</v>
+        <v>0.07100431297521979</v>
       </c>
       <c r="W83">
-        <v>0.2015423339545759</v>
+        <v>0.1865423339545759</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8268,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2359603145343594</v>
+        <v>0.2535868320543563</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8279,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1973562495774813</v>
+        <v>0.1849409504085062</v>
       </c>
       <c r="C84">
-        <v>-5629.115113878413</v>
+        <v>-5463.941328810393</v>
       </c>
       <c r="D84">
-        <v>1997.830886121588</v>
+        <v>2163.004671189608</v>
       </c>
       <c r="E84">
         <v>6922.946000000001</v>
@@ -8181,37 +8312,37 @@
         <v>390.4</v>
       </c>
       <c r="M84">
-        <v>1674.9416268</v>
+        <v>1558.5184368</v>
       </c>
       <c r="N84">
-        <v>-1284.5416268</v>
+        <v>-1168.1184368</v>
       </c>
       <c r="O84">
-        <v>-359.6716555040001</v>
+        <v>-327.0731623040002</v>
       </c>
       <c r="P84">
-        <v>-924.8699712960002</v>
+        <v>-841.0452744960003</v>
       </c>
       <c r="Q84">
-        <v>-721.4699712960003</v>
+        <v>-637.6452744960003</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1774942170793048</v>
+        <v>0.1768536661405538</v>
       </c>
       <c r="T84">
-        <v>3.039481510547935</v>
+        <v>3.026643559828032</v>
       </c>
       <c r="U84">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.06526316992243014</v>
+        <v>0.07013840671942442</v>
       </c>
       <c r="W84">
-        <v>0.2017162079307396</v>
+        <v>0.1867162079307396</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8350,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2330827497229648</v>
+        <v>0.2504943097122301</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8361,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1990562495774813</v>
+        <v>0.1864909504085061</v>
       </c>
       <c r="C85">
-        <v>-5744.470440700778</v>
+        <v>-5580.723419337306</v>
       </c>
       <c r="D85">
-        <v>1977.128559299223</v>
+        <v>2140.875580662695</v>
       </c>
       <c r="E85">
         <v>7017.599000000001</v>
@@ -8263,37 +8394,37 @@
         <v>390.4</v>
       </c>
       <c r="M85">
-        <v>1695.367744200001</v>
+        <v>1577.5247592</v>
       </c>
       <c r="N85">
-        <v>-1304.967744200001</v>
+        <v>-1187.1247592</v>
       </c>
       <c r="O85">
-        <v>-365.3909683760002</v>
+        <v>-332.3949325760001</v>
       </c>
       <c r="P85">
-        <v>-939.5767758240004</v>
+        <v>-854.7298266240002</v>
       </c>
       <c r="Q85">
-        <v>-736.1767758240004</v>
+        <v>-651.3298266240002</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1852409357310286</v>
+        <v>0.1845627053252923</v>
       </c>
       <c r="T85">
-        <v>3.218274540580166</v>
+        <v>3.204681416288505</v>
       </c>
       <c r="U85">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.06447686667035267</v>
+        <v>0.0692933656746121</v>
       </c>
       <c r="W85">
-        <v>0.2018858921725379</v>
+        <v>0.1868858921725379</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8432,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.230274523822688</v>
+        <v>0.2474763059807573</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8443,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2007562495774813</v>
+        <v>0.1880409504085061</v>
       </c>
       <c r="C86">
-        <v>-5859.401116263394</v>
+        <v>-5697.057302385</v>
       </c>
       <c r="D86">
-        <v>1956.850883736606</v>
+        <v>2119.194697615001</v>
       </c>
       <c r="E86">
         <v>7112.252</v>
@@ -8345,37 +8476,37 @@
         <v>390.4</v>
       </c>
       <c r="M86">
-        <v>1715.7938616</v>
+        <v>1596.5310816</v>
       </c>
       <c r="N86">
-        <v>-1325.3938616</v>
+        <v>-1206.1310816</v>
       </c>
       <c r="O86">
-        <v>-371.1102812480001</v>
+        <v>-337.716702848</v>
       </c>
       <c r="P86">
-        <v>-954.2835803520004</v>
+        <v>-868.4143787519999</v>
       </c>
       <c r="Q86">
-        <v>-750.8835803520004</v>
+        <v>-665.014378752</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.1939559942142178</v>
+        <v>0.193235374408123</v>
       </c>
       <c r="T86">
-        <v>3.419416699366425</v>
+        <v>3.404974004806535</v>
       </c>
       <c r="U86">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.06370928492427705</v>
+        <v>0.06846844465467625</v>
       </c>
       <c r="W86">
-        <v>0.202051536313341</v>
+        <v>0.187051536313341</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8514,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2275331604438465</v>
+        <v>0.2445301594809867</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8525,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2024562495774813</v>
+        <v>0.1895909504085062</v>
       </c>
       <c r="C87">
-        <v>-5973.920073749795</v>
+        <v>-5812.956458573428</v>
       </c>
       <c r="D87">
-        <v>1936.984926250206</v>
+        <v>2097.948541426573</v>
       </c>
       <c r="E87">
         <v>7206.905000000001</v>
@@ -8427,37 +8558,37 @@
         <v>390.4</v>
       </c>
       <c r="M87">
-        <v>1736.219979</v>
+        <v>1615.537404</v>
       </c>
       <c r="N87">
-        <v>-1345.819979</v>
+        <v>-1225.137404</v>
       </c>
       <c r="O87">
-        <v>-376.8295941200001</v>
+        <v>-343.03847312</v>
       </c>
       <c r="P87">
-        <v>-968.9903848800002</v>
+        <v>-882.09893088</v>
       </c>
       <c r="Q87">
-        <v>-765.5903848800002</v>
+        <v>-678.69893088</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2038330604951657</v>
+        <v>0.2030643993686645</v>
       </c>
       <c r="T87">
-        <v>3.64737781265752</v>
+        <v>3.631972271793637</v>
       </c>
       <c r="U87">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.0629597639251679</v>
+        <v>0.06766293354109182</v>
       </c>
       <c r="W87">
-        <v>0.2022132829449488</v>
+        <v>0.1872132829449488</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8596,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2248562997327426</v>
+        <v>0.241653334075328</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8607,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2041562495774813</v>
+        <v>0.1911409504085061</v>
       </c>
       <c r="C88">
-        <v>-6088.039726430748</v>
+        <v>-5928.433833284475</v>
       </c>
       <c r="D88">
-        <v>1917.518273569253</v>
+        <v>2077.124166715527</v>
       </c>
       <c r="E88">
         <v>7301.558000000001</v>
@@ -8509,37 +8640,37 @@
         <v>390.4</v>
       </c>
       <c r="M88">
-        <v>1756.6460964</v>
+        <v>1634.5437264</v>
       </c>
       <c r="N88">
-        <v>-1366.246096400001</v>
+        <v>-1244.1437264</v>
       </c>
       <c r="O88">
-        <v>-382.5489069920002</v>
+        <v>-348.3602433920001</v>
       </c>
       <c r="P88">
-        <v>-983.6971894080004</v>
+        <v>-895.7834830080001</v>
       </c>
       <c r="Q88">
-        <v>-780.2971894080005</v>
+        <v>-692.3834830080001</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2151211362448204</v>
+        <v>0.2142975707521406</v>
       </c>
       <c r="T88">
-        <v>3.907904799275915</v>
+        <v>3.89139886263604</v>
       </c>
       <c r="U88">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.06222767364696827</v>
+        <v>0.06687615524410237</v>
       </c>
       <c r="W88">
-        <v>0.2023712680269843</v>
+        <v>0.1873712680269843</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8678,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2222416915963152</v>
+        <v>0.2388434115860799</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8689,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2058562495774813</v>
+        <v>0.1926909504085061</v>
       </c>
       <c r="C89">
-        <v>-6201.771993529886</v>
+        <v>-6043.501862964909</v>
       </c>
       <c r="D89">
-        <v>1898.439006470115</v>
+        <v>2056.709137035092</v>
       </c>
       <c r="E89">
         <v>7396.211000000001</v>
@@ -8591,37 +8722,37 @@
         <v>390.4</v>
       </c>
       <c r="M89">
-        <v>1777.072213800001</v>
+        <v>1653.5500488</v>
       </c>
       <c r="N89">
-        <v>-1386.6722138</v>
+        <v>-1263.150048800001</v>
       </c>
       <c r="O89">
-        <v>-388.2682198640002</v>
+        <v>-353.6820136640002</v>
       </c>
       <c r="P89">
-        <v>-998.4039939360002</v>
+        <v>-909.4680351360005</v>
       </c>
       <c r="Q89">
-        <v>-795.0039939360003</v>
+        <v>-706.0680351360005</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2281458390328835</v>
+        <v>0.2272589223484591</v>
       </c>
       <c r="T89">
-        <v>4.208512860758677</v>
+        <v>4.190737236684966</v>
       </c>
       <c r="U89">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.06151241303033645</v>
+        <v>0.06610746380451497</v>
       </c>
       <c r="W89">
-        <v>0.2025256212680534</v>
+        <v>0.1875256212680534</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8760,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2196871893940588</v>
+        <v>0.2360980850161248</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8771,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2075562495774813</v>
+        <v>0.1942409504085061</v>
       </c>
       <c r="C90">
-        <v>-6315.12832456033</v>
+        <v>-6158.172499893335</v>
       </c>
       <c r="D90">
-        <v>1879.735675439672</v>
+        <v>2036.691500106667</v>
       </c>
       <c r="E90">
         <v>7490.864000000001</v>
@@ -8673,37 +8804,37 @@
         <v>390.4</v>
       </c>
       <c r="M90">
-        <v>1797.498331200001</v>
+        <v>1672.556371200001</v>
       </c>
       <c r="N90">
-        <v>-1407.098331200001</v>
+        <v>-1282.156371200001</v>
       </c>
       <c r="O90">
-        <v>-393.9875327360003</v>
+        <v>-359.0037839360002</v>
       </c>
       <c r="P90">
-        <v>-1013.110798464</v>
+        <v>-923.1525872640004</v>
       </c>
       <c r="Q90">
-        <v>-809.7107984640005</v>
+        <v>-719.7525872640005</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2433413256189572</v>
+        <v>0.2423804992108307</v>
       </c>
       <c r="T90">
-        <v>4.559222265821901</v>
+        <v>4.539965339742047</v>
       </c>
       <c r="U90">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.06081340833680991</v>
+        <v>0.06535624262491821</v>
       </c>
       <c r="W90">
-        <v>0.2026764664809164</v>
+        <v>0.1876764664809164</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8842,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2171907440600352</v>
+        <v>0.2334151522318507</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8853,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2092562495774813</v>
+        <v>0.1957909504085061</v>
       </c>
       <c r="C91">
-        <v>-6428.119722236798</v>
+        <v>-6272.457235514737</v>
       </c>
       <c r="D91">
-        <v>1861.397277763202</v>
+        <v>2017.059764485263</v>
       </c>
       <c r="E91">
         <v>7585.517</v>
@@ -8755,37 +8886,37 @@
         <v>390.4</v>
       </c>
       <c r="M91">
-        <v>1817.9244486</v>
+        <v>1691.5626936</v>
       </c>
       <c r="N91">
-        <v>-1427.5244486</v>
+        <v>-1301.1626936</v>
       </c>
       <c r="O91">
-        <v>-399.7068456080001</v>
+        <v>-364.3255542080001</v>
       </c>
       <c r="P91">
-        <v>-1027.817602992</v>
+        <v>-936.8371393920002</v>
       </c>
       <c r="Q91">
-        <v>-824.4176029920001</v>
+        <v>-733.4371393920002</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2612996279479533</v>
+        <v>0.2602514536845426</v>
       </c>
       <c r="T91">
-        <v>4.973697017260256</v>
+        <v>4.95268946153678</v>
       </c>
       <c r="U91">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.0601301116139244</v>
+        <v>0.06462190282014386</v>
       </c>
       <c r="W91">
-        <v>0.2028239219137151</v>
+        <v>0.1878239219137151</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8924,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2147503986211586</v>
+        <v>0.2307925100719423</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8935,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2109562495774813</v>
+        <v>0.1973409504085061</v>
       </c>
       <c r="C92">
-        <v>-6540.756764059508</v>
+        <v>-6386.367122438415</v>
       </c>
       <c r="D92">
-        <v>1843.413235940492</v>
+        <v>1997.802877561585</v>
       </c>
       <c r="E92">
         <v>7680.17</v>
@@ -8837,37 +8968,37 @@
         <v>390.4</v>
       </c>
       <c r="M92">
-        <v>1838.350566</v>
+        <v>1710.569016</v>
       </c>
       <c r="N92">
-        <v>-1447.950566</v>
+        <v>-1320.169016</v>
       </c>
       <c r="O92">
-        <v>-405.4261584800001</v>
+        <v>-369.6473244800001</v>
       </c>
       <c r="P92">
-        <v>-1042.52440752</v>
+        <v>-950.5216915200001</v>
       </c>
       <c r="Q92">
-        <v>-839.1244075200003</v>
+        <v>-747.1216915200001</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.2828495907427486</v>
+        <v>0.2816965990529969</v>
       </c>
       <c r="T92">
-        <v>5.471066718986282</v>
+        <v>5.447958407690458</v>
       </c>
       <c r="U92">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.05946199926265858</v>
+        <v>0.06390388167769782</v>
       </c>
       <c r="W92">
-        <v>0.2029681005591183</v>
+        <v>0.1879681005591183</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +9006,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2123642830809235</v>
+        <v>0.2282281488489207</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +9017,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2126562495774813</v>
+        <v>0.1988909504085061</v>
       </c>
       <c r="C93">
-        <v>-6653.049622658824</v>
+        <v>-6499.912795187706</v>
       </c>
       <c r="D93">
-        <v>1825.773377341177</v>
+        <v>1978.910204812294</v>
       </c>
       <c r="E93">
         <v>7774.823</v>
@@ -8919,37 +9050,37 @@
         <v>390.4</v>
       </c>
       <c r="M93">
-        <v>1858.7766834</v>
+        <v>1729.5753384</v>
       </c>
       <c r="N93">
-        <v>-1468.3766834</v>
+        <v>-1339.1753384</v>
       </c>
       <c r="O93">
-        <v>-411.1454713520001</v>
+        <v>-374.9690947520001</v>
       </c>
       <c r="P93">
-        <v>-1057.231212048</v>
+        <v>-964.2062436480003</v>
       </c>
       <c r="Q93">
-        <v>-853.8312120480001</v>
+        <v>-760.8062436480003</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.3091884341586096</v>
+        <v>0.3079073322811076</v>
       </c>
       <c r="T93">
-        <v>6.078963021095871</v>
+        <v>6.053287119656064</v>
       </c>
       <c r="U93">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.05880857069933266</v>
+        <v>0.06320164121970114</v>
       </c>
       <c r="W93">
-        <v>0.203109110443084</v>
+        <v>0.188109110443084</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +9088,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2100306096404738</v>
+        <v>0.2257201472132183</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +9099,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2143562495774813</v>
+        <v>0.2004409504085062</v>
       </c>
       <c r="C94">
-        <v>-6765.008084982915</v>
+        <v>-6613.104489783423</v>
       </c>
       <c r="D94">
-        <v>1808.467915017086</v>
+        <v>1960.371510216578</v>
       </c>
       <c r="E94">
         <v>7869.476000000001</v>
@@ -9001,37 +9132,37 @@
         <v>390.4</v>
       </c>
       <c r="M94">
-        <v>1879.2028008</v>
+        <v>1748.5816608</v>
       </c>
       <c r="N94">
-        <v>-1488.802800800001</v>
+        <v>-1358.1816608</v>
       </c>
       <c r="O94">
-        <v>-416.8647842240002</v>
+        <v>-380.2908650240001</v>
       </c>
       <c r="P94">
-        <v>-1071.938016576</v>
+        <v>-977.8907957760002</v>
       </c>
       <c r="Q94">
-        <v>-868.5380165760004</v>
+        <v>-774.4907957760003</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3421119884284359</v>
+        <v>0.3406707488162461</v>
       </c>
       <c r="T94">
-        <v>6.838833398732856</v>
+        <v>6.809948009613074</v>
       </c>
       <c r="U94">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.05816934710477469</v>
+        <v>0.06251466685861744</v>
       </c>
       <c r="W94">
-        <v>0.2032470548947896</v>
+        <v>0.1882470548947896</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9170,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2077476682313382</v>
+        <v>0.223266667352205</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9181,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2160562495774813</v>
+        <v>0.2019909504085061</v>
       </c>
       <c r="C95">
-        <v>-6876.641570404439</v>
+        <v>-6725.952062236724</v>
       </c>
       <c r="D95">
-        <v>1791.487429595561</v>
+        <v>1942.176937763277</v>
       </c>
       <c r="E95">
         <v>7964.129000000001</v>
@@ -9083,37 +9214,37 @@
         <v>390.4</v>
       </c>
       <c r="M95">
-        <v>1899.6289182</v>
+        <v>1767.5879832</v>
       </c>
       <c r="N95">
-        <v>-1509.2289182</v>
+        <v>-1377.1879832</v>
       </c>
       <c r="O95">
-        <v>-422.5840970960002</v>
+        <v>-385.6126352960002</v>
       </c>
       <c r="P95">
-        <v>-1086.644821104</v>
+        <v>-991.5753479040002</v>
       </c>
       <c r="Q95">
-        <v>-883.2448211040002</v>
+        <v>-788.1753479040002</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.384442272489641</v>
+        <v>0.3827951415042814</v>
       </c>
       <c r="T95">
-        <v>7.815809598551835</v>
+        <v>7.782797725272086</v>
       </c>
       <c r="U95">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.05754387025418572</v>
+        <v>0.06184246613970757</v>
       </c>
       <c r="W95">
-        <v>0.2033820327991467</v>
+        <v>0.1883820327991467</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9252,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2055138223363776</v>
+        <v>0.2208659504989555</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9263,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2177562495774814</v>
+        <v>0.2035409504085062</v>
       </c>
       <c r="C96">
-        <v>-6987.959147816643</v>
+        <v>-6838.465006021661</v>
       </c>
       <c r="D96">
-        <v>1774.822852183358</v>
+        <v>1924.316993978341</v>
       </c>
       <c r="E96">
         <v>8058.782000000001</v>
@@ -9165,37 +9296,37 @@
         <v>390.4</v>
       </c>
       <c r="M96">
-        <v>1920.055035600001</v>
+        <v>1786.5943056</v>
       </c>
       <c r="N96">
-        <v>-1529.655035600001</v>
+        <v>-1396.1943056</v>
       </c>
       <c r="O96">
-        <v>-428.3034099680002</v>
+        <v>-390.9344055680002</v>
       </c>
       <c r="P96">
-        <v>-1101.351625632</v>
+        <v>-1005.259900032</v>
       </c>
       <c r="Q96">
-        <v>-897.9516256320004</v>
+        <v>-801.8599000320004</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.4408826512379147</v>
+        <v>0.4389609984216616</v>
       </c>
       <c r="T96">
-        <v>9.118444531643812</v>
+        <v>9.079930679484102</v>
       </c>
       <c r="U96">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.05693170142169438</v>
+        <v>0.06118456756375323</v>
       </c>
       <c r="W96">
-        <v>0.2035141388331984</v>
+        <v>0.1885141388331984</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9334,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2033275050774799</v>
+        <v>0.21851631272769</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9345,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2194562495774813</v>
+        <v>0.2050909504085061</v>
       </c>
       <c r="C97">
-        <v>-7098.969551784079</v>
+        <v>-6950.652468592439</v>
       </c>
       <c r="D97">
-        <v>1758.465448215922</v>
+        <v>1906.782531407563</v>
       </c>
       <c r="E97">
         <v>8153.435000000001</v>
@@ -9247,37 +9378,37 @@
         <v>390.4</v>
       </c>
       <c r="M97">
-        <v>1940.481153000001</v>
+        <v>1805.600628</v>
       </c>
       <c r="N97">
-        <v>-1550.081153000001</v>
+        <v>-1415.200628000001</v>
       </c>
       <c r="O97">
-        <v>-434.0227228400002</v>
+        <v>-396.2561758400002</v>
       </c>
       <c r="P97">
-        <v>-1116.05843016</v>
+        <v>-1018.94445216</v>
       </c>
       <c r="Q97">
-        <v>-912.6584301600004</v>
+        <v>-815.5444521600003</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.5198991814854979</v>
+        <v>0.5175931981059942</v>
       </c>
       <c r="T97">
-        <v>10.94213343797258</v>
+        <v>10.89591681538093</v>
       </c>
       <c r="U97">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.05633242035409759</v>
+        <v>0.06054051948413477</v>
       </c>
       <c r="W97">
-        <v>0.2036434636875858</v>
+        <v>0.1886434636875857</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9416,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2011872155503486</v>
+        <v>0.2162161410147669</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9427,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2501198359920649</v>
+        <v>0.2066409504085061</v>
       </c>
       <c r="C98">
-        <v>-7444.279417857844</v>
+        <v>-7062.52326700581</v>
       </c>
       <c r="D98">
-        <v>1507.808582142156</v>
+        <v>1889.56473299419</v>
       </c>
       <c r="E98">
         <v>8248.088</v>
@@ -9329,45 +9460,45 @@
         <v>390.4</v>
       </c>
       <c r="M98">
-        <v>2233.5079104</v>
+        <v>1824.6069504</v>
       </c>
       <c r="N98">
-        <v>-1843.1079104</v>
+        <v>-1434.2069504</v>
       </c>
       <c r="O98">
-        <v>-516.0702149120001</v>
+        <v>-401.5779461120001</v>
       </c>
       <c r="P98">
-        <v>-1327.037695488</v>
+        <v>-1032.629004288</v>
       </c>
       <c r="Q98">
-        <v>-1123.637695488</v>
+        <v>-829.2290042880001</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.6425136372214606</v>
+        <v>0.6355414976324915</v>
       </c>
       <c r="T98">
-        <v>13.77205550593196</v>
+        <v>13.61989601922613</v>
       </c>
       <c r="U98">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.04894184591467297</v>
+        <v>0.05990988907284171</v>
       </c>
       <c r="W98">
-        <v>0.2337700942741734</v>
+        <v>0.1887700942741734</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.1747923068381178</v>
+        <v>0.2139638895458633</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9509,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2521198359920649</v>
+        <v>0.2081909504085061</v>
       </c>
       <c r="C99">
-        <v>-7552.82170478514</v>
+        <v>-7174.085902704648</v>
       </c>
       <c r="D99">
-        <v>1493.91929521486</v>
+        <v>1872.655097295353</v>
       </c>
       <c r="E99">
         <v>8342.741</v>
@@ -9411,45 +9542,45 @@
         <v>390.4</v>
       </c>
       <c r="M99">
-        <v>2256.7736178</v>
+        <v>1843.6132728</v>
       </c>
       <c r="N99">
-        <v>-1866.3736178</v>
+        <v>-1453.2132728</v>
       </c>
       <c r="O99">
-        <v>-522.5846129840002</v>
+        <v>-406.8997163840001</v>
       </c>
       <c r="P99">
-        <v>-1343.789004816</v>
+        <v>-1046.313556416</v>
       </c>
       <c r="Q99">
-        <v>-1140.389004816</v>
+        <v>-842.913556416</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.8414181829619477</v>
+        <v>0.832121996843322</v>
       </c>
       <c r="T99">
-        <v>18.36274067457595</v>
+        <v>18.15986135896818</v>
       </c>
       <c r="U99">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.04843729080215056</v>
+        <v>0.05929226135044128</v>
       </c>
       <c r="W99">
-        <v>0.2338941139208314</v>
+        <v>0.1888941139208314</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.1729903242933949</v>
+        <v>0.2117580762515761</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9591,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2541198359920649</v>
+        <v>0.2097409504085062</v>
       </c>
       <c r="C100">
-        <v>-7661.110442968931</v>
+        <v>-7285.348575514749</v>
       </c>
       <c r="D100">
-        <v>1480.28355703107</v>
+        <v>1856.045424485252</v>
       </c>
       <c r="E100">
         <v>8437.394</v>
@@ -9493,45 +9624,45 @@
         <v>390.4</v>
       </c>
       <c r="M100">
-        <v>2280.0393252</v>
+        <v>1862.6195952</v>
       </c>
       <c r="N100">
-        <v>-1889.6393252</v>
+        <v>-1472.2195952</v>
       </c>
       <c r="O100">
-        <v>-529.0990110560001</v>
+        <v>-412.2214866560001</v>
       </c>
       <c r="P100">
-        <v>-1360.540314144</v>
+        <v>-1059.998108544</v>
       </c>
       <c r="Q100">
-        <v>-1157.140314144</v>
+        <v>-856.5981085440002</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.239227274442922</v>
+        <v>1.225282995264983</v>
       </c>
       <c r="T100">
-        <v>27.54411101186392</v>
+        <v>27.23979203845226</v>
       </c>
       <c r="U100">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.04794303273274086</v>
+        <v>0.05868723827543677</v>
       </c>
       <c r="W100">
-        <v>0.2340156025542923</v>
+        <v>0.1890156025542923</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.171225116902646</v>
+        <v>0.2095972795551314</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9673,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2561198359920649</v>
+        <v>0.2112909504085062</v>
       </c>
       <c r="C101">
-        <v>-7769.152512405381</v>
+        <v>-7396.31919690334</v>
       </c>
       <c r="D101">
-        <v>1466.89448759462</v>
+        <v>1839.727803096661</v>
       </c>
       <c r="E101">
         <v>8532.047</v>
@@ -9575,45 +9706,45 @@
         <v>390.4</v>
       </c>
       <c r="M101">
-        <v>2303.3050326</v>
+        <v>1881.6259176</v>
       </c>
       <c r="N101">
-        <v>-1912.9050326</v>
+        <v>-1491.2259176</v>
       </c>
       <c r="O101">
-        <v>-535.6134091280001</v>
+        <v>-417.5432569280001</v>
       </c>
       <c r="P101">
-        <v>-1377.291623472</v>
+        <v>-1073.682660672</v>
       </c>
       <c r="Q101">
-        <v>-1173.891623472</v>
+        <v>-870.2826606720001</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.432654548885842</v>
+        <v>2.404765990529966</v>
       </c>
       <c r="T101">
-        <v>55.08822202372782</v>
+        <v>54.47958407690452</v>
       </c>
       <c r="U101">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V101">
-        <v>0.04745875967483439</v>
+        <v>0.0580944378888162</v>
       </c>
       <c r="W101">
-        <v>0.2341346368719257</v>
+        <v>0.1891346368719257</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y101">
-        <v>0.1694955702672657</v>
+        <v>0.2074801353172008</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/new_zealand/new_zealand_green_renewable_energy.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_green_renewable_energy.xlsx
@@ -1415,7 +1415,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1552,22 +1552,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07082917521137813</v>
+        <v>0.07066325352078627</v>
       </c>
       <c r="C2">
-        <v>9183.916071606847</v>
+        <v>9131.348596226577</v>
       </c>
       <c r="D2">
-        <v>9049.316071606847</v>
+        <v>9091.401596226577</v>
       </c>
       <c r="E2">
-        <v>-838.6</v>
+        <v>-743.947</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>94.65300000000001</v>
       </c>
       <c r="G2">
         <v>134.6</v>
@@ -1588,28 +1588,28 @@
         <v>390.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>4.7610459</v>
       </c>
       <c r="N2">
-        <v>390.4</v>
+        <v>385.6389541</v>
       </c>
       <c r="O2">
-        <v>109.312</v>
+        <v>107.978907148</v>
       </c>
       <c r="P2">
-        <v>281.088</v>
+        <v>277.660046952</v>
       </c>
       <c r="Q2">
-        <v>484.4879999999999</v>
+        <v>481.060046952</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07082917521137813</v>
+        <v>0.07101120557655179</v>
       </c>
       <c r="T2">
-        <v>0.5780409979533054</v>
+        <v>0.582244932483875</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>81.99878938365202</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1634,22 +1634,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07066325352078627</v>
+        <v>0.07049733183019441</v>
       </c>
       <c r="C3">
-        <v>9131.348596226577</v>
+        <v>9079.174402970768</v>
       </c>
       <c r="D3">
-        <v>9091.401596226577</v>
+        <v>9133.880402970768</v>
       </c>
       <c r="E3">
-        <v>-743.947</v>
+        <v>-649.294</v>
       </c>
       <c r="F3">
-        <v>94.65300000000001</v>
+        <v>189.306</v>
       </c>
       <c r="G3">
         <v>134.6</v>
@@ -1670,28 +1670,28 @@
         <v>390.4</v>
       </c>
       <c r="M3">
-        <v>4.7610459</v>
+        <v>9.5220918</v>
       </c>
       <c r="N3">
-        <v>385.6389541</v>
+        <v>380.8779082</v>
       </c>
       <c r="O3">
-        <v>107.978907148</v>
+        <v>106.645814296</v>
       </c>
       <c r="P3">
-        <v>277.660046952</v>
+        <v>274.232093904</v>
       </c>
       <c r="Q3">
-        <v>481.060046952</v>
+        <v>477.6320939039999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07101120557655179</v>
+        <v>0.07119695084713715</v>
       </c>
       <c r="T3">
-        <v>0.582244932483875</v>
+        <v>0.5865346615967009</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>81.99878938365202</v>
+        <v>40.99939469182601</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1716,22 +1716,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07049733183019441</v>
+        <v>0.07033141013960255</v>
       </c>
       <c r="C4">
-        <v>9079.174402970768</v>
+        <v>9027.399030450728</v>
       </c>
       <c r="D4">
-        <v>9133.880402970768</v>
+        <v>9176.758030450728</v>
       </c>
       <c r="E4">
-        <v>-649.294</v>
+        <v>-554.6410000000001</v>
       </c>
       <c r="F4">
-        <v>189.306</v>
+        <v>283.959</v>
       </c>
       <c r="G4">
         <v>134.6</v>
@@ -1752,28 +1752,28 @@
         <v>390.4</v>
       </c>
       <c r="M4">
-        <v>9.5220918</v>
+        <v>14.2831377</v>
       </c>
       <c r="N4">
-        <v>380.8779082</v>
+        <v>376.1168623</v>
       </c>
       <c r="O4">
-        <v>106.645814296</v>
+        <v>105.312721444</v>
       </c>
       <c r="P4">
-        <v>274.232093904</v>
+        <v>270.804140856</v>
       </c>
       <c r="Q4">
-        <v>477.6320939039999</v>
+        <v>474.204140856</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07119695084713715</v>
+        <v>0.07138652591711603</v>
       </c>
       <c r="T4">
-        <v>0.5865346615967009</v>
+        <v>0.5909128387324718</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>40.99939469182601</v>
+        <v>27.33292979455068</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1798,22 +1798,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07033141013960255</v>
+        <v>0.0701654884490107</v>
       </c>
       <c r="C5">
-        <v>9027.399030450728</v>
+        <v>8976.028121768994</v>
       </c>
       <c r="D5">
-        <v>9176.758030450728</v>
+        <v>9220.040121768992</v>
       </c>
       <c r="E5">
-        <v>-554.6410000000001</v>
+        <v>-459.988</v>
       </c>
       <c r="F5">
-        <v>283.959</v>
+        <v>378.612</v>
       </c>
       <c r="G5">
         <v>134.6</v>
@@ -1834,28 +1834,28 @@
         <v>390.4</v>
       </c>
       <c r="M5">
-        <v>14.2831377</v>
+        <v>19.0441836</v>
       </c>
       <c r="N5">
-        <v>376.1168623</v>
+        <v>371.3558164</v>
       </c>
       <c r="O5">
-        <v>105.312721444</v>
+        <v>103.979628592</v>
       </c>
       <c r="P5">
-        <v>270.804140856</v>
+        <v>267.376187808</v>
       </c>
       <c r="Q5">
-        <v>474.204140856</v>
+        <v>470.776187808</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07138652591711603</v>
+        <v>0.07158005046771948</v>
       </c>
       <c r="T5">
-        <v>0.5909128387324718</v>
+        <v>0.5953822278919046</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>27.33292979455068</v>
+        <v>20.49969734591301</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1880,22 +1880,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0701654884490107</v>
+        <v>0.06999956675841883</v>
       </c>
       <c r="C6">
-        <v>8976.028121768994</v>
+        <v>8925.067426995169</v>
       </c>
       <c r="D6">
-        <v>9220.040121768992</v>
+        <v>9263.732426995168</v>
       </c>
       <c r="E6">
-        <v>-459.988</v>
+        <v>-365.3349999999999</v>
       </c>
       <c r="F6">
-        <v>378.612</v>
+        <v>473.2650000000001</v>
       </c>
       <c r="G6">
         <v>134.6</v>
@@ -1916,28 +1916,28 @@
         <v>390.4</v>
       </c>
       <c r="M6">
-        <v>19.0441836</v>
+        <v>23.8052295</v>
       </c>
       <c r="N6">
-        <v>371.3558164</v>
+        <v>366.5947705</v>
       </c>
       <c r="O6">
-        <v>103.979628592</v>
+        <v>102.64653574</v>
       </c>
       <c r="P6">
-        <v>267.376187808</v>
+        <v>263.94823476</v>
       </c>
       <c r="Q6">
-        <v>470.776187808</v>
+        <v>467.34823476</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07158005046771948</v>
+        <v>0.07177764921938824</v>
       </c>
       <c r="T6">
-        <v>0.5953822278919046</v>
+        <v>0.5999457094546938</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>20.49969734591301</v>
+        <v>16.3997578767304</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1962,22 +1962,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06999956675841883</v>
+        <v>0.06983364506782698</v>
       </c>
       <c r="C7">
-        <v>8925.067426995169</v>
+        <v>8874.52280571248</v>
       </c>
       <c r="D7">
-        <v>9263.732426995168</v>
+        <v>9307.84080571248</v>
       </c>
       <c r="E7">
-        <v>-365.3349999999999</v>
+        <v>-270.6819999999999</v>
       </c>
       <c r="F7">
-        <v>473.2650000000001</v>
+        <v>567.9180000000001</v>
       </c>
       <c r="G7">
         <v>134.6</v>
@@ -1998,28 +1998,28 @@
         <v>390.4</v>
       </c>
       <c r="M7">
-        <v>23.8052295</v>
+        <v>28.56627540000001</v>
       </c>
       <c r="N7">
-        <v>366.5947705</v>
+        <v>361.8337246</v>
       </c>
       <c r="O7">
-        <v>102.64653574</v>
+        <v>101.313442888</v>
       </c>
       <c r="P7">
-        <v>263.94823476</v>
+        <v>260.520281712</v>
       </c>
       <c r="Q7">
-        <v>467.34823476</v>
+        <v>463.920281712</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07177764921938824</v>
+        <v>0.07197945219981594</v>
       </c>
       <c r="T7">
-        <v>0.5999457094546938</v>
+        <v>0.6046062863698829</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>16.3997578767304</v>
+        <v>13.66646489727533</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2044,22 +2044,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06983364506782698</v>
+        <v>0.06966772337723512</v>
       </c>
       <c r="C8">
-        <v>8874.52280571248</v>
+        <v>8824.400229637467</v>
       </c>
       <c r="D8">
-        <v>9307.84080571248</v>
+        <v>9352.371229637467</v>
       </c>
       <c r="E8">
-        <v>-270.682</v>
+        <v>-176.029</v>
       </c>
       <c r="F8">
-        <v>567.918</v>
+        <v>662.571</v>
       </c>
       <c r="G8">
         <v>134.6</v>
@@ -2080,28 +2080,28 @@
         <v>390.4</v>
       </c>
       <c r="M8">
-        <v>28.5662754</v>
+        <v>33.3273213</v>
       </c>
       <c r="N8">
-        <v>361.8337246</v>
+        <v>357.0726787</v>
       </c>
       <c r="O8">
-        <v>101.313442888</v>
+        <v>99.980350036</v>
       </c>
       <c r="P8">
-        <v>260.520281712</v>
+        <v>257.092328664</v>
       </c>
       <c r="Q8">
-        <v>463.920281712</v>
+        <v>460.492328664</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07197945219981594</v>
+        <v>0.07218559502928507</v>
       </c>
       <c r="T8">
-        <v>0.6046062863698829</v>
+        <v>0.6093670907456136</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>13.66646489727534</v>
+        <v>11.71411276909314</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2126,22 +2126,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06966772337723511</v>
+        <v>0.06950180168664326</v>
       </c>
       <c r="C9">
-        <v>8824.400229637471</v>
+        <v>8774.705785315191</v>
       </c>
       <c r="D9">
-        <v>9352.371229637471</v>
+        <v>9397.329785315191</v>
       </c>
       <c r="E9">
-        <v>-176.0289999999999</v>
+        <v>-81.37599999999998</v>
       </c>
       <c r="F9">
-        <v>662.5710000000001</v>
+        <v>757.224</v>
       </c>
       <c r="G9">
         <v>134.6</v>
@@ -2162,28 +2162,28 @@
         <v>390.4</v>
       </c>
       <c r="M9">
-        <v>33.32732130000001</v>
+        <v>38.0883672</v>
       </c>
       <c r="N9">
-        <v>357.0726787</v>
+        <v>352.3116328</v>
       </c>
       <c r="O9">
-        <v>99.980350036</v>
+        <v>98.64725718400001</v>
       </c>
       <c r="P9">
-        <v>257.092328664</v>
+        <v>253.664375616</v>
       </c>
       <c r="Q9">
-        <v>460.492328664</v>
+        <v>457.064375616</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07218559502928507</v>
+        <v>0.07239621922461223</v>
       </c>
       <c r="T9">
-        <v>0.6093670907456136</v>
+        <v>0.6142313908686428</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.71411276909314</v>
+        <v>10.2498486729565</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2208,22 +2208,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06950180168664326</v>
+        <v>0.06933587999605141</v>
       </c>
       <c r="C10">
-        <v>8774.705785315191</v>
+        <v>8725.44567689257</v>
       </c>
       <c r="D10">
-        <v>9397.329785315191</v>
+        <v>9442.72267689257</v>
       </c>
       <c r="E10">
-        <v>-81.37599999999998</v>
+        <v>13.27700000000004</v>
       </c>
       <c r="F10">
-        <v>757.224</v>
+        <v>851.8770000000001</v>
       </c>
       <c r="G10">
         <v>134.6</v>
@@ -2244,28 +2244,28 @@
         <v>390.4</v>
       </c>
       <c r="M10">
-        <v>38.0883672</v>
+        <v>42.8494131</v>
       </c>
       <c r="N10">
-        <v>352.3116328</v>
+        <v>347.5505869</v>
       </c>
       <c r="O10">
-        <v>98.64725718400001</v>
+        <v>97.314164332</v>
       </c>
       <c r="P10">
-        <v>253.664375616</v>
+        <v>250.236422568</v>
       </c>
       <c r="Q10">
-        <v>457.064375616</v>
+        <v>453.6364225679999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07239621922461223</v>
+        <v>0.07261147252313341</v>
       </c>
       <c r="T10">
-        <v>0.6142313908686428</v>
+        <v>0.6192025986866837</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>10.2498486729565</v>
+        <v>9.110976598183559</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2290,22 +2290,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06933587999605141</v>
+        <v>0.06927795830545955</v>
       </c>
       <c r="C11">
-        <v>8725.44567689257</v>
+        <v>8646.74234415202</v>
       </c>
       <c r="D11">
-        <v>9442.72267689257</v>
+        <v>9458.672344152021</v>
       </c>
       <c r="E11">
-        <v>13.27700000000004</v>
+        <v>107.9300000000001</v>
       </c>
       <c r="F11">
-        <v>851.8770000000001</v>
+        <v>946.5300000000001</v>
       </c>
       <c r="G11">
         <v>134.6</v>
@@ -2326,45 +2326,45 @@
         <v>390.4</v>
       </c>
       <c r="M11">
-        <v>42.8494131</v>
+        <v>49.03025400000001</v>
       </c>
       <c r="N11">
-        <v>347.5505869</v>
+        <v>341.369746</v>
       </c>
       <c r="O11">
-        <v>97.314164332</v>
+        <v>95.58352888</v>
       </c>
       <c r="P11">
-        <v>250.236422568</v>
+        <v>245.7862171199999</v>
       </c>
       <c r="Q11">
-        <v>453.6364225679999</v>
+        <v>449.1862171199999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07261147252313341</v>
+        <v>0.07283150922828838</v>
       </c>
       <c r="T11">
-        <v>0.6192025986866837</v>
+        <v>0.62428427778957</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.28</v>
       </c>
       <c r="W11">
-        <v>0.036216</v>
+        <v>0.037296</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>9.110976598183559</v>
+        <v>7.962430706559259</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2372,22 +2372,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06927795830545955</v>
+        <v>0.06912283661486769</v>
       </c>
       <c r="C12">
-        <v>8646.74234415202</v>
+        <v>8595.071175103172</v>
       </c>
       <c r="D12">
-        <v>9458.672344152021</v>
+        <v>9501.654175103173</v>
       </c>
       <c r="E12">
-        <v>107.9300000000002</v>
+        <v>202.5830000000002</v>
       </c>
       <c r="F12">
-        <v>946.5300000000002</v>
+        <v>1041.183</v>
       </c>
       <c r="G12">
         <v>134.6</v>
@@ -2408,28 +2408,28 @@
         <v>390.4</v>
       </c>
       <c r="M12">
-        <v>49.03025400000001</v>
+        <v>53.93327940000001</v>
       </c>
       <c r="N12">
-        <v>341.369746</v>
+        <v>336.4667206</v>
       </c>
       <c r="O12">
-        <v>95.58352888</v>
+        <v>94.210681768</v>
       </c>
       <c r="P12">
-        <v>245.7862171199999</v>
+        <v>242.256038832</v>
       </c>
       <c r="Q12">
-        <v>449.1862171199999</v>
+        <v>445.656038832</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07283150922828838</v>
+        <v>0.07305649057850301</v>
       </c>
       <c r="T12">
-        <v>0.62428427778957</v>
+        <v>0.629480151928476</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>7.962430706559259</v>
+        <v>7.238573369599326</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2454,22 +2454,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06912283661486769</v>
+        <v>0.06911459492427582</v>
       </c>
       <c r="C13">
-        <v>8595.071175103172</v>
+        <v>8502.712751876436</v>
       </c>
       <c r="D13">
-        <v>9501.654175103173</v>
+        <v>9503.948751876434</v>
       </c>
       <c r="E13">
-        <v>202.5830000000002</v>
+        <v>297.236</v>
       </c>
       <c r="F13">
-        <v>1041.183</v>
+        <v>1135.836</v>
       </c>
       <c r="G13">
         <v>134.6</v>
@@ -2490,45 +2490,45 @@
         <v>390.4</v>
       </c>
       <c r="M13">
-        <v>53.93327940000001</v>
+        <v>60.767226</v>
       </c>
       <c r="N13">
-        <v>336.4667206</v>
+        <v>329.632774</v>
       </c>
       <c r="O13">
-        <v>94.210681768</v>
+        <v>92.29717672000001</v>
       </c>
       <c r="P13">
-        <v>242.256038832</v>
+        <v>237.33559728</v>
       </c>
       <c r="Q13">
-        <v>445.656038832</v>
+        <v>440.73559728</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07305649057850301</v>
+        <v>0.07328658514122252</v>
       </c>
       <c r="T13">
-        <v>0.629480151928476</v>
+        <v>0.6347941141159936</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.28</v>
       </c>
       <c r="W13">
-        <v>0.037296</v>
+        <v>0.03852</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>7.238573369599326</v>
+        <v>6.424515741429434</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2536,22 +2536,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06911459492427582</v>
+        <v>0.06897171323368397</v>
       </c>
       <c r="C14">
-        <v>8502.712751876436</v>
+        <v>8448.016466913685</v>
       </c>
       <c r="D14">
-        <v>9503.948751876434</v>
+        <v>9543.905466913684</v>
       </c>
       <c r="E14">
-        <v>297.236</v>
+        <v>391.8890000000002</v>
       </c>
       <c r="F14">
-        <v>1135.836</v>
+        <v>1230.489</v>
       </c>
       <c r="G14">
         <v>134.6</v>
@@ -2572,28 +2572,28 @@
         <v>390.4</v>
       </c>
       <c r="M14">
-        <v>60.767226</v>
+        <v>65.83116150000001</v>
       </c>
       <c r="N14">
-        <v>329.632774</v>
+        <v>324.5688385</v>
       </c>
       <c r="O14">
-        <v>92.29717672000001</v>
+        <v>90.87927478</v>
       </c>
       <c r="P14">
-        <v>237.33559728</v>
+        <v>233.68956372</v>
       </c>
       <c r="Q14">
-        <v>440.73559728</v>
+        <v>437.08956372</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07328658514122252</v>
+        <v>0.07352196923411949</v>
       </c>
       <c r="T14">
-        <v>0.6347941141159936</v>
+        <v>0.6402302363537989</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>6.424515741429434</v>
+        <v>5.930322222857939</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2618,22 +2618,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06897171323368397</v>
+        <v>0.0689094715430921</v>
       </c>
       <c r="C15">
-        <v>8448.016466913685</v>
+        <v>8370.874538729113</v>
       </c>
       <c r="D15">
-        <v>9543.905466913684</v>
+        <v>9561.416538729112</v>
       </c>
       <c r="E15">
-        <v>391.8890000000002</v>
+        <v>486.5420000000003</v>
       </c>
       <c r="F15">
-        <v>1230.489</v>
+        <v>1325.142</v>
       </c>
       <c r="G15">
         <v>134.6</v>
@@ -2654,45 +2654,45 @@
         <v>390.4</v>
       </c>
       <c r="M15">
-        <v>65.83116150000001</v>
+        <v>71.95521060000002</v>
       </c>
       <c r="N15">
-        <v>324.5688385</v>
+        <v>318.4447894</v>
       </c>
       <c r="O15">
-        <v>90.87927478</v>
+        <v>89.164541032</v>
       </c>
       <c r="P15">
-        <v>233.68956372</v>
+        <v>229.280248368</v>
       </c>
       <c r="Q15">
-        <v>437.08956372</v>
+        <v>432.680248368</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07352196923411949</v>
+        <v>0.0737628273756885</v>
       </c>
       <c r="T15">
-        <v>0.6402302363537989</v>
+        <v>0.6457927800389952</v>
       </c>
       <c r="U15">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.28</v>
       </c>
       <c r="W15">
-        <v>0.03852</v>
+        <v>0.039096</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y15">
-        <v>5.930322222857939</v>
+        <v>5.425597350694154</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2700,22 +2700,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0689094715430921</v>
+        <v>0.06877234985250025</v>
       </c>
       <c r="C16">
-        <v>8370.874538729113</v>
+        <v>8315.026982483922</v>
       </c>
       <c r="D16">
-        <v>9561.416538729112</v>
+        <v>9600.221982483921</v>
       </c>
       <c r="E16">
-        <v>486.5420000000003</v>
+        <v>581.1950000000003</v>
       </c>
       <c r="F16">
-        <v>1325.142</v>
+        <v>1419.795</v>
       </c>
       <c r="G16">
         <v>134.6</v>
@@ -2736,28 +2736,28 @@
         <v>390.4</v>
       </c>
       <c r="M16">
-        <v>71.95521060000002</v>
+        <v>77.09486850000002</v>
       </c>
       <c r="N16">
-        <v>318.4447894</v>
+        <v>313.3051315</v>
       </c>
       <c r="O16">
-        <v>89.164541032</v>
+        <v>87.72543682</v>
       </c>
       <c r="P16">
-        <v>229.280248368</v>
+        <v>225.57969468</v>
       </c>
       <c r="Q16">
-        <v>432.680248368</v>
+        <v>428.97969468</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0737628273756885</v>
+        <v>0.07400935276764735</v>
       </c>
       <c r="T16">
-        <v>0.6457927800389952</v>
+        <v>0.6514862071050195</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.425597350694154</v>
+        <v>5.063890860647877</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2782,22 +2782,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06877234985250025</v>
+        <v>0.06863522816190838</v>
       </c>
       <c r="C17">
-        <v>8315.026982483922</v>
+        <v>8259.495697154347</v>
       </c>
       <c r="D17">
-        <v>9600.221982483921</v>
+        <v>9639.343697154347</v>
       </c>
       <c r="E17">
-        <v>581.1950000000001</v>
+        <v>675.8480000000001</v>
       </c>
       <c r="F17">
-        <v>1419.795</v>
+        <v>1514.448</v>
       </c>
       <c r="G17">
         <v>134.6</v>
@@ -2818,28 +2818,28 @@
         <v>390.4</v>
       </c>
       <c r="M17">
-        <v>77.0948685</v>
+        <v>82.23452640000001</v>
       </c>
       <c r="N17">
-        <v>313.3051315</v>
+        <v>308.1654736</v>
       </c>
       <c r="O17">
-        <v>87.72543682</v>
+        <v>86.28633260800001</v>
       </c>
       <c r="P17">
-        <v>225.57969468</v>
+        <v>221.879140992</v>
       </c>
       <c r="Q17">
-        <v>428.97969468</v>
+        <v>425.279140992</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07400935276764735</v>
+        <v>0.0742617478117957</v>
       </c>
       <c r="T17">
-        <v>0.6514862071050195</v>
+        <v>0.6573151919583302</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.063890860647877</v>
+        <v>4.747397681857386</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2864,22 +2864,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06863522816190838</v>
+        <v>0.06849810647131653</v>
       </c>
       <c r="C18">
-        <v>8259.495697154347</v>
+        <v>8204.284565053136</v>
       </c>
       <c r="D18">
-        <v>9639.343697154347</v>
+        <v>9678.785565053136</v>
       </c>
       <c r="E18">
-        <v>675.8480000000001</v>
+        <v>770.5010000000003</v>
       </c>
       <c r="F18">
-        <v>1514.448</v>
+        <v>1609.101</v>
       </c>
       <c r="G18">
         <v>134.6</v>
@@ -2900,28 +2900,28 @@
         <v>390.4</v>
       </c>
       <c r="M18">
-        <v>82.23452640000001</v>
+        <v>87.37418430000002</v>
       </c>
       <c r="N18">
-        <v>308.1654736</v>
+        <v>303.0258157</v>
       </c>
       <c r="O18">
-        <v>86.28633260800001</v>
+        <v>84.84722839599999</v>
       </c>
       <c r="P18">
-        <v>221.879140992</v>
+        <v>218.178587304</v>
       </c>
       <c r="Q18">
-        <v>425.279140992</v>
+        <v>421.5785873039999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0742617478117957</v>
+        <v>0.07452022466423679</v>
       </c>
       <c r="T18">
-        <v>0.6573151919583302</v>
+        <v>0.6632846342779857</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.747397681857386</v>
+        <v>4.468138994689303</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2946,22 +2946,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06849810647131653</v>
+        <v>0.06849058478072467</v>
       </c>
       <c r="C19">
-        <v>8204.284565053136</v>
+        <v>8111.80445469892</v>
       </c>
       <c r="D19">
-        <v>9678.785565053136</v>
+        <v>9680.958454698921</v>
       </c>
       <c r="E19">
-        <v>770.5010000000003</v>
+        <v>865.1540000000003</v>
       </c>
       <c r="F19">
-        <v>1609.101</v>
+        <v>1703.754</v>
       </c>
       <c r="G19">
         <v>134.6</v>
@@ -2982,45 +2982,45 @@
         <v>390.4</v>
       </c>
       <c r="M19">
-        <v>87.37418430000002</v>
+        <v>94.21759620000002</v>
       </c>
       <c r="N19">
-        <v>303.0258157</v>
+        <v>296.1824038</v>
       </c>
       <c r="O19">
-        <v>84.84722839599999</v>
+        <v>82.931073064</v>
       </c>
       <c r="P19">
-        <v>218.178587304</v>
+        <v>213.251330736</v>
       </c>
       <c r="Q19">
-        <v>421.5785873039999</v>
+        <v>416.651330736</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07452022466423679</v>
+        <v>0.07478500583015203</v>
       </c>
       <c r="T19">
-        <v>0.6632846342779857</v>
+        <v>0.669399672751779</v>
       </c>
       <c r="U19">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V19">
         <v>0.28</v>
       </c>
       <c r="W19">
-        <v>0.039096</v>
+        <v>0.039816</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.468138994689303</v>
+        <v>4.143599664454186</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3028,22 +3028,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06849058478072467</v>
+        <v>0.06836066309013282</v>
       </c>
       <c r="C20">
-        <v>8111.804454698921</v>
+        <v>8054.83820835495</v>
       </c>
       <c r="D20">
-        <v>9680.958454698921</v>
+        <v>9718.64520835495</v>
       </c>
       <c r="E20">
-        <v>865.1540000000001</v>
+        <v>959.8070000000001</v>
       </c>
       <c r="F20">
-        <v>1703.754</v>
+        <v>1798.407</v>
       </c>
       <c r="G20">
         <v>134.6</v>
@@ -3064,28 +3064,28 @@
         <v>390.4</v>
       </c>
       <c r="M20">
-        <v>94.21759620000002</v>
+        <v>99.45190710000001</v>
       </c>
       <c r="N20">
-        <v>296.1824038</v>
+        <v>290.9480928999999</v>
       </c>
       <c r="O20">
-        <v>82.931073064</v>
+        <v>81.46546601199999</v>
       </c>
       <c r="P20">
-        <v>213.251330736</v>
+        <v>209.482626888</v>
       </c>
       <c r="Q20">
-        <v>416.651330736</v>
+        <v>412.882626888</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07478500583015203</v>
+        <v>0.07505632480263311</v>
       </c>
       <c r="T20">
-        <v>0.669399672751779</v>
+        <v>0.6756656998298637</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -3102,7 +3102,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>4.143599664454186</v>
+        <v>3.925515471588175</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3110,22 +3110,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06836066309013282</v>
+        <v>0.06823074139954097</v>
       </c>
       <c r="C21">
-        <v>8054.83820835495</v>
+        <v>7998.166528304485</v>
       </c>
       <c r="D21">
-        <v>9718.64520835495</v>
+        <v>9756.626528304485</v>
       </c>
       <c r="E21">
-        <v>959.8070000000001</v>
+        <v>1054.46</v>
       </c>
       <c r="F21">
-        <v>1798.407</v>
+        <v>1893.06</v>
       </c>
       <c r="G21">
         <v>134.6</v>
@@ -3146,28 +3146,28 @@
         <v>390.4</v>
       </c>
       <c r="M21">
-        <v>99.45190710000001</v>
+        <v>104.686218</v>
       </c>
       <c r="N21">
-        <v>290.9480928999999</v>
+        <v>285.7137819999999</v>
       </c>
       <c r="O21">
-        <v>81.46546601199999</v>
+        <v>79.99985895999998</v>
       </c>
       <c r="P21">
-        <v>209.482626888</v>
+        <v>205.7139230399999</v>
       </c>
       <c r="Q21">
-        <v>412.882626888</v>
+        <v>409.1139230399999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07505632480263311</v>
+        <v>0.0753344267494262</v>
       </c>
       <c r="T21">
-        <v>0.6756656998298637</v>
+        <v>0.6820883775849004</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.925515471588175</v>
+        <v>3.729239698008766</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3192,22 +3192,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06823074139954097</v>
+        <v>0.0681008197089491</v>
       </c>
       <c r="C22">
-        <v>7998.166528304485</v>
+        <v>7941.792881670274</v>
       </c>
       <c r="D22">
-        <v>9756.626528304485</v>
+        <v>9794.905881670275</v>
       </c>
       <c r="E22">
-        <v>1054.46</v>
+        <v>1149.113</v>
       </c>
       <c r="F22">
-        <v>1893.06</v>
+        <v>1987.713</v>
       </c>
       <c r="G22">
         <v>134.6</v>
@@ -3228,28 +3228,28 @@
         <v>390.4</v>
       </c>
       <c r="M22">
-        <v>104.686218</v>
+        <v>109.9205289</v>
       </c>
       <c r="N22">
-        <v>285.7137819999999</v>
+        <v>280.4794711</v>
       </c>
       <c r="O22">
-        <v>79.99985895999998</v>
+        <v>78.534251908</v>
       </c>
       <c r="P22">
-        <v>205.7139230399999</v>
+        <v>201.945219192</v>
       </c>
       <c r="Q22">
-        <v>409.1139230399999</v>
+        <v>405.3452191919999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0753344267494262</v>
+        <v>0.0756195692518343</v>
       </c>
       <c r="T22">
-        <v>0.6820883775849004</v>
+        <v>0.6886736547767736</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.729239698008766</v>
+        <v>3.551656855246444</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3274,22 +3274,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0681008197089491</v>
+        <v>0.06797089801835723</v>
       </c>
       <c r="C23">
-        <v>7941.792881670275</v>
+        <v>7885.720790201305</v>
       </c>
       <c r="D23">
-        <v>9794.905881670275</v>
+        <v>9833.486790201305</v>
       </c>
       <c r="E23">
-        <v>1149.113</v>
+        <v>1243.766000000001</v>
       </c>
       <c r="F23">
-        <v>1987.713</v>
+        <v>2082.366</v>
       </c>
       <c r="G23">
         <v>134.6</v>
@@ -3310,28 +3310,28 @@
         <v>390.4</v>
       </c>
       <c r="M23">
-        <v>109.9205289</v>
+        <v>115.1548398</v>
       </c>
       <c r="N23">
-        <v>280.4794711</v>
+        <v>275.2451601999999</v>
       </c>
       <c r="O23">
-        <v>78.534251908</v>
+        <v>77.06864485599999</v>
       </c>
       <c r="P23">
-        <v>201.945219192</v>
+        <v>198.1765153439999</v>
       </c>
       <c r="Q23">
-        <v>405.3452191919999</v>
+        <v>401.576515344</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0756195692518343</v>
+        <v>0.075912023100458</v>
       </c>
       <c r="T23">
-        <v>0.6886736547767736</v>
+        <v>0.6954277852299767</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3348,7 +3348,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.551656855246445</v>
+        <v>3.390217907280697</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3356,22 +3356,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06797089801835723</v>
+        <v>0.06784097632776537</v>
       </c>
       <c r="C24">
-        <v>7885.720790201305</v>
+        <v>7829.953831352901</v>
       </c>
       <c r="D24">
-        <v>9833.486790201305</v>
+        <v>9872.372831352901</v>
       </c>
       <c r="E24">
-        <v>1243.766000000001</v>
+        <v>1338.419</v>
       </c>
       <c r="F24">
-        <v>2082.366</v>
+        <v>2177.019</v>
       </c>
       <c r="G24">
         <v>134.6</v>
@@ -3392,28 +3392,28 @@
         <v>390.4</v>
       </c>
       <c r="M24">
-        <v>115.1548398</v>
+        <v>120.3891507</v>
       </c>
       <c r="N24">
-        <v>275.2451601999999</v>
+        <v>270.0108493</v>
       </c>
       <c r="O24">
-        <v>77.06864485599999</v>
+        <v>75.603037804</v>
       </c>
       <c r="P24">
-        <v>198.1765153439999</v>
+        <v>194.407811496</v>
       </c>
       <c r="Q24">
-        <v>401.576515344</v>
+        <v>397.807811496</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.075912023100458</v>
+        <v>0.07621207315294204</v>
       </c>
       <c r="T24">
-        <v>0.6954277852299767</v>
+        <v>0.7023573476430033</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.390217907280697</v>
+        <v>3.242817128703276</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3438,22 +3438,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06784097632776537</v>
+        <v>0.06771105463717352</v>
       </c>
       <c r="C25">
-        <v>7829.953831352901</v>
+        <v>7774.495639392535</v>
       </c>
       <c r="D25">
-        <v>9872.372831352901</v>
+        <v>9911.567639392535</v>
       </c>
       <c r="E25">
-        <v>1338.419</v>
+        <v>1433.072000000001</v>
       </c>
       <c r="F25">
-        <v>2177.019</v>
+        <v>2271.672</v>
       </c>
       <c r="G25">
         <v>134.6</v>
@@ -3474,28 +3474,28 @@
         <v>390.4</v>
       </c>
       <c r="M25">
-        <v>120.3891507</v>
+        <v>125.6234616</v>
       </c>
       <c r="N25">
-        <v>270.0108493</v>
+        <v>264.7765383999999</v>
       </c>
       <c r="O25">
-        <v>75.603037804</v>
+        <v>74.13743075199999</v>
       </c>
       <c r="P25">
-        <v>194.407811496</v>
+        <v>190.6391076479999</v>
       </c>
       <c r="Q25">
-        <v>397.807811496</v>
+        <v>394.0391076479999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07621207315294204</v>
+        <v>0.07652001925943884</v>
       </c>
       <c r="T25">
-        <v>0.7023573476430033</v>
+        <v>0.709469266961636</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.242817128703276</v>
+        <v>3.107699748340639</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3520,22 +3520,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06771105463717352</v>
+        <v>0.06803113294658165</v>
       </c>
       <c r="C26">
-        <v>7774.495639392535</v>
+        <v>7583.836999724557</v>
       </c>
       <c r="D26">
-        <v>9911.567639392535</v>
+        <v>9815.561999724558</v>
       </c>
       <c r="E26">
-        <v>1433.072</v>
+        <v>1527.725</v>
       </c>
       <c r="F26">
-        <v>2271.672</v>
+        <v>2366.325</v>
       </c>
       <c r="G26">
         <v>134.6</v>
@@ -3556,45 +3556,45 @@
         <v>390.4</v>
       </c>
       <c r="M26">
-        <v>125.6234616</v>
+        <v>136.773585</v>
       </c>
       <c r="N26">
-        <v>264.7765384</v>
+        <v>253.626415</v>
       </c>
       <c r="O26">
-        <v>74.137430752</v>
+        <v>71.0153962</v>
       </c>
       <c r="P26">
-        <v>190.639107648</v>
+        <v>182.6110188</v>
       </c>
       <c r="Q26">
-        <v>394.039107648</v>
+        <v>386.0110188</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07652001925943884</v>
+        <v>0.07683617726210888</v>
       </c>
       <c r="T26">
-        <v>0.709469266961636</v>
+        <v>0.7167708374620987</v>
       </c>
       <c r="U26">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V26">
         <v>0.28</v>
       </c>
       <c r="W26">
-        <v>0.039816</v>
+        <v>0.041616</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.107699748340639</v>
+        <v>2.854352322489755</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3602,22 +3602,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06803113294658165</v>
+        <v>0.06791921125598981</v>
       </c>
       <c r="C27">
-        <v>7583.836999724557</v>
+        <v>7522.5420782649</v>
       </c>
       <c r="D27">
-        <v>9815.561999724558</v>
+        <v>9848.9200782649</v>
       </c>
       <c r="E27">
-        <v>1527.725</v>
+        <v>1622.378000000001</v>
       </c>
       <c r="F27">
-        <v>2366.325</v>
+        <v>2460.978000000001</v>
       </c>
       <c r="G27">
         <v>134.6</v>
@@ -3638,28 +3638,28 @@
         <v>390.4</v>
       </c>
       <c r="M27">
-        <v>136.773585</v>
+        <v>142.2445284</v>
       </c>
       <c r="N27">
-        <v>253.626415</v>
+        <v>248.1554715999999</v>
       </c>
       <c r="O27">
-        <v>71.0153962</v>
+        <v>69.48353204799999</v>
       </c>
       <c r="P27">
-        <v>182.6110188</v>
+        <v>178.671939552</v>
       </c>
       <c r="Q27">
-        <v>386.0110188</v>
+        <v>382.071939552</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07683617726210888</v>
+        <v>0.07716088007566189</v>
       </c>
       <c r="T27">
-        <v>0.7167708374620987</v>
+        <v>0.7242697477058173</v>
       </c>
       <c r="U27">
         <v>0.0578</v>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.854352322489755</v>
+        <v>2.744569540855533</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3684,22 +3684,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06791921125598981</v>
+        <v>0.06780728956539794</v>
       </c>
       <c r="C28">
-        <v>7522.5420782649</v>
+        <v>7461.474664105827</v>
       </c>
       <c r="D28">
-        <v>9848.9200782649</v>
+        <v>9882.505664105827</v>
       </c>
       <c r="E28">
-        <v>1622.378000000001</v>
+        <v>1717.031</v>
       </c>
       <c r="F28">
-        <v>2460.978000000001</v>
+        <v>2555.631</v>
       </c>
       <c r="G28">
         <v>134.6</v>
@@ -3720,28 +3720,28 @@
         <v>390.4</v>
       </c>
       <c r="M28">
-        <v>142.2445284</v>
+        <v>147.7154718</v>
       </c>
       <c r="N28">
-        <v>248.1554715999999</v>
+        <v>242.6845282</v>
       </c>
       <c r="O28">
-        <v>69.48353204799999</v>
+        <v>67.95166789599999</v>
       </c>
       <c r="P28">
-        <v>178.671939552</v>
+        <v>174.732860304</v>
       </c>
       <c r="Q28">
-        <v>382.071939552</v>
+        <v>378.132860304</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07716088007566189</v>
+        <v>0.07749447885670951</v>
       </c>
       <c r="T28">
-        <v>0.7242697477058173</v>
+        <v>0.7319741075452542</v>
       </c>
       <c r="U28">
         <v>0.0578</v>
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.744569540855533</v>
+        <v>2.642918817120144</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3766,22 +3766,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06780728956539794</v>
+        <v>0.06769536787480608</v>
       </c>
       <c r="C29">
-        <v>7461.474664105827</v>
+        <v>7400.637092664217</v>
       </c>
       <c r="D29">
-        <v>9882.505664105827</v>
+        <v>9916.321092664217</v>
       </c>
       <c r="E29">
-        <v>1717.031</v>
+        <v>1811.684000000001</v>
       </c>
       <c r="F29">
-        <v>2555.631</v>
+        <v>2650.284000000001</v>
       </c>
       <c r="G29">
         <v>134.6</v>
@@ -3802,28 +3802,28 @@
         <v>390.4</v>
       </c>
       <c r="M29">
-        <v>147.7154718</v>
+        <v>153.1864152000001</v>
       </c>
       <c r="N29">
-        <v>242.6845282</v>
+        <v>237.2135847999999</v>
       </c>
       <c r="O29">
-        <v>67.95166789599999</v>
+        <v>66.41980374399998</v>
       </c>
       <c r="P29">
-        <v>174.732860304</v>
+        <v>170.7937810559999</v>
       </c>
       <c r="Q29">
-        <v>378.132860304</v>
+        <v>374.1937810559999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07749447885670951</v>
+        <v>0.077837344270564</v>
       </c>
       <c r="T29">
-        <v>0.7319741075452542</v>
+        <v>0.739892477380231</v>
       </c>
       <c r="U29">
         <v>0.0578</v>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.642918817120144</v>
+        <v>2.548528859365852</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3848,22 +3848,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06769536787480608</v>
+        <v>0.06831424618421422</v>
       </c>
       <c r="C30">
-        <v>7400.637092664217</v>
+        <v>7121.843732017475</v>
       </c>
       <c r="D30">
-        <v>9916.321092664217</v>
+        <v>9732.180732017476</v>
       </c>
       <c r="E30">
-        <v>1811.684000000001</v>
+        <v>1906.337000000001</v>
       </c>
       <c r="F30">
-        <v>2650.284000000001</v>
+        <v>2744.937000000001</v>
       </c>
       <c r="G30">
         <v>134.6</v>
@@ -3884,45 +3884,45 @@
         <v>390.4</v>
       </c>
       <c r="M30">
-        <v>153.1864152000001</v>
+        <v>168.2646381</v>
       </c>
       <c r="N30">
-        <v>237.2135847999999</v>
+        <v>222.1353618999999</v>
       </c>
       <c r="O30">
-        <v>66.41980374399998</v>
+        <v>62.19790133199999</v>
       </c>
       <c r="P30">
-        <v>170.7937810559999</v>
+        <v>159.9374605679999</v>
       </c>
       <c r="Q30">
-        <v>374.1937810559999</v>
+        <v>363.337460568</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.077837344270564</v>
+        <v>0.07818986786509045</v>
       </c>
       <c r="T30">
-        <v>0.739892477380231</v>
+        <v>0.7480338998866155</v>
       </c>
       <c r="U30">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V30">
         <v>0.28</v>
       </c>
       <c r="W30">
-        <v>0.041616</v>
+        <v>0.044136</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.548528859365852</v>
+        <v>2.320154753894187</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3930,22 +3930,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06831424618421422</v>
+        <v>0.06883232449362237</v>
       </c>
       <c r="C31">
-        <v>7121.843732017476</v>
+        <v>6878.220469504364</v>
       </c>
       <c r="D31">
-        <v>9732.180732017476</v>
+        <v>9583.210469504364</v>
       </c>
       <c r="E31">
-        <v>1906.337</v>
+        <v>2000.99</v>
       </c>
       <c r="F31">
-        <v>2744.937</v>
+        <v>2839.59</v>
       </c>
       <c r="G31">
         <v>134.6</v>
@@ -3966,45 +3966,45 @@
         <v>390.4</v>
       </c>
       <c r="M31">
-        <v>168.2646381</v>
+        <v>182.017719</v>
       </c>
       <c r="N31">
-        <v>222.1353619</v>
+        <v>208.3822809999999</v>
       </c>
       <c r="O31">
-        <v>62.19790133199999</v>
+        <v>58.34703867999999</v>
       </c>
       <c r="P31">
-        <v>159.937460568</v>
+        <v>150.03524232</v>
       </c>
       <c r="Q31">
-        <v>363.337460568</v>
+        <v>353.4352423199999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07818986786509045</v>
+        <v>0.07855246356231767</v>
       </c>
       <c r="T31">
-        <v>0.7480338998866155</v>
+        <v>0.7564079344646112</v>
       </c>
       <c r="U31">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V31">
         <v>0.28</v>
       </c>
       <c r="W31">
-        <v>0.044136</v>
+        <v>0.046152</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>2.320154753894187</v>
+        <v>2.144846128963961</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4012,22 +4012,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06883232449362237</v>
+        <v>0.06876576280303051</v>
       </c>
       <c r="C32">
-        <v>6878.220469504364</v>
+        <v>6802.451048403076</v>
       </c>
       <c r="D32">
-        <v>9583.210469504364</v>
+        <v>9602.094048403076</v>
       </c>
       <c r="E32">
-        <v>2000.99</v>
+        <v>2095.643</v>
       </c>
       <c r="F32">
-        <v>2839.59</v>
+        <v>2934.243</v>
       </c>
       <c r="G32">
         <v>134.6</v>
@@ -4048,28 +4048,28 @@
         <v>390.4</v>
       </c>
       <c r="M32">
-        <v>182.017719</v>
+        <v>188.0849763000001</v>
       </c>
       <c r="N32">
-        <v>208.3822809999999</v>
+        <v>202.3150236999999</v>
       </c>
       <c r="O32">
-        <v>58.34703867999999</v>
+        <v>56.64820663599998</v>
       </c>
       <c r="P32">
-        <v>150.03524232</v>
+        <v>145.6668170639999</v>
       </c>
       <c r="Q32">
-        <v>353.4352423199999</v>
+        <v>349.0668170639999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07855246356231767</v>
+        <v>0.07892556927975436</v>
       </c>
       <c r="T32">
-        <v>0.7564079344646112</v>
+        <v>0.7650246946825486</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.144846128963961</v>
+        <v>2.075657544158671</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4094,22 +4094,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06876576280303051</v>
+        <v>0.06869920111243864</v>
       </c>
       <c r="C33">
-        <v>6802.451048403076</v>
+        <v>6726.75619387738</v>
       </c>
       <c r="D33">
-        <v>9602.094048403076</v>
+        <v>9621.05219387738</v>
       </c>
       <c r="E33">
-        <v>2095.643</v>
+        <v>2190.296</v>
       </c>
       <c r="F33">
-        <v>2934.243</v>
+        <v>3028.896</v>
       </c>
       <c r="G33">
         <v>134.6</v>
@@ -4130,28 +4130,28 @@
         <v>390.4</v>
       </c>
       <c r="M33">
-        <v>188.0849763000001</v>
+        <v>194.1522336</v>
       </c>
       <c r="N33">
-        <v>202.3150236999999</v>
+        <v>196.2477664</v>
       </c>
       <c r="O33">
-        <v>56.64820663599998</v>
+        <v>54.94937459199999</v>
       </c>
       <c r="P33">
-        <v>145.6668170639999</v>
+        <v>141.298391808</v>
       </c>
       <c r="Q33">
-        <v>349.0668170639999</v>
+        <v>344.698391808</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07892556927975436</v>
+        <v>0.07930964869476272</v>
       </c>
       <c r="T33">
-        <v>0.7650246946825486</v>
+        <v>0.7738948890245431</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.075657544158671</v>
+        <v>2.010793245903713</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4176,22 +4176,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06869920111243864</v>
+        <v>0.07141255942184678</v>
       </c>
       <c r="C34">
-        <v>6726.75619387738</v>
+        <v>5915.437367533572</v>
       </c>
       <c r="D34">
-        <v>9621.05219387738</v>
+        <v>8904.386367533572</v>
       </c>
       <c r="E34">
-        <v>2190.296</v>
+        <v>2284.949000000001</v>
       </c>
       <c r="F34">
-        <v>3028.896</v>
+        <v>3123.549</v>
       </c>
       <c r="G34">
         <v>134.6</v>
@@ -4212,45 +4212,45 @@
         <v>390.4</v>
       </c>
       <c r="M34">
-        <v>194.1522336</v>
+        <v>236.7650142000001</v>
       </c>
       <c r="N34">
-        <v>196.2477664</v>
+        <v>153.6349857999999</v>
       </c>
       <c r="O34">
-        <v>54.94937459199999</v>
+        <v>43.01779602399998</v>
       </c>
       <c r="P34">
-        <v>141.298391808</v>
+        <v>110.6171897759999</v>
       </c>
       <c r="Q34">
-        <v>344.698391808</v>
+        <v>314.017189776</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07930964869476272</v>
+        <v>0.0797051931669355</v>
       </c>
       <c r="T34">
-        <v>0.7738948890245431</v>
+        <v>0.7830298652871941</v>
       </c>
       <c r="U34">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V34">
         <v>0.28</v>
       </c>
       <c r="W34">
-        <v>0.046152</v>
+        <v>0.054576</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y34">
-        <v>2.010793245903713</v>
+        <v>1.648892262731948</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4258,22 +4258,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07141255942184678</v>
+        <v>0.07143023773125493</v>
       </c>
       <c r="C35">
-        <v>5915.437367533572</v>
+        <v>5816.464991802459</v>
       </c>
       <c r="D35">
-        <v>8904.386367533572</v>
+        <v>8900.06699180246</v>
       </c>
       <c r="E35">
-        <v>2284.949000000001</v>
+        <v>2379.602000000001</v>
       </c>
       <c r="F35">
-        <v>3123.549</v>
+        <v>3218.202000000001</v>
       </c>
       <c r="G35">
         <v>134.6</v>
@@ -4294,28 +4294,28 @@
         <v>390.4</v>
       </c>
       <c r="M35">
-        <v>236.7650142000001</v>
+        <v>243.9397116000001</v>
       </c>
       <c r="N35">
-        <v>153.6349857999999</v>
+        <v>146.4602883999999</v>
       </c>
       <c r="O35">
-        <v>43.01779602399998</v>
+        <v>41.00888075199998</v>
       </c>
       <c r="P35">
-        <v>110.6171897759999</v>
+        <v>105.4514076479999</v>
       </c>
       <c r="Q35">
-        <v>314.017189776</v>
+        <v>308.851407648</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.0797051931669355</v>
+        <v>0.08011272383523474</v>
       </c>
       <c r="T35">
-        <v>0.7830298652871941</v>
+        <v>0.7924416590123498</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.648892262731948</v>
+        <v>1.600395431475126</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4340,22 +4340,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07143023773125493</v>
+        <v>0.07144791604066308</v>
       </c>
       <c r="C36">
-        <v>5816.464991802459</v>
+        <v>5717.496804560052</v>
       </c>
       <c r="D36">
-        <v>8900.06699180246</v>
+        <v>8895.751804560052</v>
       </c>
       <c r="E36">
-        <v>2379.602000000001</v>
+        <v>2474.255000000001</v>
       </c>
       <c r="F36">
-        <v>3218.202000000001</v>
+        <v>3312.855</v>
       </c>
       <c r="G36">
         <v>134.6</v>
@@ -4376,28 +4376,28 @@
         <v>390.4</v>
       </c>
       <c r="M36">
-        <v>243.9397116000001</v>
+        <v>251.1144090000001</v>
       </c>
       <c r="N36">
-        <v>146.4602883999999</v>
+        <v>139.2855909999999</v>
       </c>
       <c r="O36">
-        <v>41.00888075199998</v>
+        <v>38.99996547999999</v>
       </c>
       <c r="P36">
-        <v>105.4514076479999</v>
+        <v>100.2856255199999</v>
       </c>
       <c r="Q36">
-        <v>308.851407648</v>
+        <v>303.6856255199999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08011272383523474</v>
+        <v>0.08053279390871243</v>
       </c>
       <c r="T36">
-        <v>0.7924416590123498</v>
+        <v>0.802143046390587</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4414,7 +4414,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>1.600395431475126</v>
+        <v>1.554669847718694</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4422,22 +4422,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07144791604066308</v>
+        <v>0.07146559435007122</v>
       </c>
       <c r="C37">
-        <v>5717.496804560052</v>
+        <v>5618.532799716962</v>
       </c>
       <c r="D37">
-        <v>8895.751804560052</v>
+        <v>8891.440799716962</v>
       </c>
       <c r="E37">
-        <v>2474.255000000001</v>
+        <v>2568.908000000001</v>
       </c>
       <c r="F37">
-        <v>3312.855</v>
+        <v>3407.508000000001</v>
       </c>
       <c r="G37">
         <v>134.6</v>
@@ -4458,28 +4458,28 @@
         <v>390.4</v>
       </c>
       <c r="M37">
-        <v>251.1144090000001</v>
+        <v>258.2891064000001</v>
       </c>
       <c r="N37">
-        <v>139.2855909999999</v>
+        <v>132.1108935999999</v>
       </c>
       <c r="O37">
-        <v>38.99996547999999</v>
+        <v>36.99105020799997</v>
       </c>
       <c r="P37">
-        <v>100.2856255199999</v>
+        <v>95.11984339199992</v>
       </c>
       <c r="Q37">
-        <v>303.6856255199999</v>
+        <v>298.5198433919999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08053279390871243</v>
+        <v>0.08096599117198627</v>
       </c>
       <c r="T37">
-        <v>0.802143046390587</v>
+        <v>0.8121476021243942</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4496,7 +4496,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>1.554669847718694</v>
+        <v>1.511484574170952</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4504,22 +4504,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07146559435007122</v>
+        <v>0.08377924249822243</v>
       </c>
       <c r="C38">
-        <v>5618.532799716962</v>
+        <v>3279.982212282349</v>
       </c>
       <c r="D38">
-        <v>8891.440799716962</v>
+        <v>6647.543212282349</v>
       </c>
       <c r="E38">
-        <v>2568.908</v>
+        <v>2663.561000000001</v>
       </c>
       <c r="F38">
-        <v>3407.508</v>
+        <v>3502.161000000001</v>
       </c>
       <c r="G38">
         <v>134.6</v>
@@ -4540,45 +4540,45 @@
         <v>390.4</v>
       </c>
       <c r="M38">
-        <v>258.2891064</v>
+        <v>415.3562946000001</v>
       </c>
       <c r="N38">
-        <v>132.1108935999999</v>
+        <v>-24.95629460000015</v>
       </c>
       <c r="O38">
-        <v>36.99105020799999</v>
+        <v>-6.987762488000042</v>
       </c>
       <c r="P38">
-        <v>95.11984339199995</v>
+        <v>-17.9685321120001</v>
       </c>
       <c r="Q38">
-        <v>298.519843392</v>
+        <v>185.4314678879999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08096599117198627</v>
+        <v>0.08166024126193011</v>
       </c>
       <c r="T38">
-        <v>0.8121476021243942</v>
+        <v>0.8281810914995404</v>
       </c>
       <c r="U38">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V38">
-        <v>0.28</v>
+        <v>0.2631764618019586</v>
       </c>
       <c r="W38">
-        <v>0.054576</v>
+        <v>0.08738727163028771</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y38">
-        <v>1.511484574170953</v>
+        <v>0.939915935006995</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4586,22 +4586,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08377924249822243</v>
+        <v>0.08450724249822242</v>
       </c>
       <c r="C39">
-        <v>3279.982212282349</v>
+        <v>3087.60441243817</v>
       </c>
       <c r="D39">
-        <v>6647.543212282349</v>
+        <v>6549.81841243817</v>
       </c>
       <c r="E39">
-        <v>2663.561000000001</v>
+        <v>2758.214</v>
       </c>
       <c r="F39">
-        <v>3502.161000000001</v>
+        <v>3596.814</v>
       </c>
       <c r="G39">
         <v>134.6</v>
@@ -4622,37 +4622,37 @@
         <v>390.4</v>
       </c>
       <c r="M39">
-        <v>415.3562946000001</v>
+        <v>426.5821404000001</v>
       </c>
       <c r="N39">
-        <v>-24.95629460000015</v>
+        <v>-36.18214040000009</v>
       </c>
       <c r="O39">
-        <v>-6.987762488000042</v>
+        <v>-10.13099931200003</v>
       </c>
       <c r="P39">
-        <v>-17.9685321120001</v>
+        <v>-26.05114108800007</v>
       </c>
       <c r="Q39">
-        <v>185.4314678879999</v>
+        <v>177.3488589119999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08166024126193011</v>
+        <v>0.08223863225002576</v>
       </c>
       <c r="T39">
-        <v>0.8281810914995404</v>
+        <v>0.8415388510398557</v>
       </c>
       <c r="U39">
         <v>0.1186</v>
       </c>
       <c r="V39">
-        <v>0.2631764618019586</v>
+        <v>0.2562507654387493</v>
       </c>
       <c r="W39">
-        <v>0.08738727163028771</v>
+        <v>0.08820865921896434</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.939915935006995</v>
+        <v>0.9151813051383899</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4668,22 +4668,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08450724249822242</v>
+        <v>0.08523524249822242</v>
       </c>
       <c r="C40">
-        <v>3087.60441243817</v>
+        <v>2898.058267759478</v>
       </c>
       <c r="D40">
-        <v>6549.81841243817</v>
+        <v>6454.925267759479</v>
       </c>
       <c r="E40">
-        <v>2758.214</v>
+        <v>2852.867000000001</v>
       </c>
       <c r="F40">
-        <v>3596.814</v>
+        <v>3691.467000000001</v>
       </c>
       <c r="G40">
         <v>134.6</v>
@@ -4704,37 +4704,37 @@
         <v>390.4</v>
       </c>
       <c r="M40">
-        <v>426.5821404000001</v>
+        <v>437.8079862000001</v>
       </c>
       <c r="N40">
-        <v>-36.18214040000009</v>
+        <v>-47.40798620000015</v>
       </c>
       <c r="O40">
-        <v>-10.13099931200003</v>
+        <v>-13.27423613600004</v>
       </c>
       <c r="P40">
-        <v>-26.05114108800007</v>
+        <v>-34.13375006400011</v>
       </c>
       <c r="Q40">
-        <v>177.3488589119999</v>
+        <v>169.2662499359999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08223863225002576</v>
+        <v>0.08283598687707536</v>
       </c>
       <c r="T40">
-        <v>0.8415388510398557</v>
+        <v>0.8553345699093615</v>
       </c>
       <c r="U40">
         <v>0.1186</v>
       </c>
       <c r="V40">
-        <v>0.2562507654387493</v>
+        <v>0.2496802329916018</v>
       </c>
       <c r="W40">
-        <v>0.08820865921896434</v>
+        <v>0.08898792436719603</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.9151813051383899</v>
+        <v>0.8917151178271491</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4750,22 +4750,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08523524249822242</v>
+        <v>0.08596324249822243</v>
       </c>
       <c r="C41">
-        <v>2898.058267759478</v>
+        <v>2711.222461619823</v>
       </c>
       <c r="D41">
-        <v>6454.925267759479</v>
+        <v>6362.742461619823</v>
       </c>
       <c r="E41">
-        <v>2852.867000000001</v>
+        <v>2947.520000000001</v>
       </c>
       <c r="F41">
-        <v>3691.467000000001</v>
+        <v>3786.120000000001</v>
       </c>
       <c r="G41">
         <v>134.6</v>
@@ -4786,37 +4786,37 @@
         <v>390.4</v>
       </c>
       <c r="M41">
-        <v>437.8079862000001</v>
+        <v>449.0338320000001</v>
       </c>
       <c r="N41">
-        <v>-47.40798620000015</v>
+        <v>-58.63383200000015</v>
       </c>
       <c r="O41">
-        <v>-13.27423613600004</v>
+        <v>-16.41747296000004</v>
       </c>
       <c r="P41">
-        <v>-34.13375006400011</v>
+        <v>-42.21635904000011</v>
       </c>
       <c r="Q41">
-        <v>169.2662499359999</v>
+        <v>161.1836409599999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08283598687707536</v>
+        <v>0.08345325332502662</v>
       </c>
       <c r="T41">
-        <v>0.8553345699093615</v>
+        <v>0.8695901460745177</v>
       </c>
       <c r="U41">
         <v>0.1186</v>
       </c>
       <c r="V41">
-        <v>0.2496802329916018</v>
+        <v>0.2434382271668117</v>
       </c>
       <c r="W41">
-        <v>0.08898792436719603</v>
+        <v>0.08972822625801613</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.8917151178271491</v>
+        <v>0.8694222398814704</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4832,22 +4832,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08596324249822243</v>
+        <v>0.08669124249822241</v>
       </c>
       <c r="C42">
-        <v>2711.222461619823</v>
+        <v>2526.982509909902</v>
       </c>
       <c r="D42">
-        <v>6362.742461619823</v>
+        <v>6273.155509909902</v>
       </c>
       <c r="E42">
-        <v>2947.520000000001</v>
+        <v>3042.173000000001</v>
       </c>
       <c r="F42">
-        <v>3786.120000000001</v>
+        <v>3880.773000000001</v>
       </c>
       <c r="G42">
         <v>134.6</v>
@@ -4868,37 +4868,37 @@
         <v>390.4</v>
       </c>
       <c r="M42">
-        <v>449.0338320000001</v>
+        <v>460.2596778000001</v>
       </c>
       <c r="N42">
-        <v>-58.63383200000015</v>
+        <v>-69.85967780000016</v>
       </c>
       <c r="O42">
-        <v>-16.41747296000004</v>
+        <v>-19.56070978400005</v>
       </c>
       <c r="P42">
-        <v>-42.21635904000011</v>
+        <v>-50.29896801600011</v>
       </c>
       <c r="Q42">
-        <v>161.1836409599999</v>
+        <v>153.1010319839999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08345325332502662</v>
+        <v>0.0840914440593491</v>
       </c>
       <c r="T42">
-        <v>0.8695901460745177</v>
+        <v>0.8843289621096788</v>
       </c>
       <c r="U42">
         <v>0.1186</v>
       </c>
       <c r="V42">
-        <v>0.2434382271668117</v>
+        <v>0.2375007094310358</v>
       </c>
       <c r="W42">
-        <v>0.08972822625801613</v>
+        <v>0.09043241586147915</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8694222398814704</v>
+        <v>0.8482168193965565</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4914,22 +4914,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08669124249822241</v>
+        <v>0.08741924249822242</v>
       </c>
       <c r="C43">
-        <v>2526.982509909902</v>
+        <v>2345.230286709344</v>
       </c>
       <c r="D43">
-        <v>6273.155509909902</v>
+        <v>6186.056286709344</v>
       </c>
       <c r="E43">
-        <v>3042.173000000001</v>
+        <v>3136.826000000001</v>
       </c>
       <c r="F43">
-        <v>3880.773000000001</v>
+        <v>3975.426000000001</v>
       </c>
       <c r="G43">
         <v>134.6</v>
@@ -4950,37 +4950,37 @@
         <v>390.4</v>
       </c>
       <c r="M43">
-        <v>460.2596778000001</v>
+        <v>471.4855236000001</v>
       </c>
       <c r="N43">
-        <v>-69.85967780000016</v>
+        <v>-81.08552360000016</v>
       </c>
       <c r="O43">
-        <v>-19.56070978400005</v>
+        <v>-22.70394660800005</v>
       </c>
       <c r="P43">
-        <v>-50.29896801600011</v>
+        <v>-58.38157699200011</v>
       </c>
       <c r="Q43">
-        <v>153.1010319839999</v>
+        <v>145.0184230079999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.0840914440593491</v>
+        <v>0.0847516413707172</v>
       </c>
       <c r="T43">
-        <v>0.8843289621096788</v>
+        <v>0.8995760131805354</v>
       </c>
       <c r="U43">
         <v>0.1186</v>
       </c>
       <c r="V43">
-        <v>0.2375007094310358</v>
+        <v>0.2318459306350588</v>
       </c>
       <c r="W43">
-        <v>0.09043241586147915</v>
+        <v>0.09110307262668203</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8482168193965565</v>
+        <v>0.8280211808394956</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4996,22 +4996,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08741924249822242</v>
+        <v>0.08814724249822242</v>
       </c>
       <c r="C44">
-        <v>2345.230286709344</v>
+        <v>2165.86358893205</v>
       </c>
       <c r="D44">
-        <v>6186.056286709344</v>
+        <v>6101.342588932051</v>
       </c>
       <c r="E44">
-        <v>3136.826</v>
+        <v>3231.479000000001</v>
       </c>
       <c r="F44">
-        <v>3975.426</v>
+        <v>4070.079000000001</v>
       </c>
       <c r="G44">
         <v>134.6</v>
@@ -5032,37 +5032,37 @@
         <v>390.4</v>
       </c>
       <c r="M44">
-        <v>471.4855236000001</v>
+        <v>482.7113694000001</v>
       </c>
       <c r="N44">
-        <v>-81.0855236000001</v>
+        <v>-92.31136940000016</v>
       </c>
       <c r="O44">
-        <v>-22.70394660800003</v>
+        <v>-25.84718343200005</v>
       </c>
       <c r="P44">
-        <v>-58.38157699200007</v>
+        <v>-66.46418596800011</v>
       </c>
       <c r="Q44">
-        <v>145.0184230079999</v>
+        <v>136.9358140319999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08475164137071718</v>
+        <v>0.08543500350002801</v>
       </c>
       <c r="T44">
-        <v>0.8995760131805353</v>
+        <v>0.9153580484994921</v>
       </c>
       <c r="U44">
         <v>0.1186</v>
       </c>
       <c r="V44">
-        <v>0.2318459306350588</v>
+        <v>0.2264541648063365</v>
       </c>
       <c r="W44">
-        <v>0.09110307262668203</v>
+        <v>0.0917425360539685</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8280211808394957</v>
+        <v>0.8087648743083445</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5078,22 +5078,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08814724249822242</v>
+        <v>0.1260409504085061</v>
       </c>
       <c r="C45">
-        <v>2165.86358893205</v>
+        <v>-467.9548878938058</v>
       </c>
       <c r="D45">
-        <v>6101.342588932051</v>
+        <v>3562.177112106195</v>
       </c>
       <c r="E45">
-        <v>3231.479000000001</v>
+        <v>3326.132000000001</v>
       </c>
       <c r="F45">
-        <v>4070.079000000001</v>
+        <v>4164.732000000001</v>
       </c>
       <c r="G45">
         <v>134.6</v>
@@ -5114,45 +5114,45 @@
         <v>390.4</v>
       </c>
       <c r="M45">
-        <v>482.7113694000001</v>
+        <v>836.2781856000003</v>
       </c>
       <c r="N45">
-        <v>-92.31136940000016</v>
+        <v>-445.8781856000003</v>
       </c>
       <c r="O45">
-        <v>-25.84718343200005</v>
+        <v>-124.8458919680001</v>
       </c>
       <c r="P45">
-        <v>-66.46418596800011</v>
+        <v>-321.0322936320002</v>
       </c>
       <c r="Q45">
-        <v>136.9358140319999</v>
+        <v>-117.6322936320002</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08543500350002801</v>
+        <v>0.08792439268803515</v>
       </c>
       <c r="T45">
-        <v>0.9153580484994921</v>
+        <v>0.97284971565901</v>
       </c>
       <c r="U45">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.2264541648063365</v>
+        <v>0.1307124852498364</v>
       </c>
       <c r="W45">
-        <v>0.0917425360539685</v>
+        <v>0.1745529329618328</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y45">
-        <v>0.8087648743083445</v>
+        <v>0.4668303044637014</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5160,22 +5160,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1260409504085061</v>
+        <v>0.1275909504085062</v>
       </c>
       <c r="C46">
-        <v>-467.9548878938058</v>
+        <v>-622.2310522739303</v>
       </c>
       <c r="D46">
-        <v>3562.177112106195</v>
+        <v>3502.55394772607</v>
       </c>
       <c r="E46">
-        <v>3326.132000000001</v>
+        <v>3420.785</v>
       </c>
       <c r="F46">
-        <v>4164.732000000001</v>
+        <v>4259.385</v>
       </c>
       <c r="G46">
         <v>134.6</v>
@@ -5196,37 +5196,37 @@
         <v>390.4</v>
       </c>
       <c r="M46">
-        <v>836.2781856000003</v>
+        <v>855.2845080000001</v>
       </c>
       <c r="N46">
-        <v>-445.8781856000003</v>
+        <v>-464.8845080000001</v>
       </c>
       <c r="O46">
-        <v>-124.8458919680001</v>
+        <v>-130.16766224</v>
       </c>
       <c r="P46">
-        <v>-321.0322936320002</v>
+        <v>-334.7168457600001</v>
       </c>
       <c r="Q46">
-        <v>-117.6322936320002</v>
+        <v>-131.3168457600001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08792439268803515</v>
+        <v>0.08869029073690851</v>
       </c>
       <c r="T46">
-        <v>0.97284971565901</v>
+        <v>0.9905378923073558</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.1307124852498364</v>
+        <v>0.1278077633553956</v>
       </c>
       <c r="W46">
-        <v>0.1745529329618328</v>
+        <v>0.1751362011182366</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4668303044637014</v>
+        <v>0.4564562976978416</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5242,22 +5242,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1275909504085062</v>
+        <v>0.1291409504085061</v>
       </c>
       <c r="C47">
-        <v>-622.2310522739303</v>
+        <v>-774.54414776051</v>
       </c>
       <c r="D47">
-        <v>3502.55394772607</v>
+        <v>3444.893852239491</v>
       </c>
       <c r="E47">
-        <v>3420.785</v>
+        <v>3515.438000000001</v>
       </c>
       <c r="F47">
-        <v>4259.385</v>
+        <v>4354.038</v>
       </c>
       <c r="G47">
         <v>134.6</v>
@@ -5278,37 +5278,37 @@
         <v>390.4</v>
       </c>
       <c r="M47">
-        <v>855.2845080000001</v>
+        <v>874.2908304000001</v>
       </c>
       <c r="N47">
-        <v>-464.8845080000001</v>
+        <v>-483.8908304000001</v>
       </c>
       <c r="O47">
-        <v>-130.16766224</v>
+        <v>-135.4894325120001</v>
       </c>
       <c r="P47">
-        <v>-334.7168457600001</v>
+        <v>-348.4013978880001</v>
       </c>
       <c r="Q47">
-        <v>-131.3168457600001</v>
+        <v>-145.0013978880001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08869029073690851</v>
+        <v>0.0894845553801846</v>
       </c>
       <c r="T47">
-        <v>0.9905378923073558</v>
+        <v>1.008881186609344</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1278077633553956</v>
+        <v>0.1250293337172349</v>
       </c>
       <c r="W47">
-        <v>0.1751362011182366</v>
+        <v>0.1756941097895793</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.4564562976978416</v>
+        <v>0.4465333347044101</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5324,22 +5324,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1291409504085061</v>
+        <v>0.1306909504085061</v>
       </c>
       <c r="C48">
-        <v>-774.54414776051</v>
+        <v>-924.9895540738171</v>
       </c>
       <c r="D48">
-        <v>3444.893852239491</v>
+        <v>3389.101445926184</v>
       </c>
       <c r="E48">
-        <v>3515.438000000001</v>
+        <v>3610.091000000001</v>
       </c>
       <c r="F48">
-        <v>4354.038</v>
+        <v>4448.691000000001</v>
       </c>
       <c r="G48">
         <v>134.6</v>
@@ -5360,37 +5360,37 @@
         <v>390.4</v>
       </c>
       <c r="M48">
-        <v>874.2908304000001</v>
+        <v>893.2971528000002</v>
       </c>
       <c r="N48">
-        <v>-483.8908304000001</v>
+        <v>-502.8971528000002</v>
       </c>
       <c r="O48">
-        <v>-135.4894325120001</v>
+        <v>-140.8112027840001</v>
       </c>
       <c r="P48">
-        <v>-348.4013978880001</v>
+        <v>-362.0859500160001</v>
       </c>
       <c r="Q48">
-        <v>-145.0013978880001</v>
+        <v>-158.6859500160001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.0894845553801846</v>
+        <v>0.09030879227415034</v>
       </c>
       <c r="T48">
-        <v>1.008881186609344</v>
+        <v>1.027916680696313</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1250293337172349</v>
+        <v>0.1223691351275065</v>
       </c>
       <c r="W48">
-        <v>0.1756941097895793</v>
+        <v>0.1762282776663967</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.4465333347044101</v>
+        <v>0.4370326254553801</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5406,22 +5406,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1306909504085061</v>
+        <v>0.1322409504085061</v>
       </c>
       <c r="C49">
-        <v>-924.9895540738171</v>
+        <v>-1073.656570453079</v>
       </c>
       <c r="D49">
-        <v>3389.101445926184</v>
+        <v>3335.087429546922</v>
       </c>
       <c r="E49">
-        <v>3610.091000000001</v>
+        <v>3704.744000000001</v>
       </c>
       <c r="F49">
-        <v>4448.691000000001</v>
+        <v>4543.344000000001</v>
       </c>
       <c r="G49">
         <v>134.6</v>
@@ -5442,37 +5442,37 @@
         <v>390.4</v>
       </c>
       <c r="M49">
-        <v>893.2971528000002</v>
+        <v>912.3034752000002</v>
       </c>
       <c r="N49">
-        <v>-502.8971528000002</v>
+        <v>-521.9034752000002</v>
       </c>
       <c r="O49">
-        <v>-140.8112027840001</v>
+        <v>-146.1329730560001</v>
       </c>
       <c r="P49">
-        <v>-362.0859500160001</v>
+        <v>-375.7705021440001</v>
       </c>
       <c r="Q49">
-        <v>-158.6859500160001</v>
+        <v>-172.3705021440001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09030879227415034</v>
+        <v>0.09116473058711477</v>
       </c>
       <c r="T49">
-        <v>1.027916680696313</v>
+        <v>1.047684309171242</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1223691351275065</v>
+        <v>0.1198197781456834</v>
       </c>
       <c r="W49">
-        <v>0.1762282776663967</v>
+        <v>0.1767401885483468</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.4370326254553801</v>
+        <v>0.4279277790917264</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5488,22 +5488,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1322409504085061</v>
+        <v>0.1337909504085061</v>
       </c>
       <c r="C50">
-        <v>-1073.656570453079</v>
+        <v>-1220.628892595474</v>
       </c>
       <c r="D50">
-        <v>3335.087429546922</v>
+        <v>3282.768107404527</v>
       </c>
       <c r="E50">
-        <v>3704.744</v>
+        <v>3799.397</v>
       </c>
       <c r="F50">
-        <v>4543.344</v>
+        <v>4637.997</v>
       </c>
       <c r="G50">
         <v>134.6</v>
@@ -5524,37 +5524,37 @@
         <v>390.4</v>
       </c>
       <c r="M50">
-        <v>912.3034752000001</v>
+        <v>931.3097976000001</v>
       </c>
       <c r="N50">
-        <v>-521.9034752000001</v>
+        <v>-540.9097976000002</v>
       </c>
       <c r="O50">
-        <v>-146.1329730560001</v>
+        <v>-151.4547433280001</v>
       </c>
       <c r="P50">
-        <v>-375.770502144</v>
+        <v>-389.4550542720001</v>
       </c>
       <c r="Q50">
-        <v>-172.370502144</v>
+        <v>-186.0550542720001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09116473058711477</v>
+        <v>0.09205423510843075</v>
       </c>
       <c r="T50">
-        <v>1.047684309171242</v>
+        <v>1.068227138762835</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1198197781456834</v>
+        <v>0.1173744765508735</v>
       </c>
       <c r="W50">
-        <v>0.1767401885483468</v>
+        <v>0.1772312051085846</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4279277790917264</v>
+        <v>0.4191945591102626</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5570,22 +5570,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1337909504085061</v>
+        <v>0.1353409504085061</v>
       </c>
       <c r="C51">
-        <v>-1220.628892595474</v>
+        <v>-1365.985045396484</v>
       </c>
       <c r="D51">
-        <v>3282.768107404527</v>
+        <v>3232.064954603517</v>
       </c>
       <c r="E51">
-        <v>3799.397</v>
+        <v>3894.050000000001</v>
       </c>
       <c r="F51">
-        <v>4637.997</v>
+        <v>4732.650000000001</v>
       </c>
       <c r="G51">
         <v>134.6</v>
@@ -5606,37 +5606,37 @@
         <v>390.4</v>
       </c>
       <c r="M51">
-        <v>931.3097976000001</v>
+        <v>950.3161200000002</v>
       </c>
       <c r="N51">
-        <v>-540.9097976000002</v>
+        <v>-559.9161200000002</v>
       </c>
       <c r="O51">
-        <v>-151.4547433280001</v>
+        <v>-156.7765136000001</v>
       </c>
       <c r="P51">
-        <v>-389.4550542720001</v>
+        <v>-403.1396064000002</v>
       </c>
       <c r="Q51">
-        <v>-186.0550542720001</v>
+        <v>-199.7396064000002</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09205423510843075</v>
+        <v>0.09297931981059937</v>
       </c>
       <c r="T51">
-        <v>1.068227138762835</v>
+        <v>1.089591681538091</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1173744765508735</v>
+        <v>0.1150269870198561</v>
       </c>
       <c r="W51">
-        <v>0.1772312051085846</v>
+        <v>0.1777025810064129</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.4191945591102626</v>
+        <v>0.4108106679280573</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5652,22 +5652,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1353409504085061</v>
+        <v>0.1368909504085061</v>
       </c>
       <c r="C52">
-        <v>-1365.985045396484</v>
+        <v>-1509.798776197549</v>
       </c>
       <c r="D52">
-        <v>3232.064954603517</v>
+        <v>3182.904223802452</v>
       </c>
       <c r="E52">
-        <v>3894.050000000001</v>
+        <v>3988.703000000001</v>
       </c>
       <c r="F52">
-        <v>4732.650000000001</v>
+        <v>4827.303000000001</v>
       </c>
       <c r="G52">
         <v>134.6</v>
@@ -5688,37 +5688,37 @@
         <v>390.4</v>
       </c>
       <c r="M52">
-        <v>950.3161200000002</v>
+        <v>969.3224424000002</v>
       </c>
       <c r="N52">
-        <v>-559.9161200000002</v>
+        <v>-578.9224424000003</v>
       </c>
       <c r="O52">
-        <v>-156.7765136000001</v>
+        <v>-162.0982838720001</v>
       </c>
       <c r="P52">
-        <v>-403.1396064000002</v>
+        <v>-416.8241585280002</v>
       </c>
       <c r="Q52">
-        <v>-199.7396064000002</v>
+        <v>-213.4241585280002</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09297931981059937</v>
+        <v>0.09394216307204017</v>
       </c>
       <c r="T52">
-        <v>1.089591681538091</v>
+        <v>1.11182824646744</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1150269870198561</v>
+        <v>0.1127715559018197</v>
       </c>
       <c r="W52">
-        <v>0.1777025810064129</v>
+        <v>0.1781554715749146</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.4108106679280573</v>
+        <v>0.4027555567922131</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5734,22 +5734,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1368909504085061</v>
+        <v>0.1384409504085062</v>
       </c>
       <c r="C53">
-        <v>-1509.798776197549</v>
+        <v>-1652.139412682887</v>
       </c>
       <c r="D53">
-        <v>3182.904223802452</v>
+        <v>3135.216587317114</v>
       </c>
       <c r="E53">
-        <v>3988.703000000001</v>
+        <v>4083.356000000001</v>
       </c>
       <c r="F53">
-        <v>4827.303000000001</v>
+        <v>4921.956000000001</v>
       </c>
       <c r="G53">
         <v>134.6</v>
@@ -5770,37 +5770,37 @@
         <v>390.4</v>
       </c>
       <c r="M53">
-        <v>969.3224424000002</v>
+        <v>988.3287648000003</v>
       </c>
       <c r="N53">
-        <v>-578.9224424000003</v>
+        <v>-597.9287648000003</v>
       </c>
       <c r="O53">
-        <v>-162.0982838720001</v>
+        <v>-167.4200541440001</v>
       </c>
       <c r="P53">
-        <v>-416.8241585280002</v>
+        <v>-430.5087106560002</v>
       </c>
       <c r="Q53">
-        <v>-213.4241585280002</v>
+        <v>-227.1087106560002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09394216307204017</v>
+        <v>0.09494512480270767</v>
       </c>
       <c r="T53">
-        <v>1.11182824646744</v>
+        <v>1.134991334935512</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1127715559018197</v>
+        <v>0.110602872134477</v>
       </c>
       <c r="W53">
-        <v>0.1781554715749146</v>
+        <v>0.178590943275397</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.4027555567922131</v>
+        <v>0.395010257623132</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5816,22 +5816,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1384409504085062</v>
+        <v>0.1399909504085061</v>
       </c>
       <c r="C54">
-        <v>-1652.139412682887</v>
+        <v>-1793.072189078243</v>
       </c>
       <c r="D54">
-        <v>3135.216587317114</v>
+        <v>3088.936810921758</v>
       </c>
       <c r="E54">
-        <v>4083.356000000001</v>
+        <v>4178.009</v>
       </c>
       <c r="F54">
-        <v>4921.956000000001</v>
+        <v>5016.609</v>
       </c>
       <c r="G54">
         <v>134.6</v>
@@ -5852,37 +5852,37 @@
         <v>390.4</v>
       </c>
       <c r="M54">
-        <v>988.3287648000003</v>
+        <v>1007.3350872</v>
       </c>
       <c r="N54">
-        <v>-597.9287648000003</v>
+        <v>-616.9350872000001</v>
       </c>
       <c r="O54">
-        <v>-167.4200541440001</v>
+        <v>-172.741824416</v>
       </c>
       <c r="P54">
-        <v>-430.5087106560002</v>
+        <v>-444.1932627840001</v>
       </c>
       <c r="Q54">
-        <v>-227.1087106560002</v>
+        <v>-240.7932627840001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09494512480270767</v>
+        <v>0.09599076575595678</v>
       </c>
       <c r="T54">
-        <v>1.134991334935512</v>
+        <v>1.15914008674265</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.110602872134477</v>
+        <v>0.1085160254904303</v>
       </c>
       <c r="W54">
-        <v>0.178590943275397</v>
+        <v>0.1790099820815216</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.395010257623132</v>
+        <v>0.3875572338943938</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5898,22 +5898,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1399909504085061</v>
+        <v>0.1415409504085061</v>
       </c>
       <c r="C55">
-        <v>-1793.072189078243</v>
+        <v>-1932.658543879263</v>
       </c>
       <c r="D55">
-        <v>3088.936810921758</v>
+        <v>3044.003456120738</v>
       </c>
       <c r="E55">
-        <v>4178.009</v>
+        <v>4272.662</v>
       </c>
       <c r="F55">
-        <v>5016.609</v>
+        <v>5111.262000000001</v>
       </c>
       <c r="G55">
         <v>134.6</v>
@@ -5934,37 +5934,37 @@
         <v>390.4</v>
       </c>
       <c r="M55">
-        <v>1007.3350872</v>
+        <v>1026.3414096</v>
       </c>
       <c r="N55">
-        <v>-616.9350872000001</v>
+        <v>-635.9414096000002</v>
       </c>
       <c r="O55">
-        <v>-172.741824416</v>
+        <v>-178.0635946880001</v>
       </c>
       <c r="P55">
-        <v>-444.1932627840001</v>
+        <v>-457.8778149120001</v>
       </c>
       <c r="Q55">
-        <v>-240.7932627840001</v>
+        <v>-254.4778149120001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09599076575595678</v>
+        <v>0.09708186935934712</v>
       </c>
       <c r="T55">
-        <v>1.15914008674265</v>
+        <v>1.184338784280534</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1085160254904303</v>
+        <v>0.1065064694628297</v>
       </c>
       <c r="W55">
-        <v>0.1790099820815216</v>
+        <v>0.1794135009318638</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3875572338943938</v>
+        <v>0.3803802480815346</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5980,22 +5980,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1415409504085061</v>
+        <v>0.1430909504085061</v>
       </c>
       <c r="C56">
-        <v>-1932.658543879263</v>
+        <v>-2070.956391966918</v>
       </c>
       <c r="D56">
-        <v>3044.003456120738</v>
+        <v>3000.358608033083</v>
       </c>
       <c r="E56">
-        <v>4272.662</v>
+        <v>4367.315000000001</v>
       </c>
       <c r="F56">
-        <v>5111.262000000001</v>
+        <v>5205.915000000001</v>
       </c>
       <c r="G56">
         <v>134.6</v>
@@ -6016,37 +6016,37 @@
         <v>390.4</v>
       </c>
       <c r="M56">
-        <v>1026.3414096</v>
+        <v>1045.347732</v>
       </c>
       <c r="N56">
-        <v>-635.9414096000002</v>
+        <v>-654.9477320000002</v>
       </c>
       <c r="O56">
-        <v>-178.0635946880001</v>
+        <v>-183.3853649600001</v>
       </c>
       <c r="P56">
-        <v>-457.8778149120001</v>
+        <v>-471.5623670400001</v>
       </c>
       <c r="Q56">
-        <v>-254.4778149120001</v>
+        <v>-268.1623670400002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09708186935934712</v>
+        <v>0.09822146645622151</v>
       </c>
       <c r="T56">
-        <v>1.184338784280534</v>
+        <v>1.210657423931213</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1065064694628297</v>
+        <v>0.1045699881998692</v>
       </c>
       <c r="W56">
-        <v>0.1794135009318638</v>
+        <v>0.1798023463694663</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3803802480815346</v>
+        <v>0.3734642435709612</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6062,22 +6062,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1430909504085061</v>
+        <v>0.1446409504085061</v>
       </c>
       <c r="C57">
-        <v>-2070.956391966918</v>
+        <v>-2208.020373644335</v>
       </c>
       <c r="D57">
-        <v>3000.358608033083</v>
+        <v>2957.947626355666</v>
       </c>
       <c r="E57">
-        <v>4367.315000000001</v>
+        <v>4461.968000000001</v>
       </c>
       <c r="F57">
-        <v>5205.915000000001</v>
+        <v>5300.568000000001</v>
       </c>
       <c r="G57">
         <v>134.6</v>
@@ -6098,37 +6098,37 @@
         <v>390.4</v>
       </c>
       <c r="M57">
-        <v>1045.347732</v>
+        <v>1064.3540544</v>
       </c>
       <c r="N57">
-        <v>-654.9477320000002</v>
+        <v>-673.9540544000002</v>
       </c>
       <c r="O57">
-        <v>-183.3853649600001</v>
+        <v>-188.7071352320001</v>
       </c>
       <c r="P57">
-        <v>-471.5623670400001</v>
+        <v>-485.2469191680001</v>
       </c>
       <c r="Q57">
-        <v>-268.1623670400002</v>
+        <v>-281.8469191680001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09822146645622151</v>
+        <v>0.09941286342113564</v>
       </c>
       <c r="T57">
-        <v>1.210657423931213</v>
+        <v>1.238172365384195</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1045699881998692</v>
+        <v>0.1027026669820143</v>
       </c>
       <c r="W57">
-        <v>0.1798023463694663</v>
+        <v>0.1801773044700115</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3734642435709612</v>
+        <v>0.3667952392214797</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6144,22 +6144,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1446409504085061</v>
+        <v>0.1461909504085061</v>
       </c>
       <c r="C58">
-        <v>-2208.020373644335</v>
+        <v>-2343.902082846751</v>
       </c>
       <c r="D58">
-        <v>2957.947626355666</v>
+        <v>2916.71891715325</v>
       </c>
       <c r="E58">
-        <v>4461.968000000001</v>
+        <v>4556.621000000001</v>
       </c>
       <c r="F58">
-        <v>5300.568000000001</v>
+        <v>5395.221000000001</v>
       </c>
       <c r="G58">
         <v>134.6</v>
@@ -6180,37 +6180,37 @@
         <v>390.4</v>
       </c>
       <c r="M58">
-        <v>1064.3540544</v>
+        <v>1083.3603768</v>
       </c>
       <c r="N58">
-        <v>-673.9540544000002</v>
+        <v>-692.9603768000003</v>
       </c>
       <c r="O58">
-        <v>-188.7071352320001</v>
+        <v>-194.0289055040001</v>
       </c>
       <c r="P58">
-        <v>-485.2469191680001</v>
+        <v>-498.9314712960002</v>
       </c>
       <c r="Q58">
-        <v>-281.8469191680001</v>
+        <v>-295.5314712960002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09941286342113564</v>
+        <v>0.1006596741983714</v>
       </c>
       <c r="T58">
-        <v>1.238172365384195</v>
+        <v>1.26696707155592</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1027026669820143</v>
+        <v>0.1009008658068913</v>
       </c>
       <c r="W58">
-        <v>0.1801773044700115</v>
+        <v>0.1805391061459762</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3667952392214797</v>
+        <v>0.3603602350246117</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6226,22 +6226,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1461909504085061</v>
+        <v>0.1477409504085062</v>
       </c>
       <c r="C59">
-        <v>-2343.902082846751</v>
+        <v>-2478.650276528694</v>
       </c>
       <c r="D59">
-        <v>2916.71891715325</v>
+        <v>2876.623723471308</v>
       </c>
       <c r="E59">
-        <v>4556.621000000001</v>
+        <v>4651.274000000001</v>
       </c>
       <c r="F59">
-        <v>5395.221000000001</v>
+        <v>5489.874000000002</v>
       </c>
       <c r="G59">
         <v>134.6</v>
@@ -6262,37 +6262,37 @@
         <v>390.4</v>
       </c>
       <c r="M59">
-        <v>1083.3603768</v>
+        <v>1102.3666992</v>
       </c>
       <c r="N59">
-        <v>-692.9603768000003</v>
+        <v>-711.9666992000003</v>
       </c>
       <c r="O59">
-        <v>-194.0289055040001</v>
+        <v>-199.3506757760001</v>
       </c>
       <c r="P59">
-        <v>-498.9314712960002</v>
+        <v>-512.6160234240002</v>
       </c>
       <c r="Q59">
-        <v>-295.5314712960002</v>
+        <v>-309.2160234240002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1006596741983714</v>
+        <v>0.1019658569173802</v>
       </c>
       <c r="T59">
-        <v>1.26696707155592</v>
+        <v>1.297132954212014</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1009008658068913</v>
+        <v>0.09916119570677247</v>
       </c>
       <c r="W59">
-        <v>0.1805391061459762</v>
+        <v>0.1808884319020801</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3603602350246117</v>
+        <v>0.3541471275241873</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6308,22 +6308,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1477409504085061</v>
+        <v>0.1492909504085061</v>
       </c>
       <c r="C60">
-        <v>-2478.650276528692</v>
+        <v>-2612.311067015079</v>
       </c>
       <c r="D60">
-        <v>2876.623723471309</v>
+        <v>2837.615932984922</v>
       </c>
       <c r="E60">
-        <v>4651.274</v>
+        <v>4745.927</v>
       </c>
       <c r="F60">
-        <v>5489.874000000001</v>
+        <v>5584.527</v>
       </c>
       <c r="G60">
         <v>134.6</v>
@@ -6344,37 +6344,37 @@
         <v>390.4</v>
       </c>
       <c r="M60">
-        <v>1102.3666992</v>
+        <v>1121.3730216</v>
       </c>
       <c r="N60">
-        <v>-711.9666992000001</v>
+        <v>-730.9730216000002</v>
       </c>
       <c r="O60">
-        <v>-199.3506757760001</v>
+        <v>-204.6724460480001</v>
       </c>
       <c r="P60">
-        <v>-512.6160234240001</v>
+        <v>-526.3005755520001</v>
       </c>
       <c r="Q60">
-        <v>-309.2160234240001</v>
+        <v>-322.9005755520001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1019658569173802</v>
+        <v>0.1033357558665846</v>
       </c>
       <c r="T60">
-        <v>1.297132954212013</v>
+        <v>1.328770343339136</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.09916119570677248</v>
+        <v>0.09748049747445431</v>
       </c>
       <c r="W60">
-        <v>0.1808884319020801</v>
+        <v>0.1812259161071296</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3541471275241874</v>
+        <v>0.3481446338373367</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6390,22 +6390,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1492909504085061</v>
+        <v>0.1508409504085061</v>
       </c>
       <c r="C61">
-        <v>-2612.311067015079</v>
+        <v>-2744.928098911709</v>
       </c>
       <c r="D61">
-        <v>2837.615932984922</v>
+        <v>2799.651901088292</v>
       </c>
       <c r="E61">
-        <v>4745.927</v>
+        <v>4840.58</v>
       </c>
       <c r="F61">
-        <v>5584.527</v>
+        <v>5679.18</v>
       </c>
       <c r="G61">
         <v>134.6</v>
@@ -6426,37 +6426,37 @@
         <v>390.4</v>
       </c>
       <c r="M61">
-        <v>1121.3730216</v>
+        <v>1140.379344</v>
       </c>
       <c r="N61">
-        <v>-730.9730216000002</v>
+        <v>-749.9793440000002</v>
       </c>
       <c r="O61">
-        <v>-204.6724460480001</v>
+        <v>-209.9942163200001</v>
       </c>
       <c r="P61">
-        <v>-526.3005755520001</v>
+        <v>-539.9851276800001</v>
       </c>
       <c r="Q61">
-        <v>-322.9005755520001</v>
+        <v>-336.5851276800001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1033357558665846</v>
+        <v>0.1047741497632492</v>
       </c>
       <c r="T61">
-        <v>1.328770343339136</v>
+        <v>1.361989601922614</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.09748049747445431</v>
+        <v>0.09585582251654673</v>
       </c>
       <c r="W61">
-        <v>0.1812259161071296</v>
+        <v>0.1815521508386774</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3481446338373367</v>
+        <v>0.3423422232733812</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6472,22 +6472,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1508409504085061</v>
+        <v>0.1523909504085061</v>
       </c>
       <c r="C62">
-        <v>-2744.928098911709</v>
+        <v>-2876.542712002079</v>
       </c>
       <c r="D62">
-        <v>2799.651901088292</v>
+        <v>2762.690287997921</v>
       </c>
       <c r="E62">
-        <v>4840.58</v>
+        <v>4935.233</v>
       </c>
       <c r="F62">
-        <v>5679.18</v>
+        <v>5773.833000000001</v>
       </c>
       <c r="G62">
         <v>134.6</v>
@@ -6508,37 +6508,37 @@
         <v>390.4</v>
       </c>
       <c r="M62">
-        <v>1140.379344</v>
+        <v>1159.3856664</v>
       </c>
       <c r="N62">
-        <v>-749.9793440000002</v>
+        <v>-768.9856664000002</v>
       </c>
       <c r="O62">
-        <v>-209.9942163200001</v>
+        <v>-215.3159865920001</v>
       </c>
       <c r="P62">
-        <v>-539.9851276800001</v>
+        <v>-553.6696798080002</v>
       </c>
       <c r="Q62">
-        <v>-336.5851276800001</v>
+        <v>-350.2696798080002</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1047741497632492</v>
+        <v>0.1062863074494864</v>
       </c>
       <c r="T62">
-        <v>1.361989601922614</v>
+        <v>1.396912412228322</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.09585582251654673</v>
+        <v>0.09428441559004597</v>
       </c>
       <c r="W62">
-        <v>0.1815521508386774</v>
+        <v>0.1818676893495188</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3423422232733812</v>
+        <v>0.3367300556787355</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6554,22 +6554,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1523909504085061</v>
+        <v>0.1539409504085061</v>
       </c>
       <c r="C63">
-        <v>-2876.542712002079</v>
+        <v>-3007.194091408755</v>
       </c>
       <c r="D63">
-        <v>2762.690287997921</v>
+        <v>2726.691908591246</v>
       </c>
       <c r="E63">
-        <v>4935.233</v>
+        <v>5029.886</v>
       </c>
       <c r="F63">
-        <v>5773.833000000001</v>
+        <v>5868.486000000001</v>
       </c>
       <c r="G63">
         <v>134.6</v>
@@ -6590,37 +6590,37 @@
         <v>390.4</v>
       </c>
       <c r="M63">
-        <v>1159.3856664</v>
+        <v>1178.3919888</v>
       </c>
       <c r="N63">
-        <v>-768.9856664000002</v>
+        <v>-787.9919888000003</v>
       </c>
       <c r="O63">
-        <v>-215.3159865920001</v>
+        <v>-220.6377568640001</v>
       </c>
       <c r="P63">
-        <v>-553.6696798080002</v>
+        <v>-567.3542319360001</v>
       </c>
       <c r="Q63">
-        <v>-350.2696798080002</v>
+        <v>-363.9542319360002</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1062863074494864</v>
+        <v>0.1078780523823676</v>
       </c>
       <c r="T63">
-        <v>1.396912412228322</v>
+        <v>1.433673265181699</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.09428441559004597</v>
+        <v>0.09276369920956135</v>
       </c>
       <c r="W63">
-        <v>0.1818676893495188</v>
+        <v>0.1821730491987201</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3367300556787355</v>
+        <v>0.3312989257484333</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6636,22 +6636,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1539409504085061</v>
+        <v>0.1554909504085061</v>
       </c>
       <c r="C64">
-        <v>-3007.194091408755</v>
+        <v>-3136.919406165939</v>
       </c>
       <c r="D64">
-        <v>2726.691908591246</v>
+        <v>2691.619593834062</v>
       </c>
       <c r="E64">
-        <v>5029.886</v>
+        <v>5124.539000000001</v>
       </c>
       <c r="F64">
-        <v>5868.486000000001</v>
+        <v>5963.139000000001</v>
       </c>
       <c r="G64">
         <v>134.6</v>
@@ -6672,37 +6672,37 @@
         <v>390.4</v>
       </c>
       <c r="M64">
-        <v>1178.3919888</v>
+        <v>1197.3983112</v>
       </c>
       <c r="N64">
-        <v>-787.9919888000003</v>
+        <v>-806.9983112000003</v>
       </c>
       <c r="O64">
-        <v>-220.6377568640001</v>
+        <v>-225.9595271360001</v>
       </c>
       <c r="P64">
-        <v>-567.3542319360001</v>
+        <v>-581.0387840640002</v>
       </c>
       <c r="Q64">
-        <v>-363.9542319360002</v>
+        <v>-377.6387840640002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1078780523823676</v>
+        <v>0.109555837581891</v>
       </c>
       <c r="T64">
-        <v>1.433673265181699</v>
+        <v>1.472421191267691</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.09276369920956135</v>
+        <v>0.09129125953956831</v>
       </c>
       <c r="W64">
-        <v>0.1821730491987201</v>
+        <v>0.1824687150844547</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3312989257484333</v>
+        <v>0.3260402126413153</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6718,22 +6718,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1554909504085061</v>
+        <v>0.1570409504085061</v>
       </c>
       <c r="C65">
-        <v>-3136.919406165939</v>
+        <v>-3265.75393723346</v>
       </c>
       <c r="D65">
-        <v>2691.619593834062</v>
+        <v>2657.438062766541</v>
       </c>
       <c r="E65">
-        <v>5124.539000000001</v>
+        <v>5219.192</v>
       </c>
       <c r="F65">
-        <v>5963.139000000001</v>
+        <v>6057.792</v>
       </c>
       <c r="G65">
         <v>134.6</v>
@@ -6754,37 +6754,37 @@
         <v>390.4</v>
       </c>
       <c r="M65">
-        <v>1197.3983112</v>
+        <v>1216.4046336</v>
       </c>
       <c r="N65">
-        <v>-806.9983112000003</v>
+        <v>-826.0046336000001</v>
       </c>
       <c r="O65">
-        <v>-225.9595271360001</v>
+        <v>-231.2812974080001</v>
       </c>
       <c r="P65">
-        <v>-581.0387840640002</v>
+        <v>-594.723336192</v>
       </c>
       <c r="Q65">
-        <v>-377.6387840640002</v>
+        <v>-391.3233361920001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.109555837581891</v>
+        <v>0.1113268330702769</v>
       </c>
       <c r="T65">
-        <v>1.472421191267691</v>
+        <v>1.513321779914016</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.09129125953956831</v>
+        <v>0.08986483360926255</v>
       </c>
       <c r="W65">
-        <v>0.1824687150844547</v>
+        <v>0.1827551414112601</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3260402126413153</v>
+        <v>0.3209458343187949</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6800,22 +6800,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1570409504085061</v>
+        <v>0.1585909504085061</v>
       </c>
       <c r="C66">
-        <v>-3265.75393723346</v>
+        <v>-3393.731195878979</v>
       </c>
       <c r="D66">
-        <v>2657.438062766541</v>
+        <v>2624.113804121022</v>
       </c>
       <c r="E66">
-        <v>5219.192</v>
+        <v>5313.845</v>
       </c>
       <c r="F66">
-        <v>6057.792</v>
+        <v>6152.445000000001</v>
       </c>
       <c r="G66">
         <v>134.6</v>
@@ -6836,37 +6836,37 @@
         <v>390.4</v>
       </c>
       <c r="M66">
-        <v>1216.4046336</v>
+        <v>1235.410956</v>
       </c>
       <c r="N66">
-        <v>-826.0046336000001</v>
+        <v>-845.0109560000002</v>
       </c>
       <c r="O66">
-        <v>-231.2812974080001</v>
+        <v>-236.6030676800001</v>
       </c>
       <c r="P66">
-        <v>-594.723336192</v>
+        <v>-608.4078883200001</v>
       </c>
       <c r="Q66">
-        <v>-391.3233361920001</v>
+        <v>-405.0078883200001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1113268330702769</v>
+        <v>0.1131990283008562</v>
       </c>
       <c r="T66">
-        <v>1.513321779914016</v>
+        <v>1.556559545054416</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.08986483360926255</v>
+        <v>0.08848229770758159</v>
       </c>
       <c r="W66">
-        <v>0.1827551414112601</v>
+        <v>0.1830327546203176</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3209458343187949</v>
+        <v>0.3160082060985057</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6882,22 +6882,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1585909504085061</v>
+        <v>0.1601409504085061</v>
       </c>
       <c r="C67">
-        <v>-3393.731195878979</v>
+        <v>-3520.883033263441</v>
       </c>
       <c r="D67">
-        <v>2624.113804121022</v>
+        <v>2591.61496673656</v>
       </c>
       <c r="E67">
-        <v>5313.845</v>
+        <v>5408.498000000001</v>
       </c>
       <c r="F67">
-        <v>6152.445000000001</v>
+        <v>6247.098000000001</v>
       </c>
       <c r="G67">
         <v>134.6</v>
@@ -6918,37 +6918,37 @@
         <v>390.4</v>
       </c>
       <c r="M67">
-        <v>1235.410956</v>
+        <v>1254.4172784</v>
       </c>
       <c r="N67">
-        <v>-845.0109560000002</v>
+        <v>-864.0172784000002</v>
       </c>
       <c r="O67">
-        <v>-236.6030676800001</v>
+        <v>-241.9248379520001</v>
       </c>
       <c r="P67">
-        <v>-608.4078883200001</v>
+        <v>-622.0924404480002</v>
       </c>
       <c r="Q67">
-        <v>-405.0078883200001</v>
+        <v>-418.6924404480002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1131990283008562</v>
+        <v>0.1151813526626461</v>
       </c>
       <c r="T67">
-        <v>1.556559545054416</v>
+        <v>1.602340708144252</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.08848229770758159</v>
+        <v>0.08714165683322431</v>
       </c>
       <c r="W67">
-        <v>0.1830327546203176</v>
+        <v>0.1833019553078886</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3160082060985057</v>
+        <v>0.311220202975801</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6964,22 +6964,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1601409504085061</v>
+        <v>0.1616909504085061</v>
       </c>
       <c r="C68">
-        <v>-3520.883033263441</v>
+        <v>-3647.239741983045</v>
       </c>
       <c r="D68">
-        <v>2591.61496673656</v>
+        <v>2559.911258016956</v>
       </c>
       <c r="E68">
-        <v>5408.498000000001</v>
+        <v>5503.151000000001</v>
       </c>
       <c r="F68">
-        <v>6247.098000000001</v>
+        <v>6341.751000000001</v>
       </c>
       <c r="G68">
         <v>134.6</v>
@@ -7000,37 +7000,37 @@
         <v>390.4</v>
       </c>
       <c r="M68">
-        <v>1254.4172784</v>
+        <v>1273.4236008</v>
       </c>
       <c r="N68">
-        <v>-864.0172784000002</v>
+        <v>-883.0236008000003</v>
       </c>
       <c r="O68">
-        <v>-241.9248379520001</v>
+        <v>-247.2466082240001</v>
       </c>
       <c r="P68">
-        <v>-622.0924404480002</v>
+        <v>-635.7769925760001</v>
       </c>
       <c r="Q68">
-        <v>-418.6924404480002</v>
+        <v>-432.3769925760001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1151813526626461</v>
+        <v>0.1172838178948475</v>
       </c>
       <c r="T68">
-        <v>1.602340708144252</v>
+        <v>1.650896487178926</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.08714165683322431</v>
+        <v>0.08584103508944484</v>
       </c>
       <c r="W68">
-        <v>0.1833019553078886</v>
+        <v>0.1835631201540395</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.311220202975801</v>
+        <v>0.3065751253194458</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7046,22 +7046,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1616909504085061</v>
+        <v>0.1632409504085061</v>
       </c>
       <c r="C69">
-        <v>-3647.239741983045</v>
+        <v>-3772.830150248206</v>
       </c>
       <c r="D69">
-        <v>2559.911258016956</v>
+        <v>2528.973849751796</v>
       </c>
       <c r="E69">
-        <v>5503.151000000001</v>
+        <v>5597.804000000001</v>
       </c>
       <c r="F69">
-        <v>6341.751000000001</v>
+        <v>6436.404000000001</v>
       </c>
       <c r="G69">
         <v>134.6</v>
@@ -7082,37 +7082,37 @@
         <v>390.4</v>
       </c>
       <c r="M69">
-        <v>1273.4236008</v>
+        <v>1292.4299232</v>
       </c>
       <c r="N69">
-        <v>-883.0236008000003</v>
+        <v>-902.0299232000003</v>
       </c>
       <c r="O69">
-        <v>-247.2466082240001</v>
+        <v>-252.5683784960001</v>
       </c>
       <c r="P69">
-        <v>-635.7769925760001</v>
+        <v>-649.4615447040002</v>
       </c>
       <c r="Q69">
-        <v>-432.3769925760001</v>
+        <v>-446.0615447040002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1172838178948475</v>
+        <v>0.1195176872040615</v>
       </c>
       <c r="T69">
-        <v>1.650896487178926</v>
+        <v>1.702487002403268</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.08584103508944484</v>
+        <v>0.08457866692636475</v>
       </c>
       <c r="W69">
-        <v>0.1835631201540395</v>
+        <v>0.183816603681186</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3065751253194458</v>
+        <v>0.3020666675941598</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7128,22 +7128,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1632409504085061</v>
+        <v>0.1647909504085061</v>
       </c>
       <c r="C70">
-        <v>-3772.830150248206</v>
+        <v>-3897.681709314937</v>
       </c>
       <c r="D70">
-        <v>2528.973849751796</v>
+        <v>2498.775290685065</v>
       </c>
       <c r="E70">
-        <v>5597.804000000001</v>
+        <v>5692.457000000001</v>
       </c>
       <c r="F70">
-        <v>6436.404000000001</v>
+        <v>6531.057000000002</v>
       </c>
       <c r="G70">
         <v>134.6</v>
@@ -7164,37 +7164,37 @@
         <v>390.4</v>
       </c>
       <c r="M70">
-        <v>1292.4299232</v>
+        <v>1311.4362456</v>
       </c>
       <c r="N70">
-        <v>-902.0299232000003</v>
+        <v>-921.0362456000004</v>
       </c>
       <c r="O70">
-        <v>-252.5683784960001</v>
+        <v>-257.8901487680001</v>
       </c>
       <c r="P70">
-        <v>-649.4615447040002</v>
+        <v>-663.1460968320002</v>
       </c>
       <c r="Q70">
-        <v>-446.0615447040002</v>
+        <v>-459.7460968320003</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1195176872040615</v>
+        <v>0.1218956771138699</v>
       </c>
       <c r="T70">
-        <v>1.702487002403268</v>
+        <v>1.757405937964664</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.08457866692636475</v>
+        <v>0.08335288914482324</v>
       </c>
       <c r="W70">
-        <v>0.183816603681186</v>
+        <v>0.1840627398597195</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3020666675941598</v>
+        <v>0.2976888898029401</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7210,22 +7210,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1647909504085061</v>
+        <v>0.1663409504085061</v>
       </c>
       <c r="C71">
-        <v>-3897.681709314937</v>
+        <v>-4021.820574726044</v>
       </c>
       <c r="D71">
-        <v>2498.775290685065</v>
+        <v>2469.289425273957</v>
       </c>
       <c r="E71">
-        <v>5692.457000000001</v>
+        <v>5787.110000000001</v>
       </c>
       <c r="F71">
-        <v>6531.057000000002</v>
+        <v>6625.710000000001</v>
       </c>
       <c r="G71">
         <v>134.6</v>
@@ -7246,37 +7246,37 @@
         <v>390.4</v>
       </c>
       <c r="M71">
-        <v>1311.4362456</v>
+        <v>1330.442568</v>
       </c>
       <c r="N71">
-        <v>-921.0362456000004</v>
+        <v>-940.0425680000002</v>
       </c>
       <c r="O71">
-        <v>-257.8901487680001</v>
+        <v>-263.2119190400001</v>
       </c>
       <c r="P71">
-        <v>-663.1460968320002</v>
+        <v>-676.8306489600002</v>
       </c>
       <c r="Q71">
-        <v>-459.7460968320003</v>
+        <v>-473.4306489600002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1218956771138699</v>
+        <v>0.1244321996843323</v>
       </c>
       <c r="T71">
-        <v>1.757405937964664</v>
+        <v>1.815986135896819</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.08335288914482324</v>
+        <v>0.08216213358561149</v>
       </c>
       <c r="W71">
-        <v>0.1840627398597195</v>
+        <v>0.1843018435760092</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2976888898029401</v>
+        <v>0.2934361913771838</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7292,22 +7292,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1663409504085061</v>
+        <v>0.1678909504085061</v>
       </c>
       <c r="C72">
-        <v>-4021.820574726044</v>
+        <v>-4145.271681867445</v>
       </c>
       <c r="D72">
-        <v>2469.289425273957</v>
+        <v>2440.491318132556</v>
       </c>
       <c r="E72">
-        <v>5787.110000000001</v>
+        <v>5881.763000000001</v>
       </c>
       <c r="F72">
-        <v>6625.710000000001</v>
+        <v>6720.363000000001</v>
       </c>
       <c r="G72">
         <v>134.6</v>
@@ -7328,37 +7328,37 @@
         <v>390.4</v>
       </c>
       <c r="M72">
-        <v>1330.442568</v>
+        <v>1349.4488904</v>
       </c>
       <c r="N72">
-        <v>-940.0425680000002</v>
+        <v>-959.0488904000002</v>
       </c>
       <c r="O72">
-        <v>-263.2119190400001</v>
+        <v>-268.5336893120001</v>
       </c>
       <c r="P72">
-        <v>-676.8306489600002</v>
+        <v>-690.5152010880001</v>
       </c>
       <c r="Q72">
-        <v>-473.4306489600002</v>
+        <v>-487.1152010880002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1244321996843323</v>
+        <v>0.127143654845861</v>
       </c>
       <c r="T72">
-        <v>1.815986135896819</v>
+        <v>1.878606347479468</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.08216213358561149</v>
+        <v>0.08100492043651837</v>
       </c>
       <c r="W72">
-        <v>0.1843018435760092</v>
+        <v>0.1845342119763471</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2934361913771838</v>
+        <v>0.2893032872732798</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7374,22 +7374,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1678909504085062</v>
+        <v>0.1694409504085061</v>
       </c>
       <c r="C73">
-        <v>-4145.271681867445</v>
+        <v>-4268.058816298388</v>
       </c>
       <c r="D73">
-        <v>2440.491318132556</v>
+        <v>2412.357183701613</v>
       </c>
       <c r="E73">
-        <v>5881.763</v>
+        <v>5976.416</v>
       </c>
       <c r="F73">
-        <v>6720.363</v>
+        <v>6815.016000000001</v>
       </c>
       <c r="G73">
         <v>134.6</v>
@@ -7410,37 +7410,37 @@
         <v>390.4</v>
       </c>
       <c r="M73">
-        <v>1349.4488904</v>
+        <v>1368.4552128</v>
       </c>
       <c r="N73">
-        <v>-959.0488904000002</v>
+        <v>-978.0552128000003</v>
       </c>
       <c r="O73">
-        <v>-268.5336893120001</v>
+        <v>-273.8554595840001</v>
       </c>
       <c r="P73">
-        <v>-690.5152010880001</v>
+        <v>-704.1997532160001</v>
       </c>
       <c r="Q73">
-        <v>-487.1152010880002</v>
+        <v>-500.7997532160001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.127143654845861</v>
+        <v>0.1300487853760703</v>
       </c>
       <c r="T73">
-        <v>1.878606347479468</v>
+        <v>1.94569943131802</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.08100492043651837</v>
+        <v>0.07987985209712227</v>
       </c>
       <c r="W73">
-        <v>0.1845342119763471</v>
+        <v>0.1847601256988979</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2893032872732798</v>
+        <v>0.2852851860611509</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7456,22 +7456,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1694409504085061</v>
+        <v>0.1709909504085061</v>
       </c>
       <c r="C74">
-        <v>-4268.058816298388</v>
+        <v>-4390.204679272492</v>
       </c>
       <c r="D74">
-        <v>2412.357183701613</v>
+        <v>2384.864320727508</v>
       </c>
       <c r="E74">
-        <v>5976.416</v>
+        <v>6071.069</v>
       </c>
       <c r="F74">
-        <v>6815.016000000001</v>
+        <v>6909.669000000001</v>
       </c>
       <c r="G74">
         <v>134.6</v>
@@ -7492,37 +7492,37 @@
         <v>390.4</v>
       </c>
       <c r="M74">
-        <v>1368.4552128</v>
+        <v>1387.4615352</v>
       </c>
       <c r="N74">
-        <v>-978.0552128000003</v>
+        <v>-997.0615352000003</v>
       </c>
       <c r="O74">
-        <v>-273.8554595840001</v>
+        <v>-279.1772298560001</v>
       </c>
       <c r="P74">
-        <v>-704.1997532160001</v>
+        <v>-717.8843053440003</v>
       </c>
       <c r="Q74">
-        <v>-500.7997532160001</v>
+        <v>-514.4843053440003</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1300487853760703</v>
+        <v>0.1331691107603692</v>
       </c>
       <c r="T74">
-        <v>1.94569943131802</v>
+        <v>2.017762373218687</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.07987985209712227</v>
+        <v>0.07878560754784662</v>
       </c>
       <c r="W74">
-        <v>0.1847601256988979</v>
+        <v>0.1849798500043924</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2852851860611509</v>
+        <v>0.2813771698137379</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7538,22 +7538,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1709909504085061</v>
+        <v>0.1725409504085061</v>
       </c>
       <c r="C75">
-        <v>-4390.204679272492</v>
+        <v>-4511.730948828927</v>
       </c>
       <c r="D75">
-        <v>2384.864320727508</v>
+        <v>2357.991051171075</v>
       </c>
       <c r="E75">
-        <v>6071.069</v>
+        <v>6165.722000000001</v>
       </c>
       <c r="F75">
-        <v>6909.669000000001</v>
+        <v>7004.322000000001</v>
       </c>
       <c r="G75">
         <v>134.6</v>
@@ -7574,37 +7574,37 @@
         <v>390.4</v>
       </c>
       <c r="M75">
-        <v>1387.4615352</v>
+        <v>1406.4678576</v>
       </c>
       <c r="N75">
-        <v>-997.0615352000003</v>
+        <v>-1016.0678576</v>
       </c>
       <c r="O75">
-        <v>-279.1772298560001</v>
+        <v>-284.4990001280001</v>
       </c>
       <c r="P75">
-        <v>-717.8843053440003</v>
+        <v>-731.5688574720002</v>
       </c>
       <c r="Q75">
-        <v>-514.4843053440003</v>
+        <v>-528.1688574720002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1331691107603692</v>
+        <v>0.1365294611742295</v>
       </c>
       <c r="T75">
-        <v>2.017762373218687</v>
+        <v>2.095368618342483</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.07878560754784662</v>
+        <v>0.07772093717557843</v>
       </c>
       <c r="W75">
-        <v>0.1849798500043924</v>
+        <v>0.1851936358151438</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2813771698137379</v>
+        <v>0.2775747756270658</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7620,22 +7620,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1725409504085061</v>
+        <v>0.1740909504085061</v>
       </c>
       <c r="C76">
-        <v>-4511.730948828927</v>
+        <v>-4632.658336799266</v>
       </c>
       <c r="D76">
-        <v>2357.991051171075</v>
+        <v>2331.716663200734</v>
       </c>
       <c r="E76">
-        <v>6165.722000000001</v>
+        <v>6260.375</v>
       </c>
       <c r="F76">
-        <v>7004.322000000001</v>
+        <v>7098.975</v>
       </c>
       <c r="G76">
         <v>134.6</v>
@@ -7656,37 +7656,37 @@
         <v>390.4</v>
       </c>
       <c r="M76">
-        <v>1406.4678576</v>
+        <v>1425.47418</v>
       </c>
       <c r="N76">
-        <v>-1016.0678576</v>
+        <v>-1035.07418</v>
       </c>
       <c r="O76">
-        <v>-284.4990001280001</v>
+        <v>-289.8207704000001</v>
       </c>
       <c r="P76">
-        <v>-731.5688574720002</v>
+        <v>-745.2534095999999</v>
       </c>
       <c r="Q76">
-        <v>-528.1688574720002</v>
+        <v>-541.8534096</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1365294611742295</v>
+        <v>0.1401586396211987</v>
       </c>
       <c r="T76">
-        <v>2.095368618342483</v>
+        <v>2.179183363076183</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.07772093717557843</v>
+        <v>0.07668465801323739</v>
       </c>
       <c r="W76">
-        <v>0.1851936358151438</v>
+        <v>0.1854017206709419</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2775747756270658</v>
+        <v>0.273873778618705</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7702,22 +7702,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1740909504085061</v>
+        <v>0.1756409504085061</v>
       </c>
       <c r="C77">
-        <v>-4632.658336799266</v>
+        <v>-4753.006642045108</v>
       </c>
       <c r="D77">
-        <v>2331.716663200734</v>
+        <v>2306.021357954893</v>
       </c>
       <c r="E77">
-        <v>6260.375</v>
+        <v>6355.028</v>
       </c>
       <c r="F77">
-        <v>7098.975</v>
+        <v>7193.628000000001</v>
       </c>
       <c r="G77">
         <v>134.6</v>
@@ -7738,37 +7738,37 @@
         <v>390.4</v>
       </c>
       <c r="M77">
-        <v>1425.47418</v>
+        <v>1444.4805024</v>
       </c>
       <c r="N77">
-        <v>-1035.07418</v>
+        <v>-1054.0805024</v>
       </c>
       <c r="O77">
-        <v>-289.8207704000001</v>
+        <v>-295.1425406720001</v>
       </c>
       <c r="P77">
-        <v>-745.2534095999999</v>
+        <v>-758.9379617280001</v>
       </c>
       <c r="Q77">
-        <v>-541.8534096</v>
+        <v>-555.5379617280001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1401586396211987</v>
+        <v>0.1440902496054153</v>
       </c>
       <c r="T77">
-        <v>2.179183363076183</v>
+        <v>2.269982669871024</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.07668465801323739</v>
+        <v>0.07567564935516846</v>
       </c>
       <c r="W77">
-        <v>0.1854017206709419</v>
+        <v>0.1856043296094822</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.273873778618705</v>
+        <v>0.2702701762684588</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7784,22 +7784,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1756409504085061</v>
+        <v>0.1771909504085061</v>
       </c>
       <c r="C78">
-        <v>-4753.006642045108</v>
+        <v>-4872.794800213973</v>
       </c>
       <c r="D78">
-        <v>2306.021357954893</v>
+        <v>2280.886199786029</v>
       </c>
       <c r="E78">
-        <v>6355.028</v>
+        <v>6449.681</v>
       </c>
       <c r="F78">
-        <v>7193.628000000001</v>
+        <v>7288.281000000001</v>
       </c>
       <c r="G78">
         <v>134.6</v>
@@ -7820,37 +7820,37 @@
         <v>390.4</v>
       </c>
       <c r="M78">
-        <v>1444.4805024</v>
+        <v>1463.4868248</v>
       </c>
       <c r="N78">
-        <v>-1054.0805024</v>
+        <v>-1073.0868248</v>
       </c>
       <c r="O78">
-        <v>-295.1425406720001</v>
+        <v>-300.4643109440001</v>
       </c>
       <c r="P78">
-        <v>-758.9379617280001</v>
+        <v>-772.6225138560001</v>
       </c>
       <c r="Q78">
-        <v>-555.5379617280001</v>
+        <v>-569.2225138560001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1440902496054153</v>
+        <v>0.1483637387186943</v>
       </c>
       <c r="T78">
-        <v>2.269982669871024</v>
+        <v>2.368677568561068</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.07567564935516846</v>
+        <v>0.07469284871419227</v>
       </c>
       <c r="W78">
-        <v>0.1856043296094822</v>
+        <v>0.1858016759781902</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2702701762684588</v>
+        <v>0.2667601739792581</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7866,22 +7866,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1771909504085061</v>
+        <v>0.1787409504085061</v>
       </c>
       <c r="C79">
-        <v>-4872.794800213973</v>
+        <v>-4992.040930276355</v>
       </c>
       <c r="D79">
-        <v>2280.886199786029</v>
+        <v>2256.293069723646</v>
       </c>
       <c r="E79">
-        <v>6449.681</v>
+        <v>6544.334000000001</v>
       </c>
       <c r="F79">
-        <v>7288.281000000001</v>
+        <v>7382.934000000001</v>
       </c>
       <c r="G79">
         <v>134.6</v>
@@ -7902,37 +7902,37 @@
         <v>390.4</v>
       </c>
       <c r="M79">
-        <v>1463.4868248</v>
+        <v>1482.4931472</v>
       </c>
       <c r="N79">
-        <v>-1073.0868248</v>
+        <v>-1092.0931472</v>
       </c>
       <c r="O79">
-        <v>-300.4643109440001</v>
+        <v>-305.7860812160001</v>
       </c>
       <c r="P79">
-        <v>-772.6225138560001</v>
+        <v>-786.3070659840001</v>
       </c>
       <c r="Q79">
-        <v>-569.2225138560001</v>
+        <v>-582.9070659840002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1483637387186943</v>
+        <v>0.1530257268422713</v>
       </c>
       <c r="T79">
-        <v>2.368677568561068</v>
+        <v>2.47634473076839</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.07469284871419227</v>
+        <v>0.07373524808965133</v>
       </c>
       <c r="W79">
-        <v>0.1858016759781902</v>
+        <v>0.185993962183598</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2667601739792581</v>
+        <v>0.2633401717487548</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7948,22 +7948,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1787409504085061</v>
+        <v>0.1802909504085061</v>
       </c>
       <c r="C80">
-        <v>-4992.040930276355</v>
+        <v>-5110.762378084219</v>
       </c>
       <c r="D80">
-        <v>2256.293069723646</v>
+        <v>2232.224621915783</v>
       </c>
       <c r="E80">
-        <v>6544.334000000001</v>
+        <v>6638.987000000001</v>
       </c>
       <c r="F80">
-        <v>7382.934000000001</v>
+        <v>7477.587000000001</v>
       </c>
       <c r="G80">
         <v>134.6</v>
@@ -7984,37 +7984,37 @@
         <v>390.4</v>
       </c>
       <c r="M80">
-        <v>1482.4931472</v>
+        <v>1501.4994696</v>
       </c>
       <c r="N80">
-        <v>-1092.0931472</v>
+        <v>-1111.0994696</v>
       </c>
       <c r="O80">
-        <v>-305.7860812160001</v>
+        <v>-311.1078514880001</v>
       </c>
       <c r="P80">
-        <v>-786.3070659840001</v>
+        <v>-799.9916181120002</v>
       </c>
       <c r="Q80">
-        <v>-582.9070659840002</v>
+        <v>-596.5916181120002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1530257268422713</v>
+        <v>0.1581317138347604</v>
       </c>
       <c r="T80">
-        <v>2.47634473076839</v>
+        <v>2.594265908424027</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.07373524808965133</v>
+        <v>0.07280189051889624</v>
       </c>
       <c r="W80">
-        <v>0.185993962183598</v>
+        <v>0.1861813803838056</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2633401717487548</v>
+        <v>0.2600067518532009</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8030,22 +8030,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1802909504085061</v>
+        <v>0.1818409504085061</v>
       </c>
       <c r="C81">
-        <v>-5110.762378084219</v>
+        <v>-5228.975757171025</v>
       </c>
       <c r="D81">
-        <v>2232.224621915783</v>
+        <v>2208.664242828976</v>
       </c>
       <c r="E81">
-        <v>6638.987000000001</v>
+        <v>6733.640000000001</v>
       </c>
       <c r="F81">
-        <v>7477.587000000001</v>
+        <v>7572.240000000002</v>
       </c>
       <c r="G81">
         <v>134.6</v>
@@ -8066,37 +8066,37 @@
         <v>390.4</v>
       </c>
       <c r="M81">
-        <v>1501.4994696</v>
+        <v>1520.505792</v>
       </c>
       <c r="N81">
-        <v>-1111.0994696</v>
+        <v>-1130.105792</v>
       </c>
       <c r="O81">
-        <v>-311.1078514880001</v>
+        <v>-316.4296217600001</v>
       </c>
       <c r="P81">
-        <v>-799.9916181120002</v>
+        <v>-813.6761702400001</v>
       </c>
       <c r="Q81">
-        <v>-596.5916181120002</v>
+        <v>-610.2761702400002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1581317138347604</v>
+        <v>0.1637482995264984</v>
       </c>
       <c r="T81">
-        <v>2.594265908424027</v>
+        <v>2.723979203845229</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.07280189051889624</v>
+        <v>0.07189186688741005</v>
       </c>
       <c r="W81">
-        <v>0.1861813803838056</v>
+        <v>0.1863641131290081</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2600067518532009</v>
+        <v>0.2567566674550359</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8112,22 +8112,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1818409504085061</v>
+        <v>0.1833909504085061</v>
       </c>
       <c r="C82">
-        <v>-5228.975757171025</v>
+        <v>-5346.696986994966</v>
       </c>
       <c r="D82">
-        <v>2208.664242828976</v>
+        <v>2185.596013005035</v>
       </c>
       <c r="E82">
-        <v>6733.640000000001</v>
+        <v>6828.293000000001</v>
       </c>
       <c r="F82">
-        <v>7572.240000000002</v>
+        <v>7666.893000000001</v>
       </c>
       <c r="G82">
         <v>134.6</v>
@@ -8148,37 +8148,37 @@
         <v>390.4</v>
       </c>
       <c r="M82">
-        <v>1520.505792</v>
+        <v>1539.5121144</v>
       </c>
       <c r="N82">
-        <v>-1130.105792</v>
+        <v>-1149.1121144</v>
       </c>
       <c r="O82">
-        <v>-316.4296217600001</v>
+        <v>-321.7513920320001</v>
       </c>
       <c r="P82">
-        <v>-813.6761702400001</v>
+        <v>-827.3607223680002</v>
       </c>
       <c r="Q82">
-        <v>-610.2761702400002</v>
+        <v>-623.9607223680002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1637482995264984</v>
+        <v>0.1699561047647352</v>
       </c>
       <c r="T82">
-        <v>2.723979203845229</v>
+        <v>2.867346530363399</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.07189186688741005</v>
+        <v>0.07100431297521979</v>
       </c>
       <c r="W82">
-        <v>0.1863641131290081</v>
+        <v>0.1865423339545759</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2567566674550359</v>
+        <v>0.2535868320543563</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8194,22 +8194,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1833909504085061</v>
+        <v>0.1849409504085062</v>
       </c>
       <c r="C83">
-        <v>-5346.696986994966</v>
+        <v>-5463.941328810393</v>
       </c>
       <c r="D83">
-        <v>2185.596013005035</v>
+        <v>2163.004671189608</v>
       </c>
       <c r="E83">
-        <v>6828.293000000001</v>
+        <v>6922.946000000001</v>
       </c>
       <c r="F83">
-        <v>7666.893000000001</v>
+        <v>7761.546000000001</v>
       </c>
       <c r="G83">
         <v>134.6</v>
@@ -8230,37 +8230,37 @@
         <v>390.4</v>
       </c>
       <c r="M83">
-        <v>1539.5121144</v>
+        <v>1558.5184368</v>
       </c>
       <c r="N83">
-        <v>-1149.1121144</v>
+        <v>-1168.1184368</v>
       </c>
       <c r="O83">
-        <v>-321.7513920320001</v>
+        <v>-327.0731623040002</v>
       </c>
       <c r="P83">
-        <v>-827.3607223680002</v>
+        <v>-841.0452744960003</v>
       </c>
       <c r="Q83">
-        <v>-623.9607223680002</v>
+        <v>-637.6452744960003</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1699561047647352</v>
+        <v>0.1768536661405538</v>
       </c>
       <c r="T83">
-        <v>2.867346530363399</v>
+        <v>3.026643559828032</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.07100431297521979</v>
+        <v>0.07013840671942442</v>
       </c>
       <c r="W83">
-        <v>0.1865423339545759</v>
+        <v>0.1867162079307396</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2535868320543563</v>
+        <v>0.2504943097122301</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8276,22 +8276,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1849409504085062</v>
+        <v>0.1864909504085061</v>
       </c>
       <c r="C84">
-        <v>-5463.941328810393</v>
+        <v>-5580.723419337306</v>
       </c>
       <c r="D84">
-        <v>2163.004671189608</v>
+        <v>2140.875580662695</v>
       </c>
       <c r="E84">
-        <v>6922.946000000001</v>
+        <v>7017.599000000001</v>
       </c>
       <c r="F84">
-        <v>7761.546000000001</v>
+        <v>7856.199000000001</v>
       </c>
       <c r="G84">
         <v>134.6</v>
@@ -8312,37 +8312,37 @@
         <v>390.4</v>
       </c>
       <c r="M84">
-        <v>1558.5184368</v>
+        <v>1577.5247592</v>
       </c>
       <c r="N84">
-        <v>-1168.1184368</v>
+        <v>-1187.1247592</v>
       </c>
       <c r="O84">
-        <v>-327.0731623040002</v>
+        <v>-332.3949325760001</v>
       </c>
       <c r="P84">
-        <v>-841.0452744960003</v>
+        <v>-854.7298266240002</v>
       </c>
       <c r="Q84">
-        <v>-637.6452744960003</v>
+        <v>-651.3298266240002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1768536661405538</v>
+        <v>0.1845627053252923</v>
       </c>
       <c r="T84">
-        <v>3.026643559828032</v>
+        <v>3.204681416288505</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.07013840671942442</v>
+        <v>0.0692933656746121</v>
       </c>
       <c r="W84">
-        <v>0.1867162079307396</v>
+        <v>0.1868858921725379</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2504943097122301</v>
+        <v>0.2474763059807573</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8358,22 +8358,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1864909504085061</v>
+        <v>0.1880409504085062</v>
       </c>
       <c r="C85">
-        <v>-5580.723419337306</v>
+        <v>-5697.057302385001</v>
       </c>
       <c r="D85">
-        <v>2140.875580662695</v>
+        <v>2119.194697615001</v>
       </c>
       <c r="E85">
-        <v>7017.599000000001</v>
+        <v>7112.252000000001</v>
       </c>
       <c r="F85">
-        <v>7856.199000000001</v>
+        <v>7950.852000000002</v>
       </c>
       <c r="G85">
         <v>134.6</v>
@@ -8394,37 +8394,37 @@
         <v>390.4</v>
       </c>
       <c r="M85">
-        <v>1577.5247592</v>
+        <v>1596.5310816</v>
       </c>
       <c r="N85">
-        <v>-1187.1247592</v>
+        <v>-1206.1310816</v>
       </c>
       <c r="O85">
-        <v>-332.3949325760001</v>
+        <v>-337.7167028480002</v>
       </c>
       <c r="P85">
-        <v>-854.7298266240002</v>
+        <v>-868.4143787520003</v>
       </c>
       <c r="Q85">
-        <v>-651.3298266240002</v>
+        <v>-665.0143787520003</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1845627053252923</v>
+        <v>0.1932353744081231</v>
       </c>
       <c r="T85">
-        <v>3.204681416288505</v>
+        <v>3.404974004806537</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.0692933656746121</v>
+        <v>0.06846844465467623</v>
       </c>
       <c r="W85">
-        <v>0.1868858921725379</v>
+        <v>0.187051536313341</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2474763059807573</v>
+        <v>0.2445301594809864</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8440,22 +8440,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1880409504085061</v>
+        <v>0.1895909504085062</v>
       </c>
       <c r="C86">
-        <v>-5697.057302385</v>
+        <v>-5812.956458573428</v>
       </c>
       <c r="D86">
-        <v>2119.194697615001</v>
+        <v>2097.948541426573</v>
       </c>
       <c r="E86">
-        <v>7112.252</v>
+        <v>7206.905000000001</v>
       </c>
       <c r="F86">
-        <v>7950.852000000001</v>
+        <v>8045.505000000001</v>
       </c>
       <c r="G86">
         <v>134.6</v>
@@ -8476,37 +8476,37 @@
         <v>390.4</v>
       </c>
       <c r="M86">
-        <v>1596.5310816</v>
+        <v>1615.537404</v>
       </c>
       <c r="N86">
-        <v>-1206.1310816</v>
+        <v>-1225.137404</v>
       </c>
       <c r="O86">
-        <v>-337.716702848</v>
+        <v>-343.03847312</v>
       </c>
       <c r="P86">
-        <v>-868.4143787519999</v>
+        <v>-882.09893088</v>
       </c>
       <c r="Q86">
-        <v>-665.014378752</v>
+        <v>-678.69893088</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.193235374408123</v>
+        <v>0.2030643993686645</v>
       </c>
       <c r="T86">
-        <v>3.404974004806535</v>
+        <v>3.631972271793637</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.06846844465467625</v>
+        <v>0.06766293354109182</v>
       </c>
       <c r="W86">
-        <v>0.187051536313341</v>
+        <v>0.1872132829449488</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2445301594809867</v>
+        <v>0.241653334075328</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8522,22 +8522,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1895909504085062</v>
+        <v>0.1911409504085061</v>
       </c>
       <c r="C87">
-        <v>-5812.956458573428</v>
+        <v>-5928.433833284475</v>
       </c>
       <c r="D87">
-        <v>2097.948541426573</v>
+        <v>2077.124166715527</v>
       </c>
       <c r="E87">
-        <v>7206.905000000001</v>
+        <v>7301.558000000001</v>
       </c>
       <c r="F87">
-        <v>8045.505000000001</v>
+        <v>8140.158000000001</v>
       </c>
       <c r="G87">
         <v>134.6</v>
@@ -8558,37 +8558,37 @@
         <v>390.4</v>
       </c>
       <c r="M87">
-        <v>1615.537404</v>
+        <v>1634.5437264</v>
       </c>
       <c r="N87">
-        <v>-1225.137404</v>
+        <v>-1244.1437264</v>
       </c>
       <c r="O87">
-        <v>-343.03847312</v>
+        <v>-348.3602433920001</v>
       </c>
       <c r="P87">
-        <v>-882.09893088</v>
+        <v>-895.7834830080001</v>
       </c>
       <c r="Q87">
-        <v>-678.69893088</v>
+        <v>-692.3834830080001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2030643993686645</v>
+        <v>0.2142975707521406</v>
       </c>
       <c r="T87">
-        <v>3.631972271793637</v>
+        <v>3.89139886263604</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.06766293354109182</v>
+        <v>0.06687615524410237</v>
       </c>
       <c r="W87">
-        <v>0.1872132829449488</v>
+        <v>0.1873712680269843</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.241653334075328</v>
+        <v>0.2388434115860799</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8604,22 +8604,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1911409504085061</v>
+        <v>0.1926909504085061</v>
       </c>
       <c r="C88">
-        <v>-5928.433833284475</v>
+        <v>-6043.501862964909</v>
       </c>
       <c r="D88">
-        <v>2077.124166715527</v>
+        <v>2056.709137035092</v>
       </c>
       <c r="E88">
-        <v>7301.558000000001</v>
+        <v>7396.211000000001</v>
       </c>
       <c r="F88">
-        <v>8140.158000000001</v>
+        <v>8234.811000000002</v>
       </c>
       <c r="G88">
         <v>134.6</v>
@@ -8640,37 +8640,37 @@
         <v>390.4</v>
       </c>
       <c r="M88">
-        <v>1634.5437264</v>
+        <v>1653.5500488</v>
       </c>
       <c r="N88">
-        <v>-1244.1437264</v>
+        <v>-1263.150048800001</v>
       </c>
       <c r="O88">
-        <v>-348.3602433920001</v>
+        <v>-353.6820136640002</v>
       </c>
       <c r="P88">
-        <v>-895.7834830080001</v>
+        <v>-909.4680351360005</v>
       </c>
       <c r="Q88">
-        <v>-692.3834830080001</v>
+        <v>-706.0680351360005</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2142975707521406</v>
+        <v>0.2272589223484591</v>
       </c>
       <c r="T88">
-        <v>3.89139886263604</v>
+        <v>4.190737236684966</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.06687615524410237</v>
+        <v>0.06610746380451497</v>
       </c>
       <c r="W88">
-        <v>0.1873712680269843</v>
+        <v>0.1875256212680534</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2388434115860799</v>
+        <v>0.2360980850161248</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8686,22 +8686,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1926909504085061</v>
+        <v>0.1942409504085061</v>
       </c>
       <c r="C89">
-        <v>-6043.501862964909</v>
+        <v>-6158.172499893335</v>
       </c>
       <c r="D89">
-        <v>2056.709137035092</v>
+        <v>2036.691500106667</v>
       </c>
       <c r="E89">
-        <v>7396.211000000001</v>
+        <v>7490.864000000001</v>
       </c>
       <c r="F89">
-        <v>8234.811000000002</v>
+        <v>8329.464000000002</v>
       </c>
       <c r="G89">
         <v>134.6</v>
@@ -8722,37 +8722,37 @@
         <v>390.4</v>
       </c>
       <c r="M89">
-        <v>1653.5500488</v>
+        <v>1672.556371200001</v>
       </c>
       <c r="N89">
-        <v>-1263.150048800001</v>
+        <v>-1282.156371200001</v>
       </c>
       <c r="O89">
-        <v>-353.6820136640002</v>
+        <v>-359.0037839360002</v>
       </c>
       <c r="P89">
-        <v>-909.4680351360005</v>
+        <v>-923.1525872640004</v>
       </c>
       <c r="Q89">
-        <v>-706.0680351360005</v>
+        <v>-719.7525872640005</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2272589223484591</v>
+        <v>0.2423804992108307</v>
       </c>
       <c r="T89">
-        <v>4.190737236684966</v>
+        <v>4.539965339742047</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.06610746380451497</v>
+        <v>0.06535624262491821</v>
       </c>
       <c r="W89">
-        <v>0.1875256212680534</v>
+        <v>0.1876764664809164</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2360980850161248</v>
+        <v>0.2334151522318507</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8768,22 +8768,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1942409504085061</v>
+        <v>0.1957909504085061</v>
       </c>
       <c r="C90">
-        <v>-6158.172499893335</v>
+        <v>-6272.457235514737</v>
       </c>
       <c r="D90">
-        <v>2036.691500106667</v>
+        <v>2017.059764485263</v>
       </c>
       <c r="E90">
-        <v>7490.864000000001</v>
+        <v>7585.517</v>
       </c>
       <c r="F90">
-        <v>8329.464000000002</v>
+        <v>8424.117</v>
       </c>
       <c r="G90">
         <v>134.6</v>
@@ -8804,37 +8804,37 @@
         <v>390.4</v>
       </c>
       <c r="M90">
-        <v>1672.556371200001</v>
+        <v>1691.5626936</v>
       </c>
       <c r="N90">
-        <v>-1282.156371200001</v>
+        <v>-1301.1626936</v>
       </c>
       <c r="O90">
-        <v>-359.0037839360002</v>
+        <v>-364.3255542080001</v>
       </c>
       <c r="P90">
-        <v>-923.1525872640004</v>
+        <v>-936.8371393920002</v>
       </c>
       <c r="Q90">
-        <v>-719.7525872640005</v>
+        <v>-733.4371393920002</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2423804992108307</v>
+        <v>0.2602514536845426</v>
       </c>
       <c r="T90">
-        <v>4.539965339742047</v>
+        <v>4.95268946153678</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.06535624262491821</v>
+        <v>0.06462190282014386</v>
       </c>
       <c r="W90">
-        <v>0.1876764664809164</v>
+        <v>0.1878239219137151</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2334151522318507</v>
+        <v>0.2307925100719423</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8850,22 +8850,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1957909504085061</v>
+        <v>0.1973409504085061</v>
       </c>
       <c r="C91">
-        <v>-6272.457235514737</v>
+        <v>-6386.367122438415</v>
       </c>
       <c r="D91">
-        <v>2017.059764485263</v>
+        <v>1997.802877561585</v>
       </c>
       <c r="E91">
-        <v>7585.517</v>
+        <v>7680.17</v>
       </c>
       <c r="F91">
-        <v>8424.117</v>
+        <v>8518.77</v>
       </c>
       <c r="G91">
         <v>134.6</v>
@@ -8886,37 +8886,37 @@
         <v>390.4</v>
       </c>
       <c r="M91">
-        <v>1691.5626936</v>
+        <v>1710.569016</v>
       </c>
       <c r="N91">
-        <v>-1301.1626936</v>
+        <v>-1320.169016</v>
       </c>
       <c r="O91">
-        <v>-364.3255542080001</v>
+        <v>-369.6473244800001</v>
       </c>
       <c r="P91">
-        <v>-936.8371393920002</v>
+        <v>-950.5216915200001</v>
       </c>
       <c r="Q91">
-        <v>-733.4371393920002</v>
+        <v>-747.1216915200001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2602514536845426</v>
+        <v>0.2816965990529969</v>
       </c>
       <c r="T91">
-        <v>4.95268946153678</v>
+        <v>5.447958407690458</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.06462190282014386</v>
+        <v>0.06390388167769782</v>
       </c>
       <c r="W91">
-        <v>0.1878239219137151</v>
+        <v>0.1879681005591183</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2307925100719423</v>
+        <v>0.2282281488489207</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8932,22 +8932,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1973409504085061</v>
+        <v>0.1988909504085061</v>
       </c>
       <c r="C92">
-        <v>-6386.367122438415</v>
+        <v>-6499.912795187706</v>
       </c>
       <c r="D92">
-        <v>1997.802877561585</v>
+        <v>1978.910204812294</v>
       </c>
       <c r="E92">
-        <v>7680.17</v>
+        <v>7774.823</v>
       </c>
       <c r="F92">
-        <v>8518.77</v>
+        <v>8613.423000000001</v>
       </c>
       <c r="G92">
         <v>134.6</v>
@@ -8968,37 +8968,37 @@
         <v>390.4</v>
       </c>
       <c r="M92">
-        <v>1710.569016</v>
+        <v>1729.5753384</v>
       </c>
       <c r="N92">
-        <v>-1320.169016</v>
+        <v>-1339.1753384</v>
       </c>
       <c r="O92">
-        <v>-369.6473244800001</v>
+        <v>-374.9690947520001</v>
       </c>
       <c r="P92">
-        <v>-950.5216915200001</v>
+        <v>-964.2062436480003</v>
       </c>
       <c r="Q92">
-        <v>-747.1216915200001</v>
+        <v>-760.8062436480003</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2816965990529969</v>
+        <v>0.3079073322811076</v>
       </c>
       <c r="T92">
-        <v>5.447958407690458</v>
+        <v>6.053287119656064</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.06390388167769782</v>
+        <v>0.06320164121970114</v>
       </c>
       <c r="W92">
-        <v>0.1879681005591183</v>
+        <v>0.188109110443084</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2282281488489207</v>
+        <v>0.2257201472132183</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9014,22 +9014,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1988909504085061</v>
+        <v>0.2004409504085062</v>
       </c>
       <c r="C93">
-        <v>-6499.912795187706</v>
+        <v>-6613.104489783423</v>
       </c>
       <c r="D93">
-        <v>1978.910204812294</v>
+        <v>1960.371510216578</v>
       </c>
       <c r="E93">
-        <v>7774.823</v>
+        <v>7869.476000000001</v>
       </c>
       <c r="F93">
-        <v>8613.423000000001</v>
+        <v>8708.076000000001</v>
       </c>
       <c r="G93">
         <v>134.6</v>
@@ -9050,37 +9050,37 @@
         <v>390.4</v>
       </c>
       <c r="M93">
-        <v>1729.5753384</v>
+        <v>1748.5816608</v>
       </c>
       <c r="N93">
-        <v>-1339.1753384</v>
+        <v>-1358.1816608</v>
       </c>
       <c r="O93">
-        <v>-374.9690947520001</v>
+        <v>-380.2908650240001</v>
       </c>
       <c r="P93">
-        <v>-964.2062436480003</v>
+        <v>-977.8907957760002</v>
       </c>
       <c r="Q93">
-        <v>-760.8062436480003</v>
+        <v>-774.4907957760003</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3079073322811076</v>
+        <v>0.3406707488162461</v>
       </c>
       <c r="T93">
-        <v>6.053287119656064</v>
+        <v>6.809948009613074</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.06320164121970114</v>
+        <v>0.06251466685861744</v>
       </c>
       <c r="W93">
-        <v>0.188109110443084</v>
+        <v>0.1882470548947896</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2257201472132183</v>
+        <v>0.223266667352205</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9096,22 +9096,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2004409504085062</v>
+        <v>0.2019909504085061</v>
       </c>
       <c r="C94">
-        <v>-6613.104489783423</v>
+        <v>-6725.952062236724</v>
       </c>
       <c r="D94">
-        <v>1960.371510216578</v>
+        <v>1942.176937763277</v>
       </c>
       <c r="E94">
-        <v>7869.476000000001</v>
+        <v>7964.129000000001</v>
       </c>
       <c r="F94">
-        <v>8708.076000000001</v>
+        <v>8802.729000000001</v>
       </c>
       <c r="G94">
         <v>134.6</v>
@@ -9132,37 +9132,37 @@
         <v>390.4</v>
       </c>
       <c r="M94">
-        <v>1748.5816608</v>
+        <v>1767.5879832</v>
       </c>
       <c r="N94">
-        <v>-1358.1816608</v>
+        <v>-1377.1879832</v>
       </c>
       <c r="O94">
-        <v>-380.2908650240001</v>
+        <v>-385.6126352960002</v>
       </c>
       <c r="P94">
-        <v>-977.8907957760002</v>
+        <v>-991.5753479040002</v>
       </c>
       <c r="Q94">
-        <v>-774.4907957760003</v>
+        <v>-788.1753479040002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3406707488162461</v>
+        <v>0.3827951415042814</v>
       </c>
       <c r="T94">
-        <v>6.809948009613074</v>
+        <v>7.782797725272086</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.06251466685861744</v>
+        <v>0.06184246613970757</v>
       </c>
       <c r="W94">
-        <v>0.1882470548947896</v>
+        <v>0.1883820327991467</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.223266667352205</v>
+        <v>0.2208659504989555</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9178,22 +9178,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2019909504085061</v>
+        <v>0.2035409504085062</v>
       </c>
       <c r="C95">
-        <v>-6725.952062236724</v>
+        <v>-6838.465006021661</v>
       </c>
       <c r="D95">
-        <v>1942.176937763277</v>
+        <v>1924.316993978341</v>
       </c>
       <c r="E95">
-        <v>7964.129000000001</v>
+        <v>8058.782000000001</v>
       </c>
       <c r="F95">
-        <v>8802.729000000001</v>
+        <v>8897.382000000001</v>
       </c>
       <c r="G95">
         <v>134.6</v>
@@ -9214,37 +9214,37 @@
         <v>390.4</v>
       </c>
       <c r="M95">
-        <v>1767.5879832</v>
+        <v>1786.5943056</v>
       </c>
       <c r="N95">
-        <v>-1377.1879832</v>
+        <v>-1396.1943056</v>
       </c>
       <c r="O95">
-        <v>-385.6126352960002</v>
+        <v>-390.9344055680002</v>
       </c>
       <c r="P95">
-        <v>-991.5753479040002</v>
+        <v>-1005.259900032</v>
       </c>
       <c r="Q95">
-        <v>-788.1753479040002</v>
+        <v>-801.8599000320004</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3827951415042814</v>
+        <v>0.4389609984216616</v>
       </c>
       <c r="T95">
-        <v>7.782797725272086</v>
+        <v>9.079930679484102</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.06184246613970757</v>
+        <v>0.06118456756375323</v>
       </c>
       <c r="W95">
-        <v>0.1883820327991467</v>
+        <v>0.1885141388331984</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2208659504989555</v>
+        <v>0.21851631272769</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9260,22 +9260,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2035409504085062</v>
+        <v>0.2050909504085061</v>
       </c>
       <c r="C96">
-        <v>-6838.465006021661</v>
+        <v>-6950.652468592439</v>
       </c>
       <c r="D96">
-        <v>1924.316993978341</v>
+        <v>1906.782531407563</v>
       </c>
       <c r="E96">
-        <v>8058.782000000001</v>
+        <v>8153.435000000001</v>
       </c>
       <c r="F96">
-        <v>8897.382000000001</v>
+        <v>8992.035000000002</v>
       </c>
       <c r="G96">
         <v>134.6</v>
@@ -9296,37 +9296,37 @@
         <v>390.4</v>
       </c>
       <c r="M96">
-        <v>1786.5943056</v>
+        <v>1805.600628</v>
       </c>
       <c r="N96">
-        <v>-1396.1943056</v>
+        <v>-1415.200628000001</v>
       </c>
       <c r="O96">
-        <v>-390.9344055680002</v>
+        <v>-396.2561758400002</v>
       </c>
       <c r="P96">
-        <v>-1005.259900032</v>
+        <v>-1018.94445216</v>
       </c>
       <c r="Q96">
-        <v>-801.8599000320004</v>
+        <v>-815.5444521600003</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4389609984216616</v>
+        <v>0.5175931981059942</v>
       </c>
       <c r="T96">
-        <v>9.079930679484102</v>
+        <v>10.89591681538093</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.06118456756375323</v>
+        <v>0.06054051948413477</v>
       </c>
       <c r="W96">
-        <v>0.1885141388331984</v>
+        <v>0.1886434636875857</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.21851631272769</v>
+        <v>0.2162161410147669</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9342,22 +9342,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2050909504085061</v>
+        <v>0.2066409504085062</v>
       </c>
       <c r="C97">
-        <v>-6950.652468592439</v>
+        <v>-7062.523267005812</v>
       </c>
       <c r="D97">
-        <v>1906.782531407563</v>
+        <v>1889.56473299419</v>
       </c>
       <c r="E97">
-        <v>8153.435000000001</v>
+        <v>8248.088000000002</v>
       </c>
       <c r="F97">
-        <v>8992.035000000002</v>
+        <v>9086.688000000002</v>
       </c>
       <c r="G97">
         <v>134.6</v>
@@ -9378,37 +9378,37 @@
         <v>390.4</v>
       </c>
       <c r="M97">
-        <v>1805.600628</v>
+        <v>1824.6069504</v>
       </c>
       <c r="N97">
-        <v>-1415.200628000001</v>
+        <v>-1434.206950400001</v>
       </c>
       <c r="O97">
-        <v>-396.2561758400002</v>
+        <v>-401.5779461120002</v>
       </c>
       <c r="P97">
-        <v>-1018.94445216</v>
+        <v>-1032.629004288</v>
       </c>
       <c r="Q97">
-        <v>-815.5444521600003</v>
+        <v>-829.2290042880005</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5175931981059942</v>
+        <v>0.6355414976324931</v>
       </c>
       <c r="T97">
-        <v>10.89591681538093</v>
+        <v>13.61989601922617</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.06054051948413477</v>
+        <v>0.05990988907284171</v>
       </c>
       <c r="W97">
-        <v>0.1886434636875857</v>
+        <v>0.1887700942741734</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2162161410147669</v>
+        <v>0.2139638895458631</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9424,22 +9424,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2066409504085061</v>
+        <v>0.2081909504085061</v>
       </c>
       <c r="C98">
-        <v>-7062.52326700581</v>
+        <v>-7174.085902704648</v>
       </c>
       <c r="D98">
-        <v>1889.56473299419</v>
+        <v>1872.655097295353</v>
       </c>
       <c r="E98">
-        <v>8248.088</v>
+        <v>8342.741</v>
       </c>
       <c r="F98">
-        <v>9086.688</v>
+        <v>9181.341</v>
       </c>
       <c r="G98">
         <v>134.6</v>
@@ -9460,37 +9460,37 @@
         <v>390.4</v>
       </c>
       <c r="M98">
-        <v>1824.6069504</v>
+        <v>1843.6132728</v>
       </c>
       <c r="N98">
-        <v>-1434.2069504</v>
+        <v>-1453.2132728</v>
       </c>
       <c r="O98">
-        <v>-401.5779461120001</v>
+        <v>-406.8997163840001</v>
       </c>
       <c r="P98">
-        <v>-1032.629004288</v>
+        <v>-1046.313556416</v>
       </c>
       <c r="Q98">
-        <v>-829.2290042880001</v>
+        <v>-842.913556416</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6355414976324915</v>
+        <v>0.832121996843322</v>
       </c>
       <c r="T98">
-        <v>13.61989601922613</v>
+        <v>18.15986135896818</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.05990988907284171</v>
+        <v>0.05929226135044128</v>
       </c>
       <c r="W98">
-        <v>0.1887700942741734</v>
+        <v>0.1888941139208314</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2139638895458633</v>
+        <v>0.2117580762515761</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9506,22 +9506,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2081909504085061</v>
+        <v>0.2097409504085062</v>
       </c>
       <c r="C99">
-        <v>-7174.085902704648</v>
+        <v>-7285.348575514749</v>
       </c>
       <c r="D99">
-        <v>1872.655097295353</v>
+        <v>1856.045424485252</v>
       </c>
       <c r="E99">
-        <v>8342.741</v>
+        <v>8437.394</v>
       </c>
       <c r="F99">
-        <v>9181.341</v>
+        <v>9275.994000000001</v>
       </c>
       <c r="G99">
         <v>134.6</v>
@@ -9542,37 +9542,37 @@
         <v>390.4</v>
       </c>
       <c r="M99">
-        <v>1843.6132728</v>
+        <v>1862.6195952</v>
       </c>
       <c r="N99">
-        <v>-1453.2132728</v>
+        <v>-1472.2195952</v>
       </c>
       <c r="O99">
-        <v>-406.8997163840001</v>
+        <v>-412.2214866560001</v>
       </c>
       <c r="P99">
-        <v>-1046.313556416</v>
+        <v>-1059.998108544</v>
       </c>
       <c r="Q99">
-        <v>-842.913556416</v>
+        <v>-856.5981085440002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.832121996843322</v>
+        <v>1.225282995264983</v>
       </c>
       <c r="T99">
-        <v>18.15986135896818</v>
+        <v>27.23979203845226</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.05929226135044128</v>
+        <v>0.05868723827543677</v>
       </c>
       <c r="W99">
-        <v>0.1888941139208314</v>
+        <v>0.1890156025542923</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2117580762515761</v>
+        <v>0.2095972795551314</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9588,22 +9588,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2097409504085062</v>
+        <v>0.2112909504085062</v>
       </c>
       <c r="C100">
-        <v>-7285.348575514749</v>
+        <v>-7396.31919690334</v>
       </c>
       <c r="D100">
-        <v>1856.045424485252</v>
+        <v>1839.727803096661</v>
       </c>
       <c r="E100">
-        <v>8437.394</v>
+        <v>8532.047</v>
       </c>
       <c r="F100">
-        <v>9275.994000000001</v>
+        <v>9370.647000000001</v>
       </c>
       <c r="G100">
         <v>134.6</v>
@@ -9624,37 +9624,37 @@
         <v>390.4</v>
       </c>
       <c r="M100">
-        <v>1862.6195952</v>
+        <v>1881.6259176</v>
       </c>
       <c r="N100">
-        <v>-1472.2195952</v>
+        <v>-1491.2259176</v>
       </c>
       <c r="O100">
-        <v>-412.2214866560001</v>
+        <v>-417.5432569280001</v>
       </c>
       <c r="P100">
-        <v>-1059.998108544</v>
+        <v>-1073.682660672</v>
       </c>
       <c r="Q100">
-        <v>-856.5981085440002</v>
+        <v>-870.2826606720001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.225282995264983</v>
+        <v>2.404765990529966</v>
       </c>
       <c r="T100">
-        <v>27.23979203845226</v>
+        <v>54.47958407690452</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.05868723827543677</v>
+        <v>0.0580944378888162</v>
       </c>
       <c r="W100">
-        <v>0.1890156025542923</v>
+        <v>0.1891346368719257</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9662,91 +9662,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2095972795551314</v>
+        <v>0.2074801353172008</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2112909504085062</v>
-      </c>
-      <c r="C101">
-        <v>-7396.31919690334</v>
-      </c>
-      <c r="D101">
-        <v>1839.727803096661</v>
-      </c>
-      <c r="E101">
-        <v>8532.047</v>
-      </c>
-      <c r="F101">
-        <v>9370.647000000001</v>
-      </c>
-      <c r="G101">
-        <v>134.6</v>
-      </c>
-      <c r="H101">
-        <v>8626.700000000001</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>593.8</v>
-      </c>
-      <c r="K101">
-        <v>203.4</v>
-      </c>
-      <c r="L101">
-        <v>390.4</v>
-      </c>
-      <c r="M101">
-        <v>1881.6259176</v>
-      </c>
-      <c r="N101">
-        <v>-1491.2259176</v>
-      </c>
-      <c r="O101">
-        <v>-417.5432569280001</v>
-      </c>
-      <c r="P101">
-        <v>-1073.682660672</v>
-      </c>
-      <c r="Q101">
-        <v>-870.2826606720001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.404765990529966</v>
-      </c>
-      <c r="T101">
-        <v>54.47958407690452</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.0580944378888162</v>
-      </c>
-      <c r="W101">
-        <v>0.1891346368719257</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2074801353172008</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
